--- a/docs/삼국지 약식체스.xlsx
+++ b/docs/삼국지 약식체스.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Hackers_IELTS_Listening_Basic_MP3_free\DGGL\Games\SamHero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Samchess\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C80B1F-8566-4715-BDFC-3BEBABD2E4AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9207FA55-1DDC-4B86-B19E-9564438C44C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-16320" yWindow="-16410" windowWidth="16440" windowHeight="28320" xr2:uid="{67B41BAA-AEF2-4AF0-8CD2-0E8DEEEF200D}"/>
   </bookViews>
@@ -1916,10 +1916,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>적군 1명을 지정. 그 적은 게임이 끝날 때 까지 time 100 마다 HP 1 감소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>모든 아군이 이번 게임에서 고유 스킬을 두 번 사용할 수 있음</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1993,6 +1989,10 @@
   </si>
   <si>
     <t>적의 SP 값을 1 내린다.</t>
+  </si>
+  <si>
+    <t>적군 1명을 지정. 그 적은 게임이 끝날 때 까지 time 200 마다 HP 1 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2164,7 +2164,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2220,9 +2220,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2820,7 +2817,7 @@
         <v>510</v>
       </c>
       <c r="E15" t="s">
-        <v>536</v>
+        <v>557</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
@@ -2939,7 +2936,7 @@
         <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
@@ -2956,7 +2953,7 @@
         <v>8</v>
       </c>
       <c r="E24" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
@@ -3041,7 +3038,7 @@
         <v>50</v>
       </c>
       <c r="E29" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
@@ -3136,13 +3133,13 @@
       <c r="B36" t="s">
         <v>176</v>
       </c>
-      <c r="C36" s="19" t="s">
+      <c r="C36" t="s">
         <v>236</v>
       </c>
-      <c r="D36" s="19" t="s">
+      <c r="D36" t="s">
         <v>237</v>
       </c>
-      <c r="E36" s="19" t="s">
+      <c r="E36" t="s">
         <v>527</v>
       </c>
     </row>
@@ -3153,13 +3150,13 @@
       <c r="B37" t="s">
         <v>188</v>
       </c>
-      <c r="C37" s="19" t="s">
+      <c r="C37" t="s">
         <v>236</v>
       </c>
-      <c r="D37" s="19" t="s">
+      <c r="D37" t="s">
         <v>237</v>
       </c>
-      <c r="E37" s="19" t="s">
+      <c r="E37" t="s">
         <v>527</v>
       </c>
     </row>
@@ -3170,14 +3167,14 @@
       <c r="B38" t="s">
         <v>159</v>
       </c>
-      <c r="C38" s="19" t="s">
+      <c r="C38" t="s">
         <v>236</v>
       </c>
-      <c r="D38" s="19" t="s">
+      <c r="D38" t="s">
         <v>237</v>
       </c>
-      <c r="E38" s="19" t="s">
-        <v>549</v>
+      <c r="E38" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
@@ -3187,14 +3184,14 @@
       <c r="B39" t="s">
         <v>164</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" t="s">
         <v>236</v>
       </c>
-      <c r="D39" s="19" t="s">
+      <c r="D39" t="s">
         <v>237</v>
       </c>
-      <c r="E39" s="19" t="s">
-        <v>549</v>
+      <c r="E39" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
@@ -3204,14 +3201,14 @@
       <c r="B40" t="s">
         <v>156</v>
       </c>
-      <c r="C40" s="19" t="s">
+      <c r="C40" t="s">
         <v>236</v>
       </c>
-      <c r="D40" s="19" t="s">
+      <c r="D40" t="s">
         <v>237</v>
       </c>
-      <c r="E40" s="19" t="s">
-        <v>549</v>
+      <c r="E40" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.45">
@@ -3221,14 +3218,14 @@
       <c r="B41" t="s">
         <v>147</v>
       </c>
-      <c r="C41" s="19" t="s">
+      <c r="C41" t="s">
         <v>236</v>
       </c>
-      <c r="D41" s="19" t="s">
+      <c r="D41" t="s">
         <v>237</v>
       </c>
-      <c r="E41" s="19" t="s">
-        <v>549</v>
+      <c r="E41" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
@@ -3238,14 +3235,14 @@
       <c r="B42" t="s">
         <v>141</v>
       </c>
-      <c r="C42" s="19" t="s">
+      <c r="C42" t="s">
         <v>236</v>
       </c>
-      <c r="D42" s="19" t="s">
+      <c r="D42" t="s">
         <v>237</v>
       </c>
-      <c r="E42" s="19" t="s">
-        <v>549</v>
+      <c r="E42" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
@@ -3255,14 +3252,14 @@
       <c r="B43" t="s">
         <v>217</v>
       </c>
-      <c r="C43" s="19" t="s">
+      <c r="C43" t="s">
         <v>236</v>
       </c>
-      <c r="D43" s="19" t="s">
+      <c r="D43" t="s">
         <v>237</v>
       </c>
-      <c r="E43" s="19" t="s">
-        <v>549</v>
+      <c r="E43" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
@@ -3272,14 +3269,14 @@
       <c r="B44" t="s">
         <v>227</v>
       </c>
-      <c r="C44" s="19" t="s">
+      <c r="C44" t="s">
         <v>236</v>
       </c>
-      <c r="D44" s="19" t="s">
+      <c r="D44" t="s">
         <v>237</v>
       </c>
-      <c r="E44" s="19" t="s">
-        <v>549</v>
+      <c r="E44" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
@@ -3289,14 +3286,14 @@
       <c r="B45" t="s">
         <v>214</v>
       </c>
-      <c r="C45" s="19" t="s">
+      <c r="C45" t="s">
         <v>236</v>
       </c>
-      <c r="D45" s="19" t="s">
+      <c r="D45" t="s">
         <v>237</v>
       </c>
-      <c r="E45" s="19" t="s">
-        <v>549</v>
+      <c r="E45" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
@@ -3306,13 +3303,13 @@
       <c r="B46" t="s">
         <v>167</v>
       </c>
-      <c r="C46" s="19" t="s">
+      <c r="C46" t="s">
         <v>238</v>
       </c>
-      <c r="D46" s="19" t="s">
+      <c r="D46" t="s">
         <v>239</v>
       </c>
-      <c r="E46" s="19" t="s">
+      <c r="E46" t="s">
         <v>528</v>
       </c>
     </row>
@@ -3323,13 +3320,13 @@
       <c r="B47" t="s">
         <v>190</v>
       </c>
-      <c r="C47" s="19" t="s">
+      <c r="C47" t="s">
         <v>238</v>
       </c>
-      <c r="D47" s="19" t="s">
+      <c r="D47" t="s">
         <v>239</v>
       </c>
-      <c r="E47" s="19" t="s">
+      <c r="E47" t="s">
         <v>528</v>
       </c>
     </row>
@@ -3340,14 +3337,14 @@
       <c r="B48" t="s">
         <v>191</v>
       </c>
-      <c r="C48" s="19" t="s">
+      <c r="C48" t="s">
         <v>238</v>
       </c>
-      <c r="D48" s="19" t="s">
+      <c r="D48" t="s">
         <v>239</v>
       </c>
-      <c r="E48" s="19" t="s">
-        <v>550</v>
+      <c r="E48" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
@@ -3357,14 +3354,14 @@
       <c r="B49" t="s">
         <v>161</v>
       </c>
-      <c r="C49" s="19" t="s">
+      <c r="C49" t="s">
         <v>238</v>
       </c>
-      <c r="D49" s="19" t="s">
+      <c r="D49" t="s">
         <v>239</v>
       </c>
-      <c r="E49" s="19" t="s">
-        <v>550</v>
+      <c r="E49" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
@@ -3374,14 +3371,14 @@
       <c r="B50" t="s">
         <v>168</v>
       </c>
-      <c r="C50" s="19" t="s">
+      <c r="C50" t="s">
         <v>238</v>
       </c>
-      <c r="D50" s="19" t="s">
+      <c r="D50" t="s">
         <v>239</v>
       </c>
-      <c r="E50" s="19" t="s">
-        <v>550</v>
+      <c r="E50" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
@@ -3391,14 +3388,14 @@
       <c r="B51" t="s">
         <v>142</v>
       </c>
-      <c r="C51" s="19" t="s">
+      <c r="C51" t="s">
         <v>238</v>
       </c>
-      <c r="D51" s="19" t="s">
+      <c r="D51" t="s">
         <v>239</v>
       </c>
-      <c r="E51" s="19" t="s">
-        <v>550</v>
+      <c r="E51" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
@@ -3430,13 +3427,13 @@
       <c r="B54" t="s">
         <v>226</v>
       </c>
-      <c r="C54" s="19" t="s">
+      <c r="C54" t="s">
         <v>240</v>
       </c>
-      <c r="D54" s="19" t="s">
+      <c r="D54" t="s">
         <v>241</v>
       </c>
-      <c r="E54" s="19" t="s">
+      <c r="E54" t="s">
         <v>529</v>
       </c>
     </row>
@@ -3447,13 +3444,13 @@
       <c r="B55" t="s">
         <v>152</v>
       </c>
-      <c r="C55" s="19" t="s">
+      <c r="C55" t="s">
         <v>240</v>
       </c>
-      <c r="D55" s="19" t="s">
+      <c r="D55" t="s">
         <v>241</v>
       </c>
-      <c r="E55" s="19" t="s">
+      <c r="E55" t="s">
         <v>529</v>
       </c>
     </row>
@@ -3464,14 +3461,14 @@
       <c r="B56" t="s">
         <v>212</v>
       </c>
-      <c r="C56" s="19" t="s">
+      <c r="C56" t="s">
         <v>240</v>
       </c>
-      <c r="D56" s="19" t="s">
+      <c r="D56" t="s">
         <v>241</v>
       </c>
-      <c r="E56" s="19" t="s">
-        <v>551</v>
+      <c r="E56" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
@@ -3481,14 +3478,14 @@
       <c r="B57" t="s">
         <v>208</v>
       </c>
-      <c r="C57" s="19" t="s">
+      <c r="C57" t="s">
         <v>240</v>
       </c>
-      <c r="D57" s="19" t="s">
+      <c r="D57" t="s">
         <v>241</v>
       </c>
-      <c r="E57" s="19" t="s">
-        <v>551</v>
+      <c r="E57" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
@@ -3498,14 +3495,14 @@
       <c r="B58" t="s">
         <v>163</v>
       </c>
-      <c r="C58" s="19" t="s">
+      <c r="C58" t="s">
         <v>240</v>
       </c>
-      <c r="D58" s="19" t="s">
+      <c r="D58" t="s">
         <v>241</v>
       </c>
-      <c r="E58" s="19" t="s">
-        <v>551</v>
+      <c r="E58" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">
@@ -3515,14 +3512,14 @@
       <c r="B59" t="s">
         <v>193</v>
       </c>
-      <c r="C59" s="19" t="s">
+      <c r="C59" t="s">
         <v>240</v>
       </c>
-      <c r="D59" s="19" t="s">
+      <c r="D59" t="s">
         <v>241</v>
       </c>
-      <c r="E59" s="19" t="s">
-        <v>551</v>
+      <c r="E59" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
@@ -3532,14 +3529,14 @@
       <c r="B60" t="s">
         <v>213</v>
       </c>
-      <c r="C60" s="19" t="s">
+      <c r="C60" t="s">
         <v>240</v>
       </c>
-      <c r="D60" s="19" t="s">
+      <c r="D60" t="s">
         <v>241</v>
       </c>
-      <c r="E60" s="19" t="s">
-        <v>551</v>
+      <c r="E60" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
@@ -3549,14 +3546,14 @@
       <c r="B61" t="s">
         <v>148</v>
       </c>
-      <c r="C61" s="19" t="s">
+      <c r="C61" t="s">
         <v>240</v>
       </c>
-      <c r="D61" s="19" t="s">
+      <c r="D61" t="s">
         <v>241</v>
       </c>
-      <c r="E61" s="19" t="s">
-        <v>551</v>
+      <c r="E61" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">
@@ -3566,14 +3563,14 @@
       <c r="B62" t="s">
         <v>189</v>
       </c>
-      <c r="C62" s="19" t="s">
+      <c r="C62" t="s">
         <v>240</v>
       </c>
-      <c r="D62" s="19" t="s">
+      <c r="D62" t="s">
         <v>241</v>
       </c>
-      <c r="E62" s="19" t="s">
-        <v>551</v>
+      <c r="E62" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.45">
@@ -3583,14 +3580,14 @@
       <c r="B63" t="s">
         <v>140</v>
       </c>
-      <c r="C63" s="19" t="s">
+      <c r="C63" t="s">
         <v>240</v>
       </c>
-      <c r="D63" s="19" t="s">
+      <c r="D63" t="s">
         <v>241</v>
       </c>
-      <c r="E63" s="19" t="s">
-        <v>551</v>
+      <c r="E63" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.45">
@@ -3600,14 +3597,14 @@
       <c r="B64" t="s">
         <v>195</v>
       </c>
-      <c r="C64" s="19" t="s">
+      <c r="C64" t="s">
         <v>240</v>
       </c>
-      <c r="D64" s="19" t="s">
+      <c r="D64" t="s">
         <v>241</v>
       </c>
-      <c r="E64" s="19" t="s">
-        <v>551</v>
+      <c r="E64" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.45">
@@ -3617,14 +3614,14 @@
       <c r="B65" t="s">
         <v>146</v>
       </c>
-      <c r="C65" s="19" t="s">
+      <c r="C65" t="s">
         <v>240</v>
       </c>
-      <c r="D65" s="19" t="s">
+      <c r="D65" t="s">
         <v>241</v>
       </c>
-      <c r="E65" s="19" t="s">
-        <v>551</v>
+      <c r="E65" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.45">
@@ -3634,14 +3631,14 @@
       <c r="B66" t="s">
         <v>145</v>
       </c>
-      <c r="C66" s="19" t="s">
+      <c r="C66" t="s">
         <v>240</v>
       </c>
-      <c r="D66" s="19" t="s">
+      <c r="D66" t="s">
         <v>241</v>
       </c>
-      <c r="E66" s="19" t="s">
-        <v>551</v>
+      <c r="E66" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.45">
@@ -3651,14 +3648,14 @@
       <c r="B67" t="s">
         <v>198</v>
       </c>
-      <c r="C67" s="19" t="s">
+      <c r="C67" t="s">
         <v>240</v>
       </c>
-      <c r="D67" s="19" t="s">
+      <c r="D67" t="s">
         <v>241</v>
       </c>
-      <c r="E67" s="19" t="s">
-        <v>551</v>
+      <c r="E67" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.45">
@@ -3668,13 +3665,13 @@
       <c r="B68" t="s">
         <v>225</v>
       </c>
-      <c r="C68" s="19" t="s">
+      <c r="C68" t="s">
         <v>243</v>
       </c>
-      <c r="D68" s="19" t="s">
+      <c r="D68" t="s">
         <v>244</v>
       </c>
-      <c r="E68" s="19" t="s">
+      <c r="E68" t="s">
         <v>530</v>
       </c>
     </row>
@@ -3685,13 +3682,13 @@
       <c r="B69" t="s">
         <v>224</v>
       </c>
-      <c r="C69" s="19" t="s">
+      <c r="C69" t="s">
         <v>243</v>
       </c>
-      <c r="D69" s="19" t="s">
+      <c r="D69" t="s">
         <v>244</v>
       </c>
-      <c r="E69" s="19" t="s">
+      <c r="E69" t="s">
         <v>530</v>
       </c>
     </row>
@@ -3702,14 +3699,14 @@
       <c r="B70" t="s">
         <v>201</v>
       </c>
-      <c r="C70" s="19" t="s">
+      <c r="C70" t="s">
         <v>243</v>
       </c>
-      <c r="D70" s="19" t="s">
+      <c r="D70" t="s">
         <v>244</v>
       </c>
-      <c r="E70" s="19" t="s">
-        <v>552</v>
+      <c r="E70" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
@@ -3719,14 +3716,14 @@
       <c r="B71" t="s">
         <v>508</v>
       </c>
-      <c r="C71" s="19" t="s">
+      <c r="C71" t="s">
         <v>243</v>
       </c>
-      <c r="D71" s="19" t="s">
+      <c r="D71" t="s">
         <v>244</v>
       </c>
-      <c r="E71" s="19" t="s">
-        <v>552</v>
+      <c r="E71" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.45">
@@ -3736,14 +3733,14 @@
       <c r="B72" t="s">
         <v>232</v>
       </c>
-      <c r="C72" s="19" t="s">
+      <c r="C72" t="s">
         <v>243</v>
       </c>
-      <c r="D72" s="19" t="s">
+      <c r="D72" t="s">
         <v>244</v>
       </c>
-      <c r="E72" s="19" t="s">
-        <v>552</v>
+      <c r="E72" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.45">
@@ -3753,14 +3750,14 @@
       <c r="B73" t="s">
         <v>207</v>
       </c>
-      <c r="C73" s="19" t="s">
+      <c r="C73" t="s">
         <v>243</v>
       </c>
-      <c r="D73" s="19" t="s">
+      <c r="D73" t="s">
         <v>244</v>
       </c>
-      <c r="E73" s="19" t="s">
-        <v>552</v>
+      <c r="E73" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.45">
@@ -3770,14 +3767,14 @@
       <c r="B74" t="s">
         <v>162</v>
       </c>
-      <c r="C74" s="19" t="s">
+      <c r="C74" t="s">
         <v>243</v>
       </c>
-      <c r="D74" s="19" t="s">
+      <c r="D74" t="s">
         <v>244</v>
       </c>
-      <c r="E74" s="19" t="s">
-        <v>552</v>
+      <c r="E74" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.45">
@@ -3787,14 +3784,14 @@
       <c r="B75" t="s">
         <v>204</v>
       </c>
-      <c r="C75" s="19" t="s">
+      <c r="C75" t="s">
         <v>243</v>
       </c>
-      <c r="D75" s="19" t="s">
+      <c r="D75" t="s">
         <v>244</v>
       </c>
-      <c r="E75" s="19" t="s">
-        <v>552</v>
+      <c r="E75" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
@@ -3804,14 +3801,14 @@
       <c r="B76" t="s">
         <v>205</v>
       </c>
-      <c r="C76" s="19" t="s">
+      <c r="C76" t="s">
         <v>243</v>
       </c>
-      <c r="D76" s="19" t="s">
+      <c r="D76" t="s">
         <v>244</v>
       </c>
-      <c r="E76" s="19" t="s">
-        <v>552</v>
+      <c r="E76" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
@@ -3821,14 +3818,14 @@
       <c r="B77" t="s">
         <v>230</v>
       </c>
-      <c r="C77" s="19" t="s">
+      <c r="C77" t="s">
         <v>243</v>
       </c>
-      <c r="D77" s="19" t="s">
+      <c r="D77" t="s">
         <v>244</v>
       </c>
-      <c r="E77" s="19" t="s">
-        <v>552</v>
+      <c r="E77" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.45">
@@ -3860,13 +3857,13 @@
       <c r="B80" t="s">
         <v>215</v>
       </c>
-      <c r="C80" s="19" t="s">
+      <c r="C80" t="s">
         <v>245</v>
       </c>
-      <c r="D80" s="19" t="s">
+      <c r="D80" t="s">
         <v>246</v>
       </c>
-      <c r="E80" s="19" t="s">
+      <c r="E80" t="s">
         <v>253</v>
       </c>
     </row>
@@ -3877,13 +3874,13 @@
       <c r="B81" t="s">
         <v>187</v>
       </c>
-      <c r="C81" s="19" t="s">
+      <c r="C81" t="s">
         <v>245</v>
       </c>
-      <c r="D81" s="19" t="s">
+      <c r="D81" t="s">
         <v>246</v>
       </c>
-      <c r="E81" s="19" t="s">
+      <c r="E81" t="s">
         <v>253</v>
       </c>
     </row>
@@ -3894,14 +3891,14 @@
       <c r="B82" t="s">
         <v>154</v>
       </c>
-      <c r="C82" s="19" t="s">
+      <c r="C82" t="s">
         <v>245</v>
       </c>
-      <c r="D82" s="19" t="s">
+      <c r="D82" t="s">
         <v>246</v>
       </c>
-      <c r="E82" s="19" t="s">
-        <v>553</v>
+      <c r="E82" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.45">
@@ -3911,14 +3908,14 @@
       <c r="B83" t="s">
         <v>231</v>
       </c>
-      <c r="C83" s="19" t="s">
+      <c r="C83" t="s">
         <v>245</v>
       </c>
-      <c r="D83" s="19" t="s">
+      <c r="D83" t="s">
         <v>246</v>
       </c>
-      <c r="E83" s="19" t="s">
-        <v>553</v>
+      <c r="E83" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.45">
@@ -3928,14 +3925,14 @@
       <c r="B84" t="s">
         <v>182</v>
       </c>
-      <c r="C84" s="19" t="s">
+      <c r="C84" t="s">
         <v>245</v>
       </c>
-      <c r="D84" s="19" t="s">
+      <c r="D84" t="s">
         <v>246</v>
       </c>
-      <c r="E84" s="19" t="s">
-        <v>553</v>
+      <c r="E84" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.45">
@@ -3945,14 +3942,14 @@
       <c r="B85" t="s">
         <v>144</v>
       </c>
-      <c r="C85" s="19" t="s">
+      <c r="C85" t="s">
         <v>245</v>
       </c>
-      <c r="D85" s="19" t="s">
+      <c r="D85" t="s">
         <v>246</v>
       </c>
-      <c r="E85" s="19" t="s">
-        <v>553</v>
+      <c r="E85" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.45">
@@ -3962,14 +3959,14 @@
       <c r="B86" t="s">
         <v>222</v>
       </c>
-      <c r="C86" s="19" t="s">
+      <c r="C86" t="s">
         <v>245</v>
       </c>
-      <c r="D86" s="19" t="s">
+      <c r="D86" t="s">
         <v>246</v>
       </c>
-      <c r="E86" s="19" t="s">
-        <v>553</v>
+      <c r="E86" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.45">
@@ -3979,14 +3976,14 @@
       <c r="B87" t="s">
         <v>155</v>
       </c>
-      <c r="C87" s="19" t="s">
+      <c r="C87" t="s">
         <v>245</v>
       </c>
-      <c r="D87" s="19" t="s">
+      <c r="D87" t="s">
         <v>246</v>
       </c>
-      <c r="E87" s="19" t="s">
-        <v>553</v>
+      <c r="E87" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.45">
@@ -3996,14 +3993,14 @@
       <c r="B88" t="s">
         <v>202</v>
       </c>
-      <c r="C88" s="19" t="s">
+      <c r="C88" t="s">
         <v>245</v>
       </c>
-      <c r="D88" s="19" t="s">
+      <c r="D88" t="s">
         <v>246</v>
       </c>
-      <c r="E88" s="19" t="s">
-        <v>553</v>
+      <c r="E88" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.45">
@@ -4013,13 +4010,13 @@
       <c r="B89" t="s">
         <v>196</v>
       </c>
-      <c r="C89" s="19" t="s">
+      <c r="C89" t="s">
         <v>255</v>
       </c>
-      <c r="D89" s="19" t="s">
+      <c r="D89" t="s">
         <v>256</v>
       </c>
-      <c r="E89" s="19" t="s">
+      <c r="E89" t="s">
         <v>531</v>
       </c>
     </row>
@@ -4030,13 +4027,13 @@
       <c r="B90" t="s">
         <v>180</v>
       </c>
-      <c r="C90" s="19" t="s">
+      <c r="C90" t="s">
         <v>255</v>
       </c>
-      <c r="D90" s="19" t="s">
+      <c r="D90" t="s">
         <v>256</v>
       </c>
-      <c r="E90" s="19" t="s">
+      <c r="E90" t="s">
         <v>531</v>
       </c>
     </row>
@@ -4047,14 +4044,14 @@
       <c r="B91" t="s">
         <v>210</v>
       </c>
-      <c r="C91" s="19" t="s">
+      <c r="C91" t="s">
         <v>255</v>
       </c>
-      <c r="D91" s="19" t="s">
+      <c r="D91" t="s">
         <v>256</v>
       </c>
-      <c r="E91" s="19" t="s">
-        <v>554</v>
+      <c r="E91" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.45">
@@ -4064,14 +4061,14 @@
       <c r="B92" t="s">
         <v>200</v>
       </c>
-      <c r="C92" s="19" t="s">
+      <c r="C92" t="s">
         <v>255</v>
       </c>
-      <c r="D92" s="19" t="s">
+      <c r="D92" t="s">
         <v>256</v>
       </c>
-      <c r="E92" s="19" t="s">
-        <v>554</v>
+      <c r="E92" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.45">
@@ -4081,14 +4078,14 @@
       <c r="B93" t="s">
         <v>149</v>
       </c>
-      <c r="C93" s="19" t="s">
+      <c r="C93" t="s">
         <v>255</v>
       </c>
-      <c r="D93" s="19" t="s">
+      <c r="D93" t="s">
         <v>256</v>
       </c>
-      <c r="E93" s="19" t="s">
-        <v>554</v>
+      <c r="E93" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.45">
@@ -4098,14 +4095,14 @@
       <c r="B94" t="s">
         <v>179</v>
       </c>
-      <c r="C94" s="19" t="s">
+      <c r="C94" t="s">
         <v>255</v>
       </c>
-      <c r="D94" s="19" t="s">
+      <c r="D94" t="s">
         <v>256</v>
       </c>
-      <c r="E94" s="19" t="s">
-        <v>554</v>
+      <c r="E94" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.45">
@@ -4115,14 +4112,14 @@
       <c r="B95" t="s">
         <v>219</v>
       </c>
-      <c r="C95" s="19" t="s">
+      <c r="C95" t="s">
         <v>255</v>
       </c>
-      <c r="D95" s="19" t="s">
+      <c r="D95" t="s">
         <v>256</v>
       </c>
-      <c r="E95" s="19" t="s">
-        <v>554</v>
+      <c r="E95" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.45">
@@ -4132,14 +4129,14 @@
       <c r="B96" t="s">
         <v>175</v>
       </c>
-      <c r="C96" s="19" t="s">
+      <c r="C96" t="s">
         <v>255</v>
       </c>
-      <c r="D96" s="19" t="s">
+      <c r="D96" t="s">
         <v>256</v>
       </c>
-      <c r="E96" s="19" t="s">
-        <v>554</v>
+      <c r="E96" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.45">
@@ -4149,14 +4146,14 @@
       <c r="B97" t="s">
         <v>181</v>
       </c>
-      <c r="C97" s="19" t="s">
+      <c r="C97" t="s">
         <v>255</v>
       </c>
-      <c r="D97" s="19" t="s">
+      <c r="D97" t="s">
         <v>256</v>
       </c>
-      <c r="E97" s="19" t="s">
-        <v>554</v>
+      <c r="E97" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.45">
@@ -4166,14 +4163,14 @@
       <c r="B98" t="s">
         <v>220</v>
       </c>
-      <c r="C98" s="19" t="s">
+      <c r="C98" t="s">
         <v>255</v>
       </c>
-      <c r="D98" s="19" t="s">
+      <c r="D98" t="s">
         <v>256</v>
       </c>
-      <c r="E98" s="19" t="s">
-        <v>554</v>
+      <c r="E98" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.45">
@@ -4205,13 +4202,13 @@
       <c r="B101" t="s">
         <v>203</v>
       </c>
-      <c r="C101" s="19" t="s">
+      <c r="C101" t="s">
         <v>258</v>
       </c>
-      <c r="D101" s="19" t="s">
+      <c r="D101" t="s">
         <v>257</v>
       </c>
-      <c r="E101" s="19" t="s">
+      <c r="E101" t="s">
         <v>254</v>
       </c>
     </row>
@@ -4222,13 +4219,13 @@
       <c r="B102" t="s">
         <v>173</v>
       </c>
-      <c r="C102" s="19" t="s">
+      <c r="C102" t="s">
         <v>258</v>
       </c>
-      <c r="D102" s="19" t="s">
+      <c r="D102" t="s">
         <v>257</v>
       </c>
-      <c r="E102" s="19" t="s">
+      <c r="E102" t="s">
         <v>254</v>
       </c>
     </row>
@@ -4239,14 +4236,14 @@
       <c r="B103" t="s">
         <v>228</v>
       </c>
-      <c r="C103" s="19" t="s">
+      <c r="C103" t="s">
         <v>258</v>
       </c>
-      <c r="D103" s="19" t="s">
+      <c r="D103" t="s">
         <v>257</v>
       </c>
-      <c r="E103" s="19" t="s">
-        <v>555</v>
+      <c r="E103" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.45">
@@ -4256,14 +4253,14 @@
       <c r="B104" t="s">
         <v>170</v>
       </c>
-      <c r="C104" s="19" t="s">
+      <c r="C104" t="s">
         <v>258</v>
       </c>
-      <c r="D104" s="19" t="s">
+      <c r="D104" t="s">
         <v>257</v>
       </c>
-      <c r="E104" s="19" t="s">
-        <v>555</v>
+      <c r="E104" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.45">
@@ -4273,14 +4270,14 @@
       <c r="B105" t="s">
         <v>153</v>
       </c>
-      <c r="C105" s="19" t="s">
+      <c r="C105" t="s">
         <v>258</v>
       </c>
-      <c r="D105" s="19" t="s">
+      <c r="D105" t="s">
         <v>257</v>
       </c>
-      <c r="E105" s="19" t="s">
-        <v>555</v>
+      <c r="E105" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.45">
@@ -4290,14 +4287,14 @@
       <c r="B106" t="s">
         <v>150</v>
       </c>
-      <c r="C106" s="19" t="s">
+      <c r="C106" t="s">
         <v>258</v>
       </c>
-      <c r="D106" s="19" t="s">
+      <c r="D106" t="s">
         <v>257</v>
       </c>
-      <c r="E106" s="19" t="s">
-        <v>555</v>
+      <c r="E106" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.45">
@@ -4307,14 +4304,14 @@
       <c r="B107" t="s">
         <v>185</v>
       </c>
-      <c r="C107" s="19" t="s">
+      <c r="C107" t="s">
         <v>258</v>
       </c>
-      <c r="D107" s="19" t="s">
+      <c r="D107" t="s">
         <v>257</v>
       </c>
-      <c r="E107" s="19" t="s">
-        <v>555</v>
+      <c r="E107" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.45">
@@ -4324,14 +4321,14 @@
       <c r="B108" t="s">
         <v>165</v>
       </c>
-      <c r="C108" s="19" t="s">
+      <c r="C108" t="s">
         <v>258</v>
       </c>
-      <c r="D108" s="19" t="s">
+      <c r="D108" t="s">
         <v>257</v>
       </c>
-      <c r="E108" s="19" t="s">
-        <v>555</v>
+      <c r="E108" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.45">
@@ -4341,14 +4338,14 @@
       <c r="B109" t="s">
         <v>216</v>
       </c>
-      <c r="C109" s="19" t="s">
+      <c r="C109" t="s">
         <v>258</v>
       </c>
-      <c r="D109" s="19" t="s">
+      <c r="D109" t="s">
         <v>257</v>
       </c>
-      <c r="E109" s="19" t="s">
-        <v>555</v>
+      <c r="E109" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.45">
@@ -4358,14 +4355,14 @@
       <c r="B110" t="s">
         <v>192</v>
       </c>
-      <c r="C110" s="19" t="s">
+      <c r="C110" t="s">
         <v>258</v>
       </c>
-      <c r="D110" s="19" t="s">
+      <c r="D110" t="s">
         <v>257</v>
       </c>
-      <c r="E110" s="19" t="s">
-        <v>555</v>
+      <c r="E110" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.45">
@@ -4375,14 +4372,14 @@
       <c r="B111" t="s">
         <v>151</v>
       </c>
-      <c r="C111" s="19" t="s">
+      <c r="C111" t="s">
         <v>258</v>
       </c>
-      <c r="D111" s="19" t="s">
+      <c r="D111" t="s">
         <v>257</v>
       </c>
-      <c r="E111" s="19" t="s">
-        <v>555</v>
+      <c r="E111" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.45">
@@ -4392,14 +4389,14 @@
       <c r="B112" t="s">
         <v>509</v>
       </c>
-      <c r="C112" s="19" t="s">
+      <c r="C112" t="s">
         <v>258</v>
       </c>
-      <c r="D112" s="19" t="s">
+      <c r="D112" t="s">
         <v>257</v>
       </c>
-      <c r="E112" s="19" t="s">
-        <v>555</v>
+      <c r="E112" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.45">
@@ -4409,14 +4406,14 @@
       <c r="B113" t="s">
         <v>177</v>
       </c>
-      <c r="C113" s="19" t="s">
+      <c r="C113" t="s">
         <v>258</v>
       </c>
-      <c r="D113" s="19" t="s">
+      <c r="D113" t="s">
         <v>257</v>
       </c>
-      <c r="E113" s="19" t="s">
-        <v>555</v>
+      <c r="E113" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.45">
@@ -4426,13 +4423,13 @@
       <c r="B114" t="s">
         <v>233</v>
       </c>
-      <c r="C114" s="19" t="s">
+      <c r="C114" t="s">
         <v>249</v>
       </c>
-      <c r="D114" s="19" t="s">
+      <c r="D114" t="s">
         <v>250</v>
       </c>
-      <c r="E114" s="19" t="s">
+      <c r="E114" t="s">
         <v>251</v>
       </c>
     </row>
@@ -4443,13 +4440,13 @@
       <c r="B115" t="s">
         <v>206</v>
       </c>
-      <c r="C115" s="19" t="s">
+      <c r="C115" t="s">
         <v>249</v>
       </c>
-      <c r="D115" s="19" t="s">
+      <c r="D115" t="s">
         <v>250</v>
       </c>
-      <c r="E115" s="19" t="s">
+      <c r="E115" t="s">
         <v>251</v>
       </c>
     </row>
@@ -4460,14 +4457,14 @@
       <c r="B116" t="s">
         <v>194</v>
       </c>
-      <c r="C116" s="19" t="s">
+      <c r="C116" t="s">
         <v>249</v>
       </c>
-      <c r="D116" s="19" t="s">
+      <c r="D116" t="s">
         <v>250</v>
       </c>
-      <c r="E116" s="19" t="s">
-        <v>556</v>
+      <c r="E116" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.45">
@@ -4477,14 +4474,14 @@
       <c r="B117" t="s">
         <v>178</v>
       </c>
-      <c r="C117" s="19" t="s">
+      <c r="C117" t="s">
         <v>249</v>
       </c>
-      <c r="D117" s="19" t="s">
+      <c r="D117" t="s">
         <v>250</v>
       </c>
-      <c r="E117" s="19" t="s">
-        <v>556</v>
+      <c r="E117" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.45">
@@ -4494,14 +4491,14 @@
       <c r="B118" t="s">
         <v>223</v>
       </c>
-      <c r="C118" s="19" t="s">
+      <c r="C118" t="s">
         <v>249</v>
       </c>
-      <c r="D118" s="19" t="s">
+      <c r="D118" t="s">
         <v>250</v>
       </c>
-      <c r="E118" s="19" t="s">
-        <v>556</v>
+      <c r="E118" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.45">
@@ -4511,14 +4508,14 @@
       <c r="B119" t="s">
         <v>143</v>
       </c>
-      <c r="C119" s="19" t="s">
+      <c r="C119" t="s">
         <v>249</v>
       </c>
-      <c r="D119" s="19" t="s">
+      <c r="D119" t="s">
         <v>250</v>
       </c>
-      <c r="E119" s="19" t="s">
-        <v>556</v>
+      <c r="E119" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.45">
@@ -4528,14 +4525,14 @@
       <c r="B120" t="s">
         <v>169</v>
       </c>
-      <c r="C120" s="19" t="s">
+      <c r="C120" t="s">
         <v>249</v>
       </c>
-      <c r="D120" s="19" t="s">
+      <c r="D120" t="s">
         <v>250</v>
       </c>
-      <c r="E120" s="19" t="s">
-        <v>556</v>
+      <c r="E120" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.45">
@@ -4545,14 +4542,14 @@
       <c r="B121" t="s">
         <v>166</v>
       </c>
-      <c r="C121" s="19" t="s">
+      <c r="C121" t="s">
         <v>249</v>
       </c>
-      <c r="D121" s="19" t="s">
+      <c r="D121" t="s">
         <v>250</v>
       </c>
-      <c r="E121" s="19" t="s">
-        <v>556</v>
+      <c r="E121" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.45">
@@ -4562,14 +4559,14 @@
       <c r="B122" t="s">
         <v>186</v>
       </c>
-      <c r="C122" s="19" t="s">
+      <c r="C122" t="s">
         <v>249</v>
       </c>
-      <c r="D122" s="19" t="s">
+      <c r="D122" t="s">
         <v>250</v>
       </c>
-      <c r="E122" s="19" t="s">
-        <v>556</v>
+      <c r="E122" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.45">
@@ -4579,14 +4576,14 @@
       <c r="B123" t="s">
         <v>199</v>
       </c>
-      <c r="C123" s="19" t="s">
+      <c r="C123" t="s">
         <v>249</v>
       </c>
-      <c r="D123" s="19" t="s">
+      <c r="D123" t="s">
         <v>250</v>
       </c>
-      <c r="E123" s="19" t="s">
-        <v>556</v>
+      <c r="E123" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.45">
@@ -4596,14 +4593,14 @@
       <c r="B124" t="s">
         <v>157</v>
       </c>
-      <c r="C124" s="19" t="s">
+      <c r="C124" t="s">
         <v>249</v>
       </c>
-      <c r="D124" s="19" t="s">
+      <c r="D124" t="s">
         <v>250</v>
       </c>
-      <c r="E124" s="19" t="s">
-        <v>556</v>
+      <c r="E124" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.45">
@@ -4613,14 +4610,14 @@
       <c r="B125" t="s">
         <v>158</v>
       </c>
-      <c r="C125" s="19" t="s">
+      <c r="C125" t="s">
         <v>249</v>
       </c>
-      <c r="D125" s="19" t="s">
+      <c r="D125" t="s">
         <v>250</v>
       </c>
-      <c r="E125" s="19" t="s">
-        <v>556</v>
+      <c r="E125" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.45">
@@ -4652,13 +4649,13 @@
       <c r="B128" t="s">
         <v>197</v>
       </c>
-      <c r="C128" s="19" t="s">
+      <c r="C128" t="s">
         <v>261</v>
       </c>
-      <c r="D128" s="19" t="s">
+      <c r="D128" t="s">
         <v>260</v>
       </c>
-      <c r="E128" s="19" t="s">
+      <c r="E128" t="s">
         <v>259</v>
       </c>
     </row>
@@ -4669,13 +4666,13 @@
       <c r="B129" t="s">
         <v>211</v>
       </c>
-      <c r="C129" s="19" t="s">
+      <c r="C129" t="s">
         <v>261</v>
       </c>
-      <c r="D129" s="19" t="s">
+      <c r="D129" t="s">
         <v>260</v>
       </c>
-      <c r="E129" s="19" t="s">
+      <c r="E129" t="s">
         <v>259</v>
       </c>
     </row>
@@ -4686,14 +4683,14 @@
       <c r="B130" t="s">
         <v>184</v>
       </c>
-      <c r="C130" s="19" t="s">
+      <c r="C130" t="s">
         <v>261</v>
       </c>
-      <c r="D130" s="19" t="s">
+      <c r="D130" t="s">
         <v>260</v>
       </c>
-      <c r="E130" s="19" t="s">
-        <v>557</v>
+      <c r="E130" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.45">
@@ -4703,14 +4700,14 @@
       <c r="B131" t="s">
         <v>229</v>
       </c>
-      <c r="C131" s="19" t="s">
+      <c r="C131" t="s">
         <v>261</v>
       </c>
-      <c r="D131" s="19" t="s">
+      <c r="D131" t="s">
         <v>260</v>
       </c>
-      <c r="E131" s="19" t="s">
-        <v>557</v>
+      <c r="E131" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.45">
@@ -4720,14 +4717,14 @@
       <c r="B132" t="s">
         <v>172</v>
       </c>
-      <c r="C132" s="19" t="s">
+      <c r="C132" t="s">
         <v>261</v>
       </c>
-      <c r="D132" s="19" t="s">
+      <c r="D132" t="s">
         <v>260</v>
       </c>
-      <c r="E132" s="19" t="s">
-        <v>557</v>
+      <c r="E132" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.45">
@@ -4737,14 +4734,14 @@
       <c r="B133" t="s">
         <v>221</v>
       </c>
-      <c r="C133" s="19" t="s">
+      <c r="C133" t="s">
         <v>261</v>
       </c>
-      <c r="D133" s="19" t="s">
+      <c r="D133" t="s">
         <v>260</v>
       </c>
-      <c r="E133" s="19" t="s">
-        <v>557</v>
+      <c r="E133" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.45">
@@ -4754,14 +4751,14 @@
       <c r="B134" t="s">
         <v>218</v>
       </c>
-      <c r="C134" s="19" t="s">
+      <c r="C134" t="s">
         <v>261</v>
       </c>
-      <c r="D134" s="19" t="s">
+      <c r="D134" t="s">
         <v>260</v>
       </c>
-      <c r="E134" s="19" t="s">
-        <v>557</v>
+      <c r="E134" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.45">
@@ -4771,14 +4768,14 @@
       <c r="B135" t="s">
         <v>174</v>
       </c>
-      <c r="C135" s="19" t="s">
+      <c r="C135" t="s">
         <v>261</v>
       </c>
-      <c r="D135" s="19" t="s">
+      <c r="D135" t="s">
         <v>260</v>
       </c>
-      <c r="E135" s="19" t="s">
-        <v>557</v>
+      <c r="E135" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.45">
@@ -4788,14 +4785,14 @@
       <c r="B136" t="s">
         <v>209</v>
       </c>
-      <c r="C136" s="19" t="s">
+      <c r="C136" t="s">
         <v>261</v>
       </c>
-      <c r="D136" s="19" t="s">
+      <c r="D136" t="s">
         <v>260</v>
       </c>
-      <c r="E136" s="19" t="s">
-        <v>557</v>
+      <c r="E136" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.45">
@@ -4805,14 +4802,14 @@
       <c r="B137" t="s">
         <v>183</v>
       </c>
-      <c r="C137" s="19" t="s">
+      <c r="C137" t="s">
         <v>261</v>
       </c>
-      <c r="D137" s="19" t="s">
+      <c r="D137" t="s">
         <v>260</v>
       </c>
-      <c r="E137" s="19" t="s">
-        <v>557</v>
+      <c r="E137" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.45">
@@ -4822,14 +4819,14 @@
       <c r="B138" t="s">
         <v>160</v>
       </c>
-      <c r="C138" s="19" t="s">
+      <c r="C138" t="s">
         <v>261</v>
       </c>
-      <c r="D138" s="19" t="s">
+      <c r="D138" t="s">
         <v>260</v>
       </c>
-      <c r="E138" s="19" t="s">
-        <v>557</v>
+      <c r="E138" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.45">
@@ -4839,14 +4836,14 @@
       <c r="B139" t="s">
         <v>171</v>
       </c>
-      <c r="C139" s="19" t="s">
+      <c r="C139" t="s">
         <v>261</v>
       </c>
-      <c r="D139" s="19" t="s">
+      <c r="D139" t="s">
         <v>260</v>
       </c>
-      <c r="E139" s="19" t="s">
-        <v>557</v>
+      <c r="E139" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.45">
@@ -4868,19 +4865,19 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
+        <v>541</v>
+      </c>
+      <c r="B142" t="s">
+        <v>539</v>
+      </c>
+      <c r="C142" t="s">
         <v>542</v>
       </c>
-      <c r="B142" t="s">
-        <v>540</v>
-      </c>
-      <c r="C142" t="s">
+      <c r="D142" t="s">
         <v>543</v>
       </c>
-      <c r="D142" t="s">
-        <v>544</v>
-      </c>
       <c r="E142" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
   </sheetData>
@@ -5711,7 +5708,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B30">
         <v>70</v>
@@ -11955,7 +11952,7 @@
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B253">
         <v>1</v>
@@ -11975,10 +11972,10 @@
         <v>1</v>
       </c>
       <c r="G253" t="s">
+        <v>540</v>
+      </c>
+      <c r="H253" t="s">
         <v>541</v>
-      </c>
-      <c r="H253" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.45">
@@ -12107,7 +12104,7 @@
         <v>72</v>
       </c>
       <c r="E258">
-        <f t="shared" ref="E258:E321" si="8">SUM(B258:D258)</f>
+        <f t="shared" ref="E258:E261" si="8">SUM(B258:D258)</f>
         <v>201</v>
       </c>
       <c r="F258">
@@ -12302,7 +12299,7 @@
         <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -12928,12 +12925,12 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">

--- a/docs/삼국지 약식체스.xlsx
+++ b/docs/삼국지 약식체스.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Samchess\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\SamChess\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9207FA55-1DDC-4B86-B19E-9564438C44C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A807ACF2-73FD-424B-9193-3D1AB10590A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-16410" windowWidth="16440" windowHeight="28320" xr2:uid="{67B41BAA-AEF2-4AF0-8CD2-0E8DEEEF200D}"/>
+    <workbookView xWindow="-16200" yWindow="-3090" windowWidth="15480" windowHeight="10170" xr2:uid="{67B41BAA-AEF2-4AF0-8CD2-0E8DEEEF200D}"/>
   </bookViews>
   <sheets>
     <sheet name="고유 스킬" sheetId="1" r:id="rId1"/>
@@ -368,10 +368,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>구류지책</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>驅虎</t>
     </r>
@@ -1992,6 +1988,10 @@
   </si>
   <si>
     <t>적군 1명을 지정. 그 적은 게임이 끝날 때 까지 time 200 마다 HP 1 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구호탄랑</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2596,7 +2596,7 @@
         <v>53</v>
       </c>
       <c r="E2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
@@ -2613,7 +2613,7 @@
         <v>57</v>
       </c>
       <c r="E3" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
@@ -2621,16 +2621,16 @@
         <v>47</v>
       </c>
       <c r="B4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" t="s">
         <v>82</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>83</v>
       </c>
-      <c r="D4" t="s">
-        <v>84</v>
-      </c>
       <c r="E4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
@@ -2638,16 +2638,16 @@
         <v>47</v>
       </c>
       <c r="B5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D5" t="s">
         <v>91</v>
       </c>
-      <c r="C5" t="s">
-        <v>121</v>
-      </c>
-      <c r="D5" t="s">
-        <v>92</v>
-      </c>
       <c r="E5" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
@@ -2655,16 +2655,16 @@
         <v>47</v>
       </c>
       <c r="B6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" t="s">
         <v>98</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>99</v>
       </c>
-      <c r="D6" t="s">
-        <v>100</v>
-      </c>
       <c r="E6" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
@@ -2672,16 +2672,16 @@
         <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" t="s">
         <v>108</v>
       </c>
-      <c r="D7" t="s">
-        <v>109</v>
-      </c>
       <c r="E7" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
@@ -2689,16 +2689,16 @@
         <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
@@ -2706,16 +2706,16 @@
         <v>47</v>
       </c>
       <c r="B9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D9" t="s">
         <v>112</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>113</v>
-      </c>
-      <c r="E9" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
@@ -2732,7 +2732,7 @@
         <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
@@ -2743,13 +2743,13 @@
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E11" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
@@ -2766,7 +2766,7 @@
         <v>31</v>
       </c>
       <c r="E12" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
@@ -2800,7 +2800,7 @@
         <v>39</v>
       </c>
       <c r="E14" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
@@ -2811,13 +2811,13 @@
         <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D15" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E15" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
@@ -2828,13 +2828,13 @@
         <v>79</v>
       </c>
       <c r="C16" t="s">
+        <v>557</v>
+      </c>
+      <c r="D16" t="s">
         <v>80</v>
       </c>
-      <c r="D16" t="s">
-        <v>81</v>
-      </c>
       <c r="E16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
@@ -2859,16 +2859,16 @@
         <v>47</v>
       </c>
       <c r="B19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" t="s">
         <v>93</v>
       </c>
-      <c r="C19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D19" t="s">
-        <v>94</v>
-      </c>
       <c r="E19" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
@@ -2876,16 +2876,16 @@
         <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E20" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
@@ -2893,16 +2893,16 @@
         <v>47</v>
       </c>
       <c r="B21" t="s">
+        <v>117</v>
+      </c>
+      <c r="C21" t="s">
         <v>118</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>119</v>
       </c>
-      <c r="D21" t="s">
-        <v>120</v>
-      </c>
       <c r="E21" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
@@ -2919,7 +2919,7 @@
         <v>10</v>
       </c>
       <c r="E22" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
@@ -2936,7 +2936,7 @@
         <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
@@ -2953,7 +2953,7 @@
         <v>8</v>
       </c>
       <c r="E24" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
@@ -2970,7 +2970,7 @@
         <v>20</v>
       </c>
       <c r="E25" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
@@ -2987,7 +2987,7 @@
         <v>23</v>
       </c>
       <c r="E26" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
@@ -3004,7 +3004,7 @@
         <v>26</v>
       </c>
       <c r="E27" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
@@ -3015,13 +3015,13 @@
         <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D28" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
@@ -3038,7 +3038,7 @@
         <v>50</v>
       </c>
       <c r="E29" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
@@ -3046,16 +3046,16 @@
         <v>47</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E30" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.45">
@@ -3063,16 +3063,16 @@
         <v>47</v>
       </c>
       <c r="B31" t="s">
+        <v>114</v>
+      </c>
+      <c r="C31" t="s">
         <v>115</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>116</v>
       </c>
-      <c r="D31" t="s">
-        <v>117</v>
-      </c>
       <c r="E31" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
@@ -3080,16 +3080,16 @@
         <v>47</v>
       </c>
       <c r="B32" t="s">
+        <v>121</v>
+      </c>
+      <c r="C32" t="s">
         <v>122</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>123</v>
       </c>
-      <c r="D32" t="s">
-        <v>124</v>
-      </c>
       <c r="E32" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
@@ -3097,16 +3097,16 @@
         <v>47</v>
       </c>
       <c r="B33" t="s">
+        <v>125</v>
+      </c>
+      <c r="C33" t="s">
         <v>126</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>127</v>
       </c>
-      <c r="D33" t="s">
-        <v>128</v>
-      </c>
       <c r="E33" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
@@ -3128,274 +3128,274 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B36" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C36" t="s">
+        <v>235</v>
+      </c>
+      <c r="D36" t="s">
         <v>236</v>
       </c>
-      <c r="D36" t="s">
-        <v>237</v>
-      </c>
       <c r="E36" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B37" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C37" t="s">
+        <v>235</v>
+      </c>
+      <c r="D37" t="s">
         <v>236</v>
       </c>
-      <c r="D37" t="s">
-        <v>237</v>
-      </c>
       <c r="E37" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B38" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C38" t="s">
+        <v>235</v>
+      </c>
+      <c r="D38" t="s">
         <v>236</v>
       </c>
-      <c r="D38" t="s">
-        <v>237</v>
-      </c>
       <c r="E38" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B39" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C39" t="s">
+        <v>235</v>
+      </c>
+      <c r="D39" t="s">
         <v>236</v>
       </c>
-      <c r="D39" t="s">
-        <v>237</v>
-      </c>
       <c r="E39" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B40" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C40" t="s">
+        <v>235</v>
+      </c>
+      <c r="D40" t="s">
         <v>236</v>
       </c>
-      <c r="D40" t="s">
-        <v>237</v>
-      </c>
       <c r="E40" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B41" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C41" t="s">
+        <v>235</v>
+      </c>
+      <c r="D41" t="s">
         <v>236</v>
       </c>
-      <c r="D41" t="s">
-        <v>237</v>
-      </c>
       <c r="E41" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B42" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C42" t="s">
+        <v>235</v>
+      </c>
+      <c r="D42" t="s">
         <v>236</v>
       </c>
-      <c r="D42" t="s">
-        <v>237</v>
-      </c>
       <c r="E42" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B43" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C43" t="s">
+        <v>235</v>
+      </c>
+      <c r="D43" t="s">
         <v>236</v>
       </c>
-      <c r="D43" t="s">
-        <v>237</v>
-      </c>
       <c r="E43" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B44" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C44" t="s">
+        <v>235</v>
+      </c>
+      <c r="D44" t="s">
         <v>236</v>
       </c>
-      <c r="D44" t="s">
-        <v>237</v>
-      </c>
       <c r="E44" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B45" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C45" t="s">
+        <v>235</v>
+      </c>
+      <c r="D45" t="s">
         <v>236</v>
       </c>
-      <c r="D45" t="s">
-        <v>237</v>
-      </c>
       <c r="E45" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B46" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C46" t="s">
+        <v>237</v>
+      </c>
+      <c r="D46" t="s">
         <v>238</v>
       </c>
-      <c r="D46" t="s">
-        <v>239</v>
-      </c>
       <c r="E46" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B47" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C47" t="s">
+        <v>237</v>
+      </c>
+      <c r="D47" t="s">
         <v>238</v>
       </c>
-      <c r="D47" t="s">
-        <v>239</v>
-      </c>
       <c r="E47" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B48" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C48" t="s">
+        <v>237</v>
+      </c>
+      <c r="D48" t="s">
         <v>238</v>
       </c>
-      <c r="D48" t="s">
-        <v>239</v>
-      </c>
       <c r="E48" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B49" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C49" t="s">
+        <v>237</v>
+      </c>
+      <c r="D49" t="s">
         <v>238</v>
       </c>
-      <c r="D49" t="s">
-        <v>239</v>
-      </c>
       <c r="E49" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B50" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C50" t="s">
+        <v>237</v>
+      </c>
+      <c r="D50" t="s">
         <v>238</v>
       </c>
-      <c r="D50" t="s">
-        <v>239</v>
-      </c>
       <c r="E50" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B51" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C51" t="s">
+        <v>237</v>
+      </c>
+      <c r="D51" t="s">
         <v>238</v>
       </c>
-      <c r="D51" t="s">
-        <v>239</v>
-      </c>
       <c r="E51" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
@@ -3422,410 +3422,410 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B54" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C54" t="s">
+        <v>239</v>
+      </c>
+      <c r="D54" t="s">
         <v>240</v>
       </c>
-      <c r="D54" t="s">
-        <v>241</v>
-      </c>
       <c r="E54" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B55" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C55" t="s">
+        <v>239</v>
+      </c>
+      <c r="D55" t="s">
         <v>240</v>
       </c>
-      <c r="D55" t="s">
-        <v>241</v>
-      </c>
       <c r="E55" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B56" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C56" t="s">
+        <v>239</v>
+      </c>
+      <c r="D56" t="s">
         <v>240</v>
       </c>
-      <c r="D56" t="s">
-        <v>241</v>
-      </c>
       <c r="E56" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B57" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C57" t="s">
+        <v>239</v>
+      </c>
+      <c r="D57" t="s">
         <v>240</v>
       </c>
-      <c r="D57" t="s">
-        <v>241</v>
-      </c>
       <c r="E57" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B58" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C58" t="s">
+        <v>239</v>
+      </c>
+      <c r="D58" t="s">
         <v>240</v>
       </c>
-      <c r="D58" t="s">
-        <v>241</v>
-      </c>
       <c r="E58" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B59" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C59" t="s">
+        <v>239</v>
+      </c>
+      <c r="D59" t="s">
         <v>240</v>
       </c>
-      <c r="D59" t="s">
-        <v>241</v>
-      </c>
       <c r="E59" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B60" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C60" t="s">
+        <v>239</v>
+      </c>
+      <c r="D60" t="s">
         <v>240</v>
       </c>
-      <c r="D60" t="s">
-        <v>241</v>
-      </c>
       <c r="E60" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B61" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C61" t="s">
+        <v>239</v>
+      </c>
+      <c r="D61" t="s">
         <v>240</v>
       </c>
-      <c r="D61" t="s">
-        <v>241</v>
-      </c>
       <c r="E61" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B62" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C62" t="s">
+        <v>239</v>
+      </c>
+      <c r="D62" t="s">
         <v>240</v>
       </c>
-      <c r="D62" t="s">
-        <v>241</v>
-      </c>
       <c r="E62" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B63" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C63" t="s">
+        <v>239</v>
+      </c>
+      <c r="D63" t="s">
         <v>240</v>
       </c>
-      <c r="D63" t="s">
-        <v>241</v>
-      </c>
       <c r="E63" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B64" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C64" t="s">
+        <v>239</v>
+      </c>
+      <c r="D64" t="s">
         <v>240</v>
       </c>
-      <c r="D64" t="s">
-        <v>241</v>
-      </c>
       <c r="E64" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B65" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C65" t="s">
+        <v>239</v>
+      </c>
+      <c r="D65" t="s">
         <v>240</v>
       </c>
-      <c r="D65" t="s">
-        <v>241</v>
-      </c>
       <c r="E65" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B66" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C66" t="s">
+        <v>239</v>
+      </c>
+      <c r="D66" t="s">
         <v>240</v>
       </c>
-      <c r="D66" t="s">
-        <v>241</v>
-      </c>
       <c r="E66" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B67" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C67" t="s">
+        <v>239</v>
+      </c>
+      <c r="D67" t="s">
         <v>240</v>
       </c>
-      <c r="D67" t="s">
-        <v>241</v>
-      </c>
       <c r="E67" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B68" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C68" t="s">
+        <v>242</v>
+      </c>
+      <c r="D68" t="s">
         <v>243</v>
       </c>
-      <c r="D68" t="s">
-        <v>244</v>
-      </c>
       <c r="E68" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B69" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C69" t="s">
+        <v>242</v>
+      </c>
+      <c r="D69" t="s">
         <v>243</v>
       </c>
-      <c r="D69" t="s">
-        <v>244</v>
-      </c>
       <c r="E69" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B70" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C70" t="s">
+        <v>242</v>
+      </c>
+      <c r="D70" t="s">
         <v>243</v>
       </c>
-      <c r="D70" t="s">
-        <v>244</v>
-      </c>
       <c r="E70" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B71" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C71" t="s">
+        <v>242</v>
+      </c>
+      <c r="D71" t="s">
         <v>243</v>
       </c>
-      <c r="D71" t="s">
-        <v>244</v>
-      </c>
       <c r="E71" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B72" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C72" t="s">
+        <v>242</v>
+      </c>
+      <c r="D72" t="s">
         <v>243</v>
       </c>
-      <c r="D72" t="s">
-        <v>244</v>
-      </c>
       <c r="E72" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B73" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C73" t="s">
+        <v>242</v>
+      </c>
+      <c r="D73" t="s">
         <v>243</v>
       </c>
-      <c r="D73" t="s">
-        <v>244</v>
-      </c>
       <c r="E73" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B74" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C74" t="s">
+        <v>242</v>
+      </c>
+      <c r="D74" t="s">
         <v>243</v>
       </c>
-      <c r="D74" t="s">
-        <v>244</v>
-      </c>
       <c r="E74" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B75" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C75" t="s">
+        <v>242</v>
+      </c>
+      <c r="D75" t="s">
         <v>243</v>
       </c>
-      <c r="D75" t="s">
-        <v>244</v>
-      </c>
       <c r="E75" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B76" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C76" t="s">
+        <v>242</v>
+      </c>
+      <c r="D76" t="s">
         <v>243</v>
       </c>
-      <c r="D76" t="s">
-        <v>244</v>
-      </c>
       <c r="E76" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B77" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C77" t="s">
+        <v>242</v>
+      </c>
+      <c r="D77" t="s">
         <v>243</v>
       </c>
-      <c r="D77" t="s">
-        <v>244</v>
-      </c>
       <c r="E77" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.45">
@@ -3852,325 +3852,325 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B80" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C80" t="s">
+        <v>244</v>
+      </c>
+      <c r="D80" t="s">
         <v>245</v>
       </c>
-      <c r="D80" t="s">
-        <v>246</v>
-      </c>
       <c r="E80" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B81" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C81" t="s">
+        <v>244</v>
+      </c>
+      <c r="D81" t="s">
         <v>245</v>
       </c>
-      <c r="D81" t="s">
-        <v>246</v>
-      </c>
       <c r="E81" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B82" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C82" t="s">
+        <v>244</v>
+      </c>
+      <c r="D82" t="s">
         <v>245</v>
       </c>
-      <c r="D82" t="s">
-        <v>246</v>
-      </c>
       <c r="E82" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B83" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C83" t="s">
+        <v>244</v>
+      </c>
+      <c r="D83" t="s">
         <v>245</v>
       </c>
-      <c r="D83" t="s">
-        <v>246</v>
-      </c>
       <c r="E83" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B84" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C84" t="s">
+        <v>244</v>
+      </c>
+      <c r="D84" t="s">
         <v>245</v>
       </c>
-      <c r="D84" t="s">
-        <v>246</v>
-      </c>
       <c r="E84" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B85" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C85" t="s">
+        <v>244</v>
+      </c>
+      <c r="D85" t="s">
         <v>245</v>
       </c>
-      <c r="D85" t="s">
-        <v>246</v>
-      </c>
       <c r="E85" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B86" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C86" t="s">
+        <v>244</v>
+      </c>
+      <c r="D86" t="s">
         <v>245</v>
       </c>
-      <c r="D86" t="s">
-        <v>246</v>
-      </c>
       <c r="E86" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B87" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C87" t="s">
+        <v>244</v>
+      </c>
+      <c r="D87" t="s">
         <v>245</v>
       </c>
-      <c r="D87" t="s">
-        <v>246</v>
-      </c>
       <c r="E87" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B88" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C88" t="s">
+        <v>244</v>
+      </c>
+      <c r="D88" t="s">
         <v>245</v>
       </c>
-      <c r="D88" t="s">
-        <v>246</v>
-      </c>
       <c r="E88" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B89" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C89" t="s">
+        <v>254</v>
+      </c>
+      <c r="D89" t="s">
         <v>255</v>
       </c>
-      <c r="D89" t="s">
-        <v>256</v>
-      </c>
       <c r="E89" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B90" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C90" t="s">
+        <v>254</v>
+      </c>
+      <c r="D90" t="s">
         <v>255</v>
       </c>
-      <c r="D90" t="s">
-        <v>256</v>
-      </c>
       <c r="E90" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B91" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C91" t="s">
+        <v>254</v>
+      </c>
+      <c r="D91" t="s">
         <v>255</v>
       </c>
-      <c r="D91" t="s">
-        <v>256</v>
-      </c>
       <c r="E91" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B92" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C92" t="s">
+        <v>254</v>
+      </c>
+      <c r="D92" t="s">
         <v>255</v>
       </c>
-      <c r="D92" t="s">
-        <v>256</v>
-      </c>
       <c r="E92" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B93" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C93" t="s">
+        <v>254</v>
+      </c>
+      <c r="D93" t="s">
         <v>255</v>
       </c>
-      <c r="D93" t="s">
-        <v>256</v>
-      </c>
       <c r="E93" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B94" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C94" t="s">
+        <v>254</v>
+      </c>
+      <c r="D94" t="s">
         <v>255</v>
       </c>
-      <c r="D94" t="s">
-        <v>256</v>
-      </c>
       <c r="E94" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B95" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C95" t="s">
+        <v>254</v>
+      </c>
+      <c r="D95" t="s">
         <v>255</v>
       </c>
-      <c r="D95" t="s">
-        <v>256</v>
-      </c>
       <c r="E95" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B96" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C96" t="s">
+        <v>254</v>
+      </c>
+      <c r="D96" t="s">
         <v>255</v>
       </c>
-      <c r="D96" t="s">
-        <v>256</v>
-      </c>
       <c r="E96" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B97" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C97" t="s">
+        <v>254</v>
+      </c>
+      <c r="D97" t="s">
         <v>255</v>
       </c>
-      <c r="D97" t="s">
-        <v>256</v>
-      </c>
       <c r="E97" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B98" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C98" t="s">
+        <v>254</v>
+      </c>
+      <c r="D98" t="s">
         <v>255</v>
       </c>
-      <c r="D98" t="s">
-        <v>256</v>
-      </c>
       <c r="E98" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.45">
@@ -4197,427 +4197,427 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B101" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C101" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D101" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E101" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B102" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C102" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D102" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E102" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B103" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C103" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D103" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E103" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B104" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C104" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D104" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E104" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B105" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C105" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D105" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E105" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B106" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C106" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D106" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E106" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B107" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C107" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D107" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E107" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B108" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C108" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D108" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E108" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B109" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C109" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D109" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E109" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B110" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C110" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D110" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E110" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B111" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C111" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D111" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E111" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B112" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C112" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D112" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E112" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B113" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C113" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D113" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E113" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B114" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C114" t="s">
+        <v>248</v>
+      </c>
+      <c r="D114" t="s">
         <v>249</v>
       </c>
-      <c r="D114" t="s">
+      <c r="E114" t="s">
         <v>250</v>
-      </c>
-      <c r="E114" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B115" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C115" t="s">
+        <v>248</v>
+      </c>
+      <c r="D115" t="s">
         <v>249</v>
       </c>
-      <c r="D115" t="s">
+      <c r="E115" t="s">
         <v>250</v>
-      </c>
-      <c r="E115" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B116" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C116" t="s">
+        <v>248</v>
+      </c>
+      <c r="D116" t="s">
         <v>249</v>
       </c>
-      <c r="D116" t="s">
-        <v>250</v>
-      </c>
       <c r="E116" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B117" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C117" t="s">
+        <v>248</v>
+      </c>
+      <c r="D117" t="s">
         <v>249</v>
       </c>
-      <c r="D117" t="s">
-        <v>250</v>
-      </c>
       <c r="E117" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B118" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C118" t="s">
+        <v>248</v>
+      </c>
+      <c r="D118" t="s">
         <v>249</v>
       </c>
-      <c r="D118" t="s">
-        <v>250</v>
-      </c>
       <c r="E118" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B119" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C119" t="s">
+        <v>248</v>
+      </c>
+      <c r="D119" t="s">
         <v>249</v>
       </c>
-      <c r="D119" t="s">
-        <v>250</v>
-      </c>
       <c r="E119" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B120" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C120" t="s">
+        <v>248</v>
+      </c>
+      <c r="D120" t="s">
         <v>249</v>
       </c>
-      <c r="D120" t="s">
-        <v>250</v>
-      </c>
       <c r="E120" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B121" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C121" t="s">
+        <v>248</v>
+      </c>
+      <c r="D121" t="s">
         <v>249</v>
       </c>
-      <c r="D121" t="s">
-        <v>250</v>
-      </c>
       <c r="E121" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B122" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C122" t="s">
+        <v>248</v>
+      </c>
+      <c r="D122" t="s">
         <v>249</v>
       </c>
-      <c r="D122" t="s">
-        <v>250</v>
-      </c>
       <c r="E122" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B123" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C123" t="s">
+        <v>248</v>
+      </c>
+      <c r="D123" t="s">
         <v>249</v>
       </c>
-      <c r="D123" t="s">
-        <v>250</v>
-      </c>
       <c r="E123" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B124" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C124" t="s">
+        <v>248</v>
+      </c>
+      <c r="D124" t="s">
         <v>249</v>
       </c>
-      <c r="D124" t="s">
-        <v>250</v>
-      </c>
       <c r="E124" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B125" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C125" t="s">
+        <v>248</v>
+      </c>
+      <c r="D125" t="s">
         <v>249</v>
       </c>
-      <c r="D125" t="s">
-        <v>250</v>
-      </c>
       <c r="E125" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.45">
@@ -4644,206 +4644,206 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B128" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C128" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D128" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E128" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B129" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C129" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D129" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E129" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B130" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C130" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D130" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E130" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B131" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C131" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D131" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E131" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B132" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C132" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D132" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E132" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B133" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C133" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D133" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E133" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B134" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C134" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D134" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E134" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B135" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C135" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D135" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E135" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B136" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D136" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E136" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B137" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D137" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E137" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B138" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C138" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D138" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E138" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B139" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C139" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D139" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E139" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.45">
@@ -4865,19 +4865,19 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
+        <v>540</v>
+      </c>
+      <c r="B142" t="s">
+        <v>538</v>
+      </c>
+      <c r="C142" t="s">
         <v>541</v>
       </c>
-      <c r="B142" t="s">
-        <v>539</v>
-      </c>
-      <c r="C142" t="s">
+      <c r="D142" t="s">
         <v>542</v>
       </c>
-      <c r="D142" t="s">
-        <v>543</v>
-      </c>
       <c r="E142" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
   </sheetData>
@@ -4898,33 +4898,33 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B1" t="s">
         <v>319</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>320</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>321</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F1" t="s">
+        <v>506</v>
+      </c>
+      <c r="G1" t="s">
         <v>322</v>
       </c>
-      <c r="E1" t="s">
-        <v>504</v>
-      </c>
-      <c r="F1" t="s">
-        <v>507</v>
-      </c>
-      <c r="G1" t="s">
-        <v>323</v>
-      </c>
       <c r="H1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B2">
         <v>40</v>
@@ -4944,15 +4944,15 @@
         <v>96</v>
       </c>
       <c r="G2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B3">
         <v>42</v>
@@ -4972,15 +4972,15 @@
         <v>74</v>
       </c>
       <c r="G3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B4">
         <v>91</v>
@@ -5000,15 +5000,15 @@
         <v>91</v>
       </c>
       <c r="G4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B5">
         <v>45</v>
@@ -5028,15 +5028,15 @@
         <v>78</v>
       </c>
       <c r="G5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H5" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B6">
         <v>90</v>
@@ -5056,15 +5056,15 @@
         <v>94</v>
       </c>
       <c r="G6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H6" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B7">
         <v>44</v>
@@ -5084,15 +5084,15 @@
         <v>53</v>
       </c>
       <c r="G7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B8">
         <v>75</v>
@@ -5112,15 +5112,15 @@
         <v>75</v>
       </c>
       <c r="G8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H8" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B9">
         <v>56</v>
@@ -5140,15 +5140,15 @@
         <v>63</v>
       </c>
       <c r="G9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H9" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B10">
         <v>18</v>
@@ -5168,15 +5168,15 @@
         <v>72</v>
       </c>
       <c r="G10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H10" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B11">
         <v>72</v>
@@ -5196,15 +5196,15 @@
         <v>72</v>
       </c>
       <c r="G11" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H11" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B12">
         <v>59</v>
@@ -5224,15 +5224,15 @@
         <v>59</v>
       </c>
       <c r="G12" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H12" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B13">
         <v>60</v>
@@ -5252,15 +5252,15 @@
         <v>60</v>
       </c>
       <c r="G13" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H13" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B14">
         <v>71</v>
@@ -5280,15 +5280,15 @@
         <v>71</v>
       </c>
       <c r="G14" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H14" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B15">
         <v>58</v>
@@ -5308,15 +5308,15 @@
         <v>83</v>
       </c>
       <c r="G15" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H15" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B16">
         <v>44</v>
@@ -5336,15 +5336,15 @@
         <v>63</v>
       </c>
       <c r="G16" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H16" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B17">
         <v>36</v>
@@ -5364,15 +5364,15 @@
         <v>97</v>
       </c>
       <c r="G17" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H17" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B18">
         <v>34</v>
@@ -5392,15 +5392,15 @@
         <v>76</v>
       </c>
       <c r="G18" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H18" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B19">
         <v>61</v>
@@ -5420,15 +5420,15 @@
         <v>61</v>
       </c>
       <c r="G19" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H19" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B20">
         <v>35</v>
@@ -5448,15 +5448,15 @@
         <v>63</v>
       </c>
       <c r="G20" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H20" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B21">
         <v>67</v>
@@ -5476,15 +5476,15 @@
         <v>67</v>
       </c>
       <c r="G21" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H21" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B22">
         <v>42</v>
@@ -5504,10 +5504,10 @@
         <v>61</v>
       </c>
       <c r="G22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.45">
@@ -5532,15 +5532,15 @@
         <v>100</v>
       </c>
       <c r="G23" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H23" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B24">
         <v>80</v>
@@ -5560,15 +5560,15 @@
         <v>80</v>
       </c>
       <c r="G24" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H24" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B25">
         <v>68</v>
@@ -5588,15 +5588,15 @@
         <v>68</v>
       </c>
       <c r="G25" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H25" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B26">
         <v>88</v>
@@ -5616,15 +5616,15 @@
         <v>88</v>
       </c>
       <c r="G26" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H26" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B27">
         <v>29</v>
@@ -5644,15 +5644,15 @@
         <v>74</v>
       </c>
       <c r="G27" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H27" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B28">
         <v>73</v>
@@ -5672,15 +5672,15 @@
         <v>73</v>
       </c>
       <c r="G28" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H28" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B29">
         <v>52</v>
@@ -5700,15 +5700,15 @@
         <v>52</v>
       </c>
       <c r="G29" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H29" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B30">
         <v>70</v>
@@ -5728,15 +5728,15 @@
         <v>70</v>
       </c>
       <c r="G30" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H30" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B31">
         <v>66</v>
@@ -5756,15 +5756,15 @@
         <v>66</v>
       </c>
       <c r="G31" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H31" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B32">
         <v>65</v>
@@ -5784,15 +5784,15 @@
         <v>65</v>
       </c>
       <c r="G32" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H32" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B33">
         <v>61</v>
@@ -5812,15 +5812,15 @@
         <v>95</v>
       </c>
       <c r="G33" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H33" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B34">
         <v>86</v>
@@ -5840,15 +5840,15 @@
         <v>86</v>
       </c>
       <c r="G34" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H34" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B35">
         <v>81</v>
@@ -5868,15 +5868,15 @@
         <v>81</v>
       </c>
       <c r="G35" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H35" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B36">
         <v>53</v>
@@ -5896,15 +5896,15 @@
         <v>61</v>
       </c>
       <c r="G36" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H36" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B37">
         <v>69</v>
@@ -5924,15 +5924,15 @@
         <v>69</v>
       </c>
       <c r="G37" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H37" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B38">
         <v>52</v>
@@ -5952,15 +5952,15 @@
         <v>62</v>
       </c>
       <c r="G38" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H38" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B39">
         <v>89</v>
@@ -5980,15 +5980,15 @@
         <v>89</v>
       </c>
       <c r="G39" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H39" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B40">
         <v>57</v>
@@ -6008,15 +6008,15 @@
         <v>57</v>
       </c>
       <c r="G40" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H40" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B41">
         <v>69</v>
@@ -6036,15 +6036,15 @@
         <v>69</v>
       </c>
       <c r="G41" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H41" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B42">
         <v>84</v>
@@ -6064,15 +6064,15 @@
         <v>84</v>
       </c>
       <c r="G42" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H42" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B43">
         <v>94</v>
@@ -6092,15 +6092,15 @@
         <v>94</v>
       </c>
       <c r="G43" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H43" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B44">
         <v>45</v>
@@ -6120,15 +6120,15 @@
         <v>90</v>
       </c>
       <c r="G44" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H44" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B45">
         <v>65</v>
@@ -6148,15 +6148,15 @@
         <v>84</v>
       </c>
       <c r="G45" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H45" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B46">
         <v>65</v>
@@ -6176,15 +6176,15 @@
         <v>65</v>
       </c>
       <c r="G46" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H46" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B47">
         <v>97</v>
@@ -6204,15 +6204,15 @@
         <v>97</v>
       </c>
       <c r="G47" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H47" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B48">
         <v>58</v>
@@ -6232,15 +6232,15 @@
         <v>58</v>
       </c>
       <c r="G48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H48" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B49">
         <v>27</v>
@@ -6260,15 +6260,15 @@
         <v>68</v>
       </c>
       <c r="G49" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H49" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B50">
         <v>73</v>
@@ -6288,15 +6288,15 @@
         <v>73</v>
       </c>
       <c r="G50" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H50" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B51">
         <v>69</v>
@@ -6316,15 +6316,15 @@
         <v>69</v>
       </c>
       <c r="G51" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H51" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B52">
         <v>57</v>
@@ -6344,15 +6344,15 @@
         <v>57</v>
       </c>
       <c r="G52" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H52" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B53">
         <v>84</v>
@@ -6372,15 +6372,15 @@
         <v>84</v>
       </c>
       <c r="G53" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H53" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B54">
         <v>91</v>
@@ -6400,15 +6400,15 @@
         <v>91</v>
       </c>
       <c r="G54" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H54" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B55">
         <v>63</v>
@@ -6428,15 +6428,15 @@
         <v>63</v>
       </c>
       <c r="G55" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H55" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B56">
         <v>40</v>
@@ -6456,15 +6456,15 @@
         <v>64</v>
       </c>
       <c r="G56" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H56" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B57">
         <v>75</v>
@@ -6484,15 +6484,15 @@
         <v>75</v>
       </c>
       <c r="G57" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H57" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B58">
         <v>94</v>
@@ -6512,15 +6512,15 @@
         <v>94</v>
       </c>
       <c r="G58" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H58" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B59">
         <v>51</v>
@@ -6540,15 +6540,15 @@
         <v>98</v>
       </c>
       <c r="G59" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H59" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B60">
         <v>62</v>
@@ -6568,15 +6568,15 @@
         <v>71</v>
       </c>
       <c r="G60" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H60" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B61">
         <v>52</v>
@@ -6596,15 +6596,15 @@
         <v>87</v>
       </c>
       <c r="G61" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H61" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B62">
         <v>25</v>
@@ -6624,15 +6624,15 @@
         <v>65</v>
       </c>
       <c r="G62" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H62" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B63">
         <v>54</v>
@@ -6652,15 +6652,15 @@
         <v>82</v>
       </c>
       <c r="G63" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H63" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B64">
         <v>49</v>
@@ -6680,15 +6680,15 @@
         <v>58</v>
       </c>
       <c r="G64" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H64" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B65">
         <v>23</v>
@@ -6708,15 +6708,15 @@
         <v>80</v>
       </c>
       <c r="G65" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H65" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B66">
         <v>91</v>
@@ -6736,15 +6736,15 @@
         <v>91</v>
       </c>
       <c r="G66" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H66" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B67">
         <v>65</v>
@@ -6764,15 +6764,15 @@
         <v>87</v>
       </c>
       <c r="G67" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H67" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B68">
         <v>66</v>
@@ -6792,15 +6792,15 @@
         <v>85</v>
       </c>
       <c r="G68" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H68" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B69">
         <v>48</v>
@@ -6820,15 +6820,15 @@
         <v>99</v>
       </c>
       <c r="G69" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H69" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B70">
         <v>69</v>
@@ -6848,15 +6848,15 @@
         <v>74</v>
       </c>
       <c r="G70" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H70" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B71">
         <v>82</v>
@@ -6876,15 +6876,15 @@
         <v>82</v>
       </c>
       <c r="G71" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H71" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B72">
         <v>44</v>
@@ -6904,15 +6904,15 @@
         <v>97</v>
       </c>
       <c r="G72" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H72" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B73">
         <v>72</v>
@@ -6932,15 +6932,15 @@
         <v>72</v>
       </c>
       <c r="G73" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H73" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B74">
         <v>54</v>
@@ -6960,15 +6960,15 @@
         <v>54</v>
       </c>
       <c r="G74" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H74" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B75">
         <v>91</v>
@@ -6988,15 +6988,15 @@
         <v>91</v>
       </c>
       <c r="G75" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H75" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B76">
         <v>35</v>
@@ -7016,15 +7016,15 @@
         <v>62</v>
       </c>
       <c r="G76" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H76" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B77">
         <v>38</v>
@@ -7044,15 +7044,15 @@
         <v>74</v>
       </c>
       <c r="G77" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H77" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B78">
         <v>90</v>
@@ -7072,15 +7072,15 @@
         <v>90</v>
       </c>
       <c r="G78" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H78" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B79">
         <v>67</v>
@@ -7100,15 +7100,15 @@
         <v>67</v>
       </c>
       <c r="G79" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H79" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B80">
         <v>86</v>
@@ -7128,15 +7128,15 @@
         <v>87</v>
       </c>
       <c r="G80" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H80" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B81">
         <v>64</v>
@@ -7156,15 +7156,15 @@
         <v>64</v>
       </c>
       <c r="G81" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H81" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B82">
         <v>65</v>
@@ -7184,15 +7184,15 @@
         <v>72</v>
       </c>
       <c r="G82" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H82" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B83">
         <v>59</v>
@@ -7212,15 +7212,15 @@
         <v>59</v>
       </c>
       <c r="G83" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H83" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B84">
         <v>64</v>
@@ -7240,15 +7240,15 @@
         <v>64</v>
       </c>
       <c r="G84" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H84" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B85">
         <v>33</v>
@@ -7268,15 +7268,15 @@
         <v>41</v>
       </c>
       <c r="G85" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H85" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B86">
         <v>45</v>
@@ -7296,15 +7296,15 @@
         <v>70</v>
       </c>
       <c r="G86" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H86" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B87">
         <v>73</v>
@@ -7324,15 +7324,15 @@
         <v>73</v>
       </c>
       <c r="G87" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H87" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B88">
         <v>37</v>
@@ -7352,15 +7352,15 @@
         <v>96</v>
       </c>
       <c r="G88" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H88" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B89">
         <v>40</v>
@@ -7380,15 +7380,15 @@
         <v>94</v>
       </c>
       <c r="G89" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H89" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B90">
         <v>59</v>
@@ -7408,15 +7408,15 @@
         <v>59</v>
       </c>
       <c r="G90" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H90" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B91">
         <v>71</v>
@@ -7436,15 +7436,15 @@
         <v>73</v>
       </c>
       <c r="G91" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H91" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B92">
         <v>74</v>
@@ -7464,15 +7464,15 @@
         <v>74</v>
       </c>
       <c r="G92" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H92" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B93">
         <v>70</v>
@@ -7492,15 +7492,15 @@
         <v>70</v>
       </c>
       <c r="G93" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H93" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B94">
         <v>87</v>
@@ -7520,15 +7520,15 @@
         <v>87</v>
       </c>
       <c r="G94" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H94" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B95">
         <v>62</v>
@@ -7548,15 +7548,15 @@
         <v>62</v>
       </c>
       <c r="G95" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H95" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B96">
         <v>48</v>
@@ -7576,15 +7576,15 @@
         <v>51</v>
       </c>
       <c r="G96" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H96" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B97">
         <v>28</v>
@@ -7604,15 +7604,15 @@
         <v>76</v>
       </c>
       <c r="G97" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H97" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B98">
         <v>45</v>
@@ -7632,15 +7632,15 @@
         <v>57</v>
       </c>
       <c r="G98" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H98" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B99">
         <v>29</v>
@@ -7660,15 +7660,15 @@
         <v>85</v>
       </c>
       <c r="G99" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H99" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B100">
         <v>67</v>
@@ -7688,15 +7688,15 @@
         <v>76</v>
       </c>
       <c r="G100" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H100" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B101">
         <v>72</v>
@@ -7716,15 +7716,15 @@
         <v>72</v>
       </c>
       <c r="G101" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H101" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B102">
         <v>45</v>
@@ -7744,15 +7744,15 @@
         <v>57</v>
       </c>
       <c r="G102" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H102" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B103">
         <v>58</v>
@@ -7772,15 +7772,15 @@
         <v>66</v>
       </c>
       <c r="G103" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H103" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B104">
         <v>75</v>
@@ -7800,15 +7800,15 @@
         <v>75</v>
       </c>
       <c r="G104" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H104" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B105">
         <v>66</v>
@@ -7828,15 +7828,15 @@
         <v>66</v>
       </c>
       <c r="G105" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H105" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B106">
         <v>70</v>
@@ -7856,15 +7856,15 @@
         <v>70</v>
       </c>
       <c r="G106" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H106" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B107">
         <v>86</v>
@@ -7884,15 +7884,15 @@
         <v>87</v>
       </c>
       <c r="G107" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H107" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B108">
         <v>25</v>
@@ -7912,15 +7912,15 @@
         <v>71</v>
       </c>
       <c r="G108" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H108" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B109">
         <v>51</v>
@@ -7940,15 +7940,15 @@
         <v>51</v>
       </c>
       <c r="G109" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H109" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B110">
         <v>73</v>
@@ -7968,15 +7968,15 @@
         <v>73</v>
       </c>
       <c r="G110" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H110" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B111">
         <v>84</v>
@@ -7996,15 +7996,15 @@
         <v>91</v>
       </c>
       <c r="G111" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H111" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B112">
         <v>30</v>
@@ -8024,15 +8024,15 @@
         <v>72</v>
       </c>
       <c r="G112" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H112" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B113">
         <v>57</v>
@@ -8052,15 +8052,15 @@
         <v>70</v>
       </c>
       <c r="G113" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H113" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B114">
         <v>100</v>
@@ -8080,15 +8080,15 @@
         <v>100</v>
       </c>
       <c r="G114" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H114" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B115">
         <v>36</v>
@@ -8108,15 +8108,15 @@
         <v>80</v>
       </c>
       <c r="G115" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H115" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B116">
         <v>88</v>
@@ -8136,15 +8136,15 @@
         <v>88</v>
       </c>
       <c r="G116" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H116" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B117">
         <v>65</v>
@@ -8164,15 +8164,15 @@
         <v>65</v>
       </c>
       <c r="G117" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H117" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B118">
         <v>71</v>
@@ -8192,15 +8192,15 @@
         <v>71</v>
       </c>
       <c r="G118" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H118" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B119">
         <v>42</v>
@@ -8220,15 +8220,15 @@
         <v>60</v>
       </c>
       <c r="G119" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H119" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B120">
         <v>32</v>
@@ -8248,15 +8248,15 @@
         <v>54</v>
       </c>
       <c r="G120" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H120" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B121">
         <v>23</v>
@@ -8276,15 +8276,15 @@
         <v>80</v>
       </c>
       <c r="G121" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H121" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B122">
         <v>52</v>
@@ -8304,15 +8304,15 @@
         <v>74</v>
       </c>
       <c r="G122" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H122" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B123">
         <v>40</v>
@@ -8332,15 +8332,15 @@
         <v>58</v>
       </c>
       <c r="G123" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H123" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B124">
         <v>30</v>
@@ -8360,15 +8360,15 @@
         <v>70</v>
       </c>
       <c r="G124" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H124" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B125">
         <v>60</v>
@@ -8388,15 +8388,15 @@
         <v>60</v>
       </c>
       <c r="G125" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H125" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B126">
         <v>55</v>
@@ -8416,15 +8416,15 @@
         <v>55</v>
       </c>
       <c r="G126" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H126" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B127">
         <v>72</v>
@@ -8444,15 +8444,15 @@
         <v>72</v>
       </c>
       <c r="G127" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H127" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B128">
         <v>78</v>
@@ -8472,15 +8472,15 @@
         <v>78</v>
       </c>
       <c r="G128" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H128" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B129">
         <v>60</v>
@@ -8500,15 +8500,15 @@
         <v>62</v>
       </c>
       <c r="G129" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H129" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B130">
         <v>40</v>
@@ -8528,15 +8528,15 @@
         <v>78</v>
       </c>
       <c r="G130" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H130" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B131">
         <v>23</v>
@@ -8556,15 +8556,15 @@
         <v>46</v>
       </c>
       <c r="G131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H131" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B132">
         <v>58</v>
@@ -8584,15 +8584,15 @@
         <v>71</v>
       </c>
       <c r="G132" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H132" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B133">
         <v>79</v>
@@ -8612,15 +8612,15 @@
         <v>79</v>
       </c>
       <c r="G133" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H133" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B134">
         <v>25</v>
@@ -8640,15 +8640,15 @@
         <v>59</v>
       </c>
       <c r="G134" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H134" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B135">
         <v>72</v>
@@ -8668,15 +8668,15 @@
         <v>72</v>
       </c>
       <c r="G135" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H135" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B136">
         <v>92</v>
@@ -8696,15 +8696,15 @@
         <v>92</v>
       </c>
       <c r="G136" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H136" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B137">
         <v>51</v>
@@ -8724,15 +8724,15 @@
         <v>60</v>
       </c>
       <c r="G137" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H137" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B138">
         <v>30</v>
@@ -8752,15 +8752,15 @@
         <v>63</v>
       </c>
       <c r="G138" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H138" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B139">
         <v>64</v>
@@ -8780,15 +8780,15 @@
         <v>64</v>
       </c>
       <c r="G139" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H139" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B140">
         <v>53</v>
@@ -8808,15 +8808,15 @@
         <v>55</v>
       </c>
       <c r="G140" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H140" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B141">
         <v>67</v>
@@ -8836,15 +8836,15 @@
         <v>67</v>
       </c>
       <c r="G141" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H141" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B142">
         <v>63</v>
@@ -8864,15 +8864,15 @@
         <v>63</v>
       </c>
       <c r="G142" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H142" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B143">
         <v>75</v>
@@ -8892,15 +8892,15 @@
         <v>91</v>
       </c>
       <c r="G143" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H143" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B144">
         <v>22</v>
@@ -8920,15 +8920,15 @@
         <v>22</v>
       </c>
       <c r="G144" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H144" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B145">
         <v>58</v>
@@ -8948,15 +8948,15 @@
         <v>58</v>
       </c>
       <c r="G145" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H145" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B146">
         <v>35</v>
@@ -8976,15 +8976,15 @@
         <v>85</v>
       </c>
       <c r="G146" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H146" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B147">
         <v>52</v>
@@ -9004,15 +9004,15 @@
         <v>52</v>
       </c>
       <c r="G147" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H147" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B148">
         <v>59</v>
@@ -9032,15 +9032,15 @@
         <v>59</v>
       </c>
       <c r="G148" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H148" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B149">
         <v>70</v>
@@ -9060,15 +9060,15 @@
         <v>70</v>
       </c>
       <c r="G149" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H149" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B150">
         <v>58</v>
@@ -9088,15 +9088,15 @@
         <v>58</v>
       </c>
       <c r="G150" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H150" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B151">
         <v>80</v>
@@ -9116,15 +9116,15 @@
         <v>95</v>
       </c>
       <c r="G151" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H151" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B152">
         <v>32</v>
@@ -9144,15 +9144,15 @@
         <v>68</v>
       </c>
       <c r="G152" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H152" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B153">
         <v>63</v>
@@ -9172,15 +9172,15 @@
         <v>63</v>
       </c>
       <c r="G153" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H153" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B154">
         <v>28</v>
@@ -9200,15 +9200,15 @@
         <v>58</v>
       </c>
       <c r="G154" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H154" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B155">
         <v>70</v>
@@ -9228,15 +9228,15 @@
         <v>72</v>
       </c>
       <c r="G155" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H155" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B156">
         <v>54</v>
@@ -9256,15 +9256,15 @@
         <v>68</v>
       </c>
       <c r="G156" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H156" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B157">
         <v>75</v>
@@ -9284,15 +9284,15 @@
         <v>75</v>
       </c>
       <c r="G157" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H157" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B158">
         <v>73</v>
@@ -9312,15 +9312,15 @@
         <v>73</v>
       </c>
       <c r="G158" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H158" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B159">
         <v>25</v>
@@ -9340,15 +9340,15 @@
         <v>90</v>
       </c>
       <c r="G159" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H159" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B160">
         <v>79</v>
@@ -9368,15 +9368,15 @@
         <v>79</v>
       </c>
       <c r="G160" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H160" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B161">
         <v>21</v>
@@ -9396,15 +9396,15 @@
         <v>84</v>
       </c>
       <c r="G161" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H161" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B162">
         <v>72</v>
@@ -9424,15 +9424,15 @@
         <v>73</v>
       </c>
       <c r="G162" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H162" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B163">
         <v>68</v>
@@ -9452,15 +9452,15 @@
         <v>68</v>
       </c>
       <c r="G163" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H163" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B164">
         <v>70</v>
@@ -9480,15 +9480,15 @@
         <v>88</v>
       </c>
       <c r="G164" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H164" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B165">
         <v>72</v>
@@ -9508,15 +9508,15 @@
         <v>72</v>
       </c>
       <c r="G165" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H165" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B166">
         <v>56</v>
@@ -9536,15 +9536,15 @@
         <v>56</v>
       </c>
       <c r="G166" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H166" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B167">
         <v>72</v>
@@ -9564,15 +9564,15 @@
         <v>80</v>
       </c>
       <c r="G167" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H167" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B168">
         <v>57</v>
@@ -9592,15 +9592,15 @@
         <v>57</v>
       </c>
       <c r="G168" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H168" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B169">
         <v>64</v>
@@ -9620,10 +9620,10 @@
         <v>64</v>
       </c>
       <c r="G169" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H169" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.45">
@@ -9648,15 +9648,15 @@
         <v>99</v>
       </c>
       <c r="G170" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H170" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B171">
         <v>32</v>
@@ -9676,15 +9676,15 @@
         <v>92</v>
       </c>
       <c r="G171" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H171" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B172">
         <v>34</v>
@@ -9704,15 +9704,15 @@
         <v>86</v>
       </c>
       <c r="G172" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H172" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B173">
         <v>74</v>
@@ -9732,15 +9732,15 @@
         <v>74</v>
       </c>
       <c r="G173" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H173" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B174">
         <v>64</v>
@@ -9760,15 +9760,15 @@
         <v>64</v>
       </c>
       <c r="G174" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H174" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B175">
         <v>60</v>
@@ -9788,15 +9788,15 @@
         <v>85</v>
       </c>
       <c r="G175" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H175" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B176">
         <v>90</v>
@@ -9816,7 +9816,7 @@
         <v>90</v>
       </c>
       <c r="G176" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H176" t="s">
         <v>47</v>
@@ -9824,7 +9824,7 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B177">
         <v>72</v>
@@ -9844,15 +9844,15 @@
         <v>72</v>
       </c>
       <c r="G177" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H177" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B178">
         <v>59</v>
@@ -9872,15 +9872,15 @@
         <v>60</v>
       </c>
       <c r="G178" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H178" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B179">
         <v>87</v>
@@ -9900,15 +9900,15 @@
         <v>87</v>
       </c>
       <c r="G179" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H179" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B180">
         <v>92</v>
@@ -9928,15 +9928,15 @@
         <v>92</v>
       </c>
       <c r="G180" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H180" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B181">
         <v>90</v>
@@ -9956,15 +9956,15 @@
         <v>90</v>
       </c>
       <c r="G181" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H181" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B182">
         <v>78</v>
@@ -9984,15 +9984,15 @@
         <v>78</v>
       </c>
       <c r="G182" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H182" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B183">
         <v>67</v>
@@ -10012,15 +10012,15 @@
         <v>67</v>
       </c>
       <c r="G183" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H183" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B184">
         <v>60</v>
@@ -10040,15 +10040,15 @@
         <v>85</v>
       </c>
       <c r="G184" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H184" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B185">
         <v>45</v>
@@ -10068,15 +10068,15 @@
         <v>90</v>
       </c>
       <c r="G185" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H185" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B186">
         <v>70</v>
@@ -10096,15 +10096,15 @@
         <v>70</v>
       </c>
       <c r="G186" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H186" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B187">
         <v>69</v>
@@ -10124,15 +10124,15 @@
         <v>81</v>
       </c>
       <c r="G187" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H187" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B188">
         <v>75</v>
@@ -10152,15 +10152,15 @@
         <v>75</v>
       </c>
       <c r="G188" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H188" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B189">
         <v>25</v>
@@ -10180,15 +10180,15 @@
         <v>90</v>
       </c>
       <c r="G189" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H189" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B190">
         <v>55</v>
@@ -10208,15 +10208,15 @@
         <v>91</v>
       </c>
       <c r="G190" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H190" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B191">
         <v>44</v>
@@ -10236,15 +10236,15 @@
         <v>100</v>
       </c>
       <c r="G191" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H191" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B192">
         <v>60</v>
@@ -10264,15 +10264,15 @@
         <v>70</v>
       </c>
       <c r="G192" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H192" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B193">
         <v>52</v>
@@ -10292,15 +10292,15 @@
         <v>54</v>
       </c>
       <c r="G193" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H193" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B194">
         <v>68</v>
@@ -10320,15 +10320,15 @@
         <v>68</v>
       </c>
       <c r="G194" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H194" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B195">
         <v>70</v>
@@ -10348,15 +10348,15 @@
         <v>70</v>
       </c>
       <c r="G195" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H195" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B196">
         <v>60</v>
@@ -10376,15 +10376,15 @@
         <v>60</v>
       </c>
       <c r="G196" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H196" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B197">
         <v>15</v>
@@ -10404,15 +10404,15 @@
         <v>78</v>
       </c>
       <c r="G197" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H197" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B198">
         <v>98</v>
@@ -10432,15 +10432,15 @@
         <v>98</v>
       </c>
       <c r="G198" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H198" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B199">
         <v>80</v>
@@ -10460,15 +10460,15 @@
         <v>80</v>
       </c>
       <c r="G199" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H199" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B200">
         <v>63</v>
@@ -10488,15 +10488,15 @@
         <v>63</v>
       </c>
       <c r="G200" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H200" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B201">
         <v>75</v>
@@ -10516,15 +10516,15 @@
         <v>98</v>
       </c>
       <c r="G201" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H201" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B202">
         <v>74</v>
@@ -10544,15 +10544,15 @@
         <v>88</v>
       </c>
       <c r="G202" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H202" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B203">
         <v>81</v>
@@ -10572,15 +10572,15 @@
         <v>93</v>
       </c>
       <c r="G203" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H203" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B204">
         <v>52</v>
@@ -10600,15 +10600,15 @@
         <v>52</v>
       </c>
       <c r="G204" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H204" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B205">
         <v>55</v>
@@ -10628,15 +10628,15 @@
         <v>55</v>
       </c>
       <c r="G205" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H205" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B206">
         <v>74</v>
@@ -10656,15 +10656,15 @@
         <v>74</v>
       </c>
       <c r="G206" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H206" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B207">
         <v>72</v>
@@ -10684,15 +10684,15 @@
         <v>72</v>
       </c>
       <c r="G207" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H207" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B208">
         <v>51</v>
@@ -10712,15 +10712,15 @@
         <v>68</v>
       </c>
       <c r="G208" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H208" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B209">
         <v>66</v>
@@ -10740,15 +10740,15 @@
         <v>66</v>
       </c>
       <c r="G209" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H209" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B210">
         <v>70</v>
@@ -10768,15 +10768,15 @@
         <v>70</v>
       </c>
       <c r="G210" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H210" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B211">
         <v>74</v>
@@ -10796,15 +10796,15 @@
         <v>74</v>
       </c>
       <c r="G211" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H211" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A212" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B212">
         <v>75</v>
@@ -10824,15 +10824,15 @@
         <v>95</v>
       </c>
       <c r="G212" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H212" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A213" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B213">
         <v>85</v>
@@ -10852,15 +10852,15 @@
         <v>85</v>
       </c>
       <c r="G213" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H213" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A214" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B214">
         <v>87</v>
@@ -10880,15 +10880,15 @@
         <v>87</v>
       </c>
       <c r="G214" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H214" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B215">
         <v>20</v>
@@ -10908,15 +10908,15 @@
         <v>74</v>
       </c>
       <c r="G215" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H215" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A216" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B216">
         <v>54</v>
@@ -10936,15 +10936,15 @@
         <v>85</v>
       </c>
       <c r="G216" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H216" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B217">
         <v>68</v>
@@ -10964,15 +10964,15 @@
         <v>68</v>
       </c>
       <c r="G217" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H217" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B218">
         <v>36</v>
@@ -10992,15 +10992,15 @@
         <v>70</v>
       </c>
       <c r="G218" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H218" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B219">
         <v>23</v>
@@ -11020,15 +11020,15 @@
         <v>80</v>
       </c>
       <c r="G219" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H219" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B220">
         <v>69</v>
@@ -11048,15 +11048,15 @@
         <v>69</v>
       </c>
       <c r="G220" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H220" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B221">
         <v>65</v>
@@ -11076,15 +11076,15 @@
         <v>65</v>
       </c>
       <c r="G221" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H221" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B222">
         <v>67</v>
@@ -11104,15 +11104,15 @@
         <v>67</v>
       </c>
       <c r="G222" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H222" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B223">
         <v>63</v>
@@ -11132,15 +11132,15 @@
         <v>63</v>
       </c>
       <c r="G223" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H223" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B224">
         <v>58</v>
@@ -11160,15 +11160,15 @@
         <v>58</v>
       </c>
       <c r="G224" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H224" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B225">
         <v>35</v>
@@ -11188,15 +11188,15 @@
         <v>65</v>
       </c>
       <c r="G225" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H225" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B226">
         <v>72</v>
@@ -11216,15 +11216,15 @@
         <v>72</v>
       </c>
       <c r="G226" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H226" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A227" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B227">
         <v>70</v>
@@ -11244,15 +11244,15 @@
         <v>70</v>
       </c>
       <c r="G227" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H227" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A228" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B228">
         <v>53</v>
@@ -11272,15 +11272,15 @@
         <v>53</v>
       </c>
       <c r="G228" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H228" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A229" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B229">
         <v>51</v>
@@ -11300,15 +11300,15 @@
         <v>51</v>
       </c>
       <c r="G229" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H229" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A230" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B230">
         <v>65</v>
@@ -11328,15 +11328,15 @@
         <v>65</v>
       </c>
       <c r="G230" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H230" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A231" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B231">
         <v>65</v>
@@ -11356,15 +11356,15 @@
         <v>65</v>
       </c>
       <c r="G231" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H231" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A232" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B232">
         <v>82</v>
@@ -11384,15 +11384,15 @@
         <v>82</v>
       </c>
       <c r="G232" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H232" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B233">
         <v>94</v>
@@ -11412,15 +11412,15 @@
         <v>94</v>
       </c>
       <c r="G233" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H233" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A234" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B234">
         <v>34</v>
@@ -11440,15 +11440,15 @@
         <v>62</v>
       </c>
       <c r="G234" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H234" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B235">
         <v>72</v>
@@ -11468,15 +11468,15 @@
         <v>72</v>
       </c>
       <c r="G235" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H235" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A236" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B236">
         <v>69</v>
@@ -11496,15 +11496,15 @@
         <v>69</v>
       </c>
       <c r="G236" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H236" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A237" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B237">
         <v>95</v>
@@ -11524,15 +11524,15 @@
         <v>95</v>
       </c>
       <c r="G237" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H237" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A238" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B238">
         <v>72</v>
@@ -11552,15 +11552,15 @@
         <v>72</v>
       </c>
       <c r="G238" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H238" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A239" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B239">
         <v>70</v>
@@ -11580,15 +11580,15 @@
         <v>70</v>
       </c>
       <c r="G239" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H239" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A240" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B240">
         <v>90</v>
@@ -11608,15 +11608,15 @@
         <v>90</v>
       </c>
       <c r="G240" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H240" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B241">
         <v>60</v>
@@ -11636,15 +11636,15 @@
         <v>62</v>
       </c>
       <c r="G241" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H241" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A242" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B242">
         <v>60</v>
@@ -11664,15 +11664,15 @@
         <v>60</v>
       </c>
       <c r="G242" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H242" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A243" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B243">
         <v>68</v>
@@ -11692,15 +11692,15 @@
         <v>91</v>
       </c>
       <c r="G243" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H243" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B244">
         <v>60</v>
@@ -11720,15 +11720,15 @@
         <v>60</v>
       </c>
       <c r="G244" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H244" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A245" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B245">
         <v>65</v>
@@ -11748,15 +11748,15 @@
         <v>65</v>
       </c>
       <c r="G245" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H245" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A246" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B246">
         <v>56</v>
@@ -11776,15 +11776,15 @@
         <v>56</v>
       </c>
       <c r="G246" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H246" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A247" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B247">
         <v>61</v>
@@ -11804,15 +11804,15 @@
         <v>61</v>
       </c>
       <c r="G247" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H247" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A248" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B248">
         <v>62</v>
@@ -11832,15 +11832,15 @@
         <v>62</v>
       </c>
       <c r="G248" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H248" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B249">
         <v>57</v>
@@ -11860,15 +11860,15 @@
         <v>57</v>
       </c>
       <c r="G249" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H249" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B250">
         <v>23</v>
@@ -11888,15 +11888,15 @@
         <v>78</v>
       </c>
       <c r="G250" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H250" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A251" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B251">
         <v>45</v>
@@ -11916,15 +11916,15 @@
         <v>61</v>
       </c>
       <c r="G251" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H251" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A252" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B252">
         <v>97</v>
@@ -11944,15 +11944,15 @@
         <v>97</v>
       </c>
       <c r="G252" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H252" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B253">
         <v>1</v>
@@ -11972,15 +11972,15 @@
         <v>1</v>
       </c>
       <c r="G253" t="s">
+        <v>539</v>
+      </c>
+      <c r="H253" t="s">
         <v>540</v>
-      </c>
-      <c r="H253" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A254" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B254">
         <v>78</v>
@@ -12000,15 +12000,15 @@
         <v>78</v>
       </c>
       <c r="G254" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H254" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A255" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B255">
         <v>58</v>
@@ -12028,15 +12028,15 @@
         <v>58</v>
       </c>
       <c r="G255" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H255" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A256" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B256">
         <v>90</v>
@@ -12056,15 +12056,15 @@
         <v>90</v>
       </c>
       <c r="G256" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H256" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A257" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B257">
         <v>86</v>
@@ -12084,15 +12084,15 @@
         <v>86</v>
       </c>
       <c r="G257" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H257" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A258" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B258">
         <v>45</v>
@@ -12112,15 +12112,15 @@
         <v>84</v>
       </c>
       <c r="G258" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H258" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B259">
         <v>95</v>
@@ -12140,15 +12140,15 @@
         <v>95</v>
       </c>
       <c r="G259" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H259" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A260" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B260">
         <v>65</v>
@@ -12168,15 +12168,15 @@
         <v>65</v>
       </c>
       <c r="G260" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H260" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A261" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B261">
         <v>67</v>
@@ -12196,10 +12196,10 @@
         <v>67</v>
       </c>
       <c r="G261" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H261" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
   </sheetData>
@@ -12340,13 +12340,13 @@
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B7" t="s">
         <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -12768,7 +12768,7 @@
       <c r="AA56" s="5"/>
       <c r="AB56" s="5"/>
       <c r="AH56" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="57" spans="5:34" x14ac:dyDescent="0.45">
@@ -12869,7 +12869,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
@@ -12892,22 +12892,22 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.45">
@@ -12915,27 +12915,27 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
@@ -12943,21 +12943,21 @@
         <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G21" s="11" t="s">
         <v>43</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G22" s="11">
         <v>2</v>
@@ -12971,7 +12971,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G23" s="11">
         <v>3</v>
@@ -13051,24 +13051,24 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B33" s="16" t="s">
+        <v>312</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>311</v>
+      </c>
+      <c r="D33" t="s">
         <v>313</v>
       </c>
-      <c r="C33" s="15" t="s">
-        <v>312</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>314</v>
       </c>
-      <c r="E33" t="s">
-        <v>315</v>
-      </c>
       <c r="F33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.45">
@@ -13224,198 +13224,198 @@
     <row r="44" spans="2:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="45" spans="2:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B45" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="C45" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="C45" s="12" t="s">
+      <c r="D45" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="E45" s="12" t="s">
         <v>264</v>
-      </c>
-      <c r="E45" s="12" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="46" spans="2:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B46" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C46" s="12" t="s">
         <v>266</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="D46" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="D46" s="13" t="s">
+      <c r="E46" s="14" t="s">
         <v>268</v>
-      </c>
-      <c r="E46" s="14" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="47" spans="2:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B47" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="C47" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="C47" s="12" t="s">
+      <c r="D47" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="D47" s="13" t="s">
-        <v>272</v>
-      </c>
       <c r="E47" s="14" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="48" spans="2:6" ht="28.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B48" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="C48" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="C48" s="12" t="s">
+      <c r="D48" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="E48" s="14" t="s">
         <v>274</v>
-      </c>
-      <c r="D48" s="13" t="s">
-        <v>301</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="49" spans="2:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B49" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C49" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="C49" s="12" t="s">
+      <c r="D49" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="E49" s="14" t="s">
         <v>277</v>
-      </c>
-      <c r="D49" s="13" t="s">
-        <v>302</v>
-      </c>
-      <c r="E49" s="14" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="50" spans="2:5" ht="56.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B50" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="C50" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="C50" s="12" t="s">
+      <c r="D50" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="E50" s="14" t="s">
         <v>280</v>
-      </c>
-      <c r="D50" s="13" t="s">
-        <v>303</v>
-      </c>
-      <c r="E50" s="14" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="51" spans="2:5" ht="56.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B51" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="C51" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="C51" s="12" t="s">
-        <v>283</v>
-      </c>
       <c r="D51" s="13" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="52" spans="2:5" ht="70.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B52" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="C52" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="D52" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="E52" s="14" t="s">
         <v>285</v>
-      </c>
-      <c r="D52" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="E52" s="14" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="53" spans="2:5" ht="56.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B53" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="C53" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="C53" s="12" t="s">
-        <v>288</v>
-      </c>
       <c r="D53" s="13" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="54" spans="2:5" ht="56.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B54" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="C54" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="C54" s="12" t="s">
-        <v>290</v>
-      </c>
       <c r="D54" s="13" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="55" spans="2:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B55" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C55" s="12" t="s">
         <v>291</v>
       </c>
-      <c r="C55" s="12" t="s">
-        <v>292</v>
-      </c>
       <c r="D55" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="56" spans="2:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B56" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="C56" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="C56" s="12" t="s">
-        <v>294</v>
-      </c>
       <c r="D56" s="13" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="57" spans="2:5" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B57" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="C57" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="C57" s="12" t="s">
+      <c r="D57" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="D57" s="13" t="s">
-        <v>297</v>
-      </c>
       <c r="E57" s="14" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="58" spans="2:5" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B58" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="C58" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="C58" s="12" t="s">
+      <c r="D58" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="D58" s="13" t="s">
-        <v>300</v>
-      </c>
       <c r="E58" s="14" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>

--- a/docs/삼국지 약식체스.xlsx
+++ b/docs/삼국지 약식체스.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\SamChess\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A807ACF2-73FD-424B-9193-3D1AB10590A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B401FCB-A0F0-41AA-8FF1-8A1C43C02E51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16200" yWindow="-3090" windowWidth="15480" windowHeight="10170" xr2:uid="{67B41BAA-AEF2-4AF0-8CD2-0E8DEEEF200D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{67B41BAA-AEF2-4AF0-8CD2-0E8DEEEF200D}"/>
   </bookViews>
   <sheets>
     <sheet name="고유 스킬" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="558">
   <si>
     <t>관우</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1801,10 +1801,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>장노</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>진궁</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1992,6 +1988,10 @@
   </si>
   <si>
     <t>구호탄랑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장로</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2557,7 +2557,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C99257-A4BA-4664-86A0-27A3B586B2CF}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:E142"/>
+  <dimension ref="A1:E141"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="4.83203125" bestFit="1" customWidth="1"/>
@@ -2596,7 +2596,7 @@
         <v>53</v>
       </c>
       <c r="E2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
@@ -2613,7 +2613,7 @@
         <v>57</v>
       </c>
       <c r="E3" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
@@ -2630,7 +2630,7 @@
         <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
@@ -2647,7 +2647,7 @@
         <v>91</v>
       </c>
       <c r="E5" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
@@ -2664,7 +2664,7 @@
         <v>99</v>
       </c>
       <c r="E6" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
@@ -2681,7 +2681,7 @@
         <v>108</v>
       </c>
       <c r="E7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
@@ -2698,7 +2698,7 @@
         <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
@@ -2732,7 +2732,7 @@
         <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
@@ -2749,7 +2749,7 @@
         <v>86</v>
       </c>
       <c r="E11" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
@@ -2766,7 +2766,7 @@
         <v>31</v>
       </c>
       <c r="E12" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
@@ -2811,13 +2811,13 @@
         <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D15" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E15" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
@@ -2828,7 +2828,7 @@
         <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D16" t="s">
         <v>80</v>
@@ -2868,7 +2868,7 @@
         <v>93</v>
       </c>
       <c r="E19" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
@@ -2902,7 +2902,7 @@
         <v>119</v>
       </c>
       <c r="E21" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
@@ -2919,7 +2919,7 @@
         <v>10</v>
       </c>
       <c r="E22" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
@@ -2936,7 +2936,7 @@
         <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
@@ -2953,7 +2953,7 @@
         <v>8</v>
       </c>
       <c r="E24" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
@@ -2970,7 +2970,7 @@
         <v>20</v>
       </c>
       <c r="E25" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
@@ -2987,7 +2987,7 @@
         <v>23</v>
       </c>
       <c r="E26" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
@@ -3004,7 +3004,7 @@
         <v>26</v>
       </c>
       <c r="E27" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
@@ -3038,7 +3038,7 @@
         <v>50</v>
       </c>
       <c r="E29" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
@@ -3055,7 +3055,7 @@
         <v>100</v>
       </c>
       <c r="E30" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.45">
@@ -3089,7 +3089,7 @@
         <v>123</v>
       </c>
       <c r="E32" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
@@ -3106,7 +3106,7 @@
         <v>127</v>
       </c>
       <c r="E33" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
@@ -3140,7 +3140,7 @@
         <v>236</v>
       </c>
       <c r="E36" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
@@ -3157,7 +3157,7 @@
         <v>236</v>
       </c>
       <c r="E37" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.45">
@@ -3174,7 +3174,7 @@
         <v>236</v>
       </c>
       <c r="E38" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
@@ -3191,7 +3191,7 @@
         <v>236</v>
       </c>
       <c r="E39" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
@@ -3208,7 +3208,7 @@
         <v>236</v>
       </c>
       <c r="E40" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.45">
@@ -3225,7 +3225,7 @@
         <v>236</v>
       </c>
       <c r="E41" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
@@ -3242,7 +3242,7 @@
         <v>236</v>
       </c>
       <c r="E42" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
@@ -3259,7 +3259,7 @@
         <v>236</v>
       </c>
       <c r="E43" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
@@ -3276,7 +3276,7 @@
         <v>236</v>
       </c>
       <c r="E44" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
@@ -3293,7 +3293,7 @@
         <v>236</v>
       </c>
       <c r="E45" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
@@ -3310,7 +3310,7 @@
         <v>238</v>
       </c>
       <c r="E46" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
@@ -3327,7 +3327,7 @@
         <v>238</v>
       </c>
       <c r="E47" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">
@@ -3344,7 +3344,7 @@
         <v>238</v>
       </c>
       <c r="E48" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
@@ -3361,7 +3361,7 @@
         <v>238</v>
       </c>
       <c r="E49" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
@@ -3378,7 +3378,7 @@
         <v>238</v>
       </c>
       <c r="E50" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
@@ -3395,7 +3395,7 @@
         <v>238</v>
       </c>
       <c r="E51" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
@@ -3434,7 +3434,7 @@
         <v>240</v>
       </c>
       <c r="E54" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
@@ -3451,7 +3451,7 @@
         <v>240</v>
       </c>
       <c r="E55" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
@@ -3468,7 +3468,7 @@
         <v>240</v>
       </c>
       <c r="E56" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
@@ -3485,7 +3485,7 @@
         <v>240</v>
       </c>
       <c r="E57" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
@@ -3502,7 +3502,7 @@
         <v>240</v>
       </c>
       <c r="E58" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">
@@ -3519,7 +3519,7 @@
         <v>240</v>
       </c>
       <c r="E59" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
@@ -3536,7 +3536,7 @@
         <v>240</v>
       </c>
       <c r="E60" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
@@ -3553,7 +3553,7 @@
         <v>240</v>
       </c>
       <c r="E61" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">
@@ -3570,7 +3570,7 @@
         <v>240</v>
       </c>
       <c r="E62" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.45">
@@ -3587,7 +3587,7 @@
         <v>240</v>
       </c>
       <c r="E63" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.45">
@@ -3604,7 +3604,7 @@
         <v>240</v>
       </c>
       <c r="E64" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.45">
@@ -3621,7 +3621,7 @@
         <v>240</v>
       </c>
       <c r="E65" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.45">
@@ -3638,7 +3638,7 @@
         <v>240</v>
       </c>
       <c r="E66" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.45">
@@ -3655,7 +3655,7 @@
         <v>240</v>
       </c>
       <c r="E67" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.45">
@@ -3672,7 +3672,7 @@
         <v>243</v>
       </c>
       <c r="E68" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.45">
@@ -3689,7 +3689,7 @@
         <v>243</v>
       </c>
       <c r="E69" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.45">
@@ -3706,7 +3706,7 @@
         <v>243</v>
       </c>
       <c r="E70" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
@@ -3714,7 +3714,7 @@
         <v>233</v>
       </c>
       <c r="B71" t="s">
-        <v>507</v>
+        <v>557</v>
       </c>
       <c r="C71" t="s">
         <v>242</v>
@@ -3723,7 +3723,7 @@
         <v>243</v>
       </c>
       <c r="E71" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.45">
@@ -3740,7 +3740,7 @@
         <v>243</v>
       </c>
       <c r="E72" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.45">
@@ -3757,7 +3757,7 @@
         <v>243</v>
       </c>
       <c r="E73" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.45">
@@ -3774,7 +3774,7 @@
         <v>243</v>
       </c>
       <c r="E74" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.45">
@@ -3791,7 +3791,7 @@
         <v>243</v>
       </c>
       <c r="E75" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
@@ -3808,7 +3808,7 @@
         <v>243</v>
       </c>
       <c r="E76" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
@@ -3825,7 +3825,7 @@
         <v>243</v>
       </c>
       <c r="E77" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.45">
@@ -3898,7 +3898,7 @@
         <v>245</v>
       </c>
       <c r="E82" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.45">
@@ -3915,7 +3915,7 @@
         <v>245</v>
       </c>
       <c r="E83" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.45">
@@ -3932,7 +3932,7 @@
         <v>245</v>
       </c>
       <c r="E84" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.45">
@@ -3949,7 +3949,7 @@
         <v>245</v>
       </c>
       <c r="E85" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.45">
@@ -3966,7 +3966,7 @@
         <v>245</v>
       </c>
       <c r="E86" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.45">
@@ -3983,7 +3983,7 @@
         <v>245</v>
       </c>
       <c r="E87" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.45">
@@ -4000,7 +4000,7 @@
         <v>245</v>
       </c>
       <c r="E88" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.45">
@@ -4017,7 +4017,7 @@
         <v>255</v>
       </c>
       <c r="E89" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.45">
@@ -4034,7 +4034,7 @@
         <v>255</v>
       </c>
       <c r="E90" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.45">
@@ -4051,7 +4051,7 @@
         <v>255</v>
       </c>
       <c r="E91" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.45">
@@ -4068,7 +4068,7 @@
         <v>255</v>
       </c>
       <c r="E92" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.45">
@@ -4085,7 +4085,7 @@
         <v>255</v>
       </c>
       <c r="E93" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.45">
@@ -4102,7 +4102,7 @@
         <v>255</v>
       </c>
       <c r="E94" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.45">
@@ -4119,7 +4119,7 @@
         <v>255</v>
       </c>
       <c r="E95" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.45">
@@ -4136,7 +4136,7 @@
         <v>255</v>
       </c>
       <c r="E96" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.45">
@@ -4153,7 +4153,7 @@
         <v>255</v>
       </c>
       <c r="E97" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.45">
@@ -4170,7 +4170,7 @@
         <v>255</v>
       </c>
       <c r="E98" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.45">
@@ -4243,7 +4243,7 @@
         <v>256</v>
       </c>
       <c r="E103" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.45">
@@ -4260,7 +4260,7 @@
         <v>256</v>
       </c>
       <c r="E104" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.45">
@@ -4277,7 +4277,7 @@
         <v>256</v>
       </c>
       <c r="E105" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.45">
@@ -4294,7 +4294,7 @@
         <v>256</v>
       </c>
       <c r="E106" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.45">
@@ -4311,7 +4311,7 @@
         <v>256</v>
       </c>
       <c r="E107" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.45">
@@ -4328,7 +4328,7 @@
         <v>256</v>
       </c>
       <c r="E108" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.45">
@@ -4336,7 +4336,7 @@
         <v>234</v>
       </c>
       <c r="B109" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="C109" t="s">
         <v>257</v>
@@ -4345,7 +4345,7 @@
         <v>256</v>
       </c>
       <c r="E109" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.45">
@@ -4353,7 +4353,7 @@
         <v>234</v>
       </c>
       <c r="B110" t="s">
-        <v>191</v>
+        <v>150</v>
       </c>
       <c r="C110" t="s">
         <v>257</v>
@@ -4362,7 +4362,7 @@
         <v>256</v>
       </c>
       <c r="E110" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.45">
@@ -4370,7 +4370,7 @@
         <v>234</v>
       </c>
       <c r="B111" t="s">
-        <v>150</v>
+        <v>507</v>
       </c>
       <c r="C111" t="s">
         <v>257</v>
@@ -4379,7 +4379,7 @@
         <v>256</v>
       </c>
       <c r="E111" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.45">
@@ -4387,7 +4387,7 @@
         <v>234</v>
       </c>
       <c r="B112" t="s">
-        <v>508</v>
+        <v>176</v>
       </c>
       <c r="C112" t="s">
         <v>257</v>
@@ -4396,7 +4396,7 @@
         <v>256</v>
       </c>
       <c r="E112" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.45">
@@ -4404,16 +4404,16 @@
         <v>234</v>
       </c>
       <c r="B113" t="s">
-        <v>176</v>
+        <v>232</v>
       </c>
       <c r="C113" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="D113" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="E113" t="s">
-        <v>553</v>
+        <v>250</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.45">
@@ -4421,7 +4421,7 @@
         <v>234</v>
       </c>
       <c r="B114" t="s">
-        <v>232</v>
+        <v>205</v>
       </c>
       <c r="C114" t="s">
         <v>248</v>
@@ -4438,7 +4438,7 @@
         <v>234</v>
       </c>
       <c r="B115" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="C115" t="s">
         <v>248</v>
@@ -4447,7 +4447,7 @@
         <v>249</v>
       </c>
       <c r="E115" t="s">
-        <v>250</v>
+        <v>553</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.45">
@@ -4455,7 +4455,7 @@
         <v>234</v>
       </c>
       <c r="B116" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="C116" t="s">
         <v>248</v>
@@ -4464,7 +4464,7 @@
         <v>249</v>
       </c>
       <c r="E116" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.45">
@@ -4472,7 +4472,7 @@
         <v>234</v>
       </c>
       <c r="B117" t="s">
-        <v>177</v>
+        <v>222</v>
       </c>
       <c r="C117" t="s">
         <v>248</v>
@@ -4481,7 +4481,7 @@
         <v>249</v>
       </c>
       <c r="E117" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.45">
@@ -4489,7 +4489,7 @@
         <v>234</v>
       </c>
       <c r="B118" t="s">
-        <v>222</v>
+        <v>142</v>
       </c>
       <c r="C118" t="s">
         <v>248</v>
@@ -4498,7 +4498,7 @@
         <v>249</v>
       </c>
       <c r="E118" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.45">
@@ -4506,7 +4506,7 @@
         <v>234</v>
       </c>
       <c r="B119" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="C119" t="s">
         <v>248</v>
@@ -4515,7 +4515,7 @@
         <v>249</v>
       </c>
       <c r="E119" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.45">
@@ -4523,7 +4523,7 @@
         <v>234</v>
       </c>
       <c r="B120" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C120" t="s">
         <v>248</v>
@@ -4532,7 +4532,7 @@
         <v>249</v>
       </c>
       <c r="E120" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.45">
@@ -4540,7 +4540,7 @@
         <v>234</v>
       </c>
       <c r="B121" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="C121" t="s">
         <v>248</v>
@@ -4549,7 +4549,7 @@
         <v>249</v>
       </c>
       <c r="E121" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.45">
@@ -4557,7 +4557,7 @@
         <v>234</v>
       </c>
       <c r="B122" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="C122" t="s">
         <v>248</v>
@@ -4566,7 +4566,7 @@
         <v>249</v>
       </c>
       <c r="E122" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.45">
@@ -4574,7 +4574,7 @@
         <v>234</v>
       </c>
       <c r="B123" t="s">
-        <v>198</v>
+        <v>156</v>
       </c>
       <c r="C123" t="s">
         <v>248</v>
@@ -4583,7 +4583,7 @@
         <v>249</v>
       </c>
       <c r="E123" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.45">
@@ -4591,7 +4591,7 @@
         <v>234</v>
       </c>
       <c r="B124" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C124" t="s">
         <v>248</v>
@@ -4600,46 +4600,46 @@
         <v>249</v>
       </c>
       <c r="E124" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A125" t="s">
-        <v>234</v>
-      </c>
-      <c r="B125" t="s">
-        <v>157</v>
-      </c>
-      <c r="C125" t="s">
-        <v>248</v>
-      </c>
-      <c r="D125" t="s">
-        <v>249</v>
-      </c>
-      <c r="E125" t="s">
-        <v>554</v>
-      </c>
+      <c r="C125" s="9"/>
+      <c r="D125" s="9"/>
+      <c r="E125" s="9"/>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="C126" s="9"/>
-      <c r="D126" s="9"/>
-      <c r="E126" s="9"/>
+      <c r="A126" t="s">
+        <v>46</v>
+      </c>
+      <c r="B126" t="s">
+        <v>4</v>
+      </c>
+      <c r="C126" t="s">
+        <v>3</v>
+      </c>
+      <c r="D126" t="s">
+        <v>5</v>
+      </c>
+      <c r="E126" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
-        <v>46</v>
+        <v>234</v>
       </c>
       <c r="B127" t="s">
-        <v>4</v>
+        <v>196</v>
       </c>
       <c r="C127" t="s">
-        <v>3</v>
+        <v>260</v>
       </c>
       <c r="D127" t="s">
-        <v>5</v>
+        <v>259</v>
       </c>
       <c r="E127" t="s">
-        <v>12</v>
+        <v>258</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.45">
@@ -4647,7 +4647,7 @@
         <v>234</v>
       </c>
       <c r="B128" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="C128" t="s">
         <v>260</v>
@@ -4664,7 +4664,7 @@
         <v>234</v>
       </c>
       <c r="B129" t="s">
-        <v>210</v>
+        <v>183</v>
       </c>
       <c r="C129" t="s">
         <v>260</v>
@@ -4673,7 +4673,7 @@
         <v>259</v>
       </c>
       <c r="E129" t="s">
-        <v>258</v>
+        <v>554</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.45">
@@ -4681,7 +4681,7 @@
         <v>234</v>
       </c>
       <c r="B130" t="s">
-        <v>183</v>
+        <v>228</v>
       </c>
       <c r="C130" t="s">
         <v>260</v>
@@ -4690,7 +4690,7 @@
         <v>259</v>
       </c>
       <c r="E130" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.45">
@@ -4698,7 +4698,7 @@
         <v>234</v>
       </c>
       <c r="B131" t="s">
-        <v>228</v>
+        <v>171</v>
       </c>
       <c r="C131" t="s">
         <v>260</v>
@@ -4707,7 +4707,7 @@
         <v>259</v>
       </c>
       <c r="E131" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.45">
@@ -4715,7 +4715,7 @@
         <v>234</v>
       </c>
       <c r="B132" t="s">
-        <v>171</v>
+        <v>220</v>
       </c>
       <c r="C132" t="s">
         <v>260</v>
@@ -4724,7 +4724,7 @@
         <v>259</v>
       </c>
       <c r="E132" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.45">
@@ -4732,7 +4732,7 @@
         <v>234</v>
       </c>
       <c r="B133" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C133" t="s">
         <v>260</v>
@@ -4741,7 +4741,7 @@
         <v>259</v>
       </c>
       <c r="E133" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.45">
@@ -4749,7 +4749,7 @@
         <v>234</v>
       </c>
       <c r="B134" t="s">
-        <v>217</v>
+        <v>173</v>
       </c>
       <c r="C134" t="s">
         <v>260</v>
@@ -4758,7 +4758,7 @@
         <v>259</v>
       </c>
       <c r="E134" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.45">
@@ -4766,7 +4766,7 @@
         <v>234</v>
       </c>
       <c r="B135" t="s">
-        <v>173</v>
+        <v>208</v>
       </c>
       <c r="C135" t="s">
         <v>260</v>
@@ -4775,7 +4775,7 @@
         <v>259</v>
       </c>
       <c r="E135" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.45">
@@ -4783,7 +4783,7 @@
         <v>234</v>
       </c>
       <c r="B136" t="s">
-        <v>208</v>
+        <v>182</v>
       </c>
       <c r="C136" t="s">
         <v>260</v>
@@ -4792,7 +4792,7 @@
         <v>259</v>
       </c>
       <c r="E136" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.45">
@@ -4800,7 +4800,7 @@
         <v>234</v>
       </c>
       <c r="B137" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="C137" t="s">
         <v>260</v>
@@ -4809,7 +4809,7 @@
         <v>259</v>
       </c>
       <c r="E137" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.45">
@@ -4817,7 +4817,7 @@
         <v>234</v>
       </c>
       <c r="B138" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="C138" t="s">
         <v>260</v>
@@ -4826,58 +4826,41 @@
         <v>259</v>
       </c>
       <c r="E138" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A139" t="s">
-        <v>234</v>
-      </c>
-      <c r="B139" t="s">
-        <v>170</v>
-      </c>
-      <c r="C139" t="s">
-        <v>260</v>
-      </c>
-      <c r="D139" t="s">
-        <v>259</v>
-      </c>
-      <c r="E139" t="s">
-        <v>555</v>
+        <v>554</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A140" t="s">
+        <v>46</v>
+      </c>
+      <c r="B140" t="s">
+        <v>4</v>
+      </c>
+      <c r="C140" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" t="s">
+        <v>5</v>
+      </c>
+      <c r="E140" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
-        <v>46</v>
+        <v>539</v>
       </c>
       <c r="B141" t="s">
-        <v>4</v>
+        <v>537</v>
       </c>
       <c r="C141" t="s">
-        <v>3</v>
+        <v>540</v>
       </c>
       <c r="D141" t="s">
-        <v>5</v>
+        <v>541</v>
       </c>
       <c r="E141" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A142" t="s">
-        <v>540</v>
-      </c>
-      <c r="B142" t="s">
-        <v>538</v>
-      </c>
-      <c r="C142" t="s">
-        <v>541</v>
-      </c>
-      <c r="D142" t="s">
-        <v>542</v>
-      </c>
-      <c r="E142" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
   </sheetData>
@@ -5708,7 +5691,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B30">
         <v>70</v>
@@ -11952,7 +11935,7 @@
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B253">
         <v>1</v>
@@ -11972,10 +11955,10 @@
         <v>1</v>
       </c>
       <c r="G253" t="s">
+        <v>538</v>
+      </c>
+      <c r="H253" t="s">
         <v>539</v>
-      </c>
-      <c r="H253" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.45">
@@ -12925,12 +12908,12 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">

--- a/docs/삼국지 약식체스.xlsx
+++ b/docs/삼국지 약식체스.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\SamChess\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B401FCB-A0F0-41AA-8FF1-8A1C43C02E51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C3AD7A-2D46-4F5D-AE65-C12F0C57F7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{67B41BAA-AEF2-4AF0-8CD2-0E8DEEEF200D}"/>
+    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="13770" xr2:uid="{67B41BAA-AEF2-4AF0-8CD2-0E8DEEEF200D}"/>
   </bookViews>
   <sheets>
     <sheet name="고유 스킬" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1841" uniqueCount="600">
   <si>
     <t>관우</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1217,10 +1217,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>레벨업 확률</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>적군 전체의 MP를 0으로 만듦</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1992,6 +1988,176 @@
   </si>
   <si>
     <t>장로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>냥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>만원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오라 타입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지 반감</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유형</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아군 1인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적군 전체</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무적</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>크리티컬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아군 전체</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자유 이동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아군 자신</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아군 다수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적군 1인</t>
+  </si>
+  <si>
+    <t>적군 1인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>컨트롤 탈취</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적군 2인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시한부 사망</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오라 대상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>환술성공</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적공격 절반</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적군 다수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>즉사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지반감+크리티컬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조건부 컨트롤 탈취</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조건 달성된 적군</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격력 누적</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>반격</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP 회복</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조건부 아군 1인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쌍방 공격 강제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아군 자신, 적군 1인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시간 조절</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사망후 부활</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP 소모 0</t>
+  </si>
+  <si>
+    <t>MP 소모 0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대기시간 증가</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2111,7 +2277,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -2158,13 +2324,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2221,6 +2398,12 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2557,15 +2740,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C99257-A4BA-4664-86A0-27A3B586B2CF}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:E141"/>
+  <dimension ref="A1:N141"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="4.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="17" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="49.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.58203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.6640625" style="20"/>
+    <col min="13" max="13" width="8.6640625" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>46</v>
       </c>
@@ -2581,8 +2769,17 @@
       <c r="E1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="H1" t="s">
+        <v>563</v>
+      </c>
+      <c r="I1" t="s">
+        <v>565</v>
+      </c>
+      <c r="J1" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -2596,10 +2793,19 @@
         <v>53</v>
       </c>
       <c r="E2" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+        <v>511</v>
+      </c>
+      <c r="H2" s="20">
+        <v>1</v>
+      </c>
+      <c r="I2" t="s">
+        <v>564</v>
+      </c>
+      <c r="J2" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>47</v>
       </c>
@@ -2613,10 +2819,19 @@
         <v>57</v>
       </c>
       <c r="E3" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+        <v>510</v>
+      </c>
+      <c r="H3" s="20">
+        <v>5</v>
+      </c>
+      <c r="I3" t="s">
+        <v>572</v>
+      </c>
+      <c r="J3" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>47</v>
       </c>
@@ -2630,10 +2845,19 @@
         <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+        <v>529</v>
+      </c>
+      <c r="H4" s="20">
+        <v>2</v>
+      </c>
+      <c r="I4" t="s">
+        <v>566</v>
+      </c>
+      <c r="J4" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>47</v>
       </c>
@@ -2647,10 +2871,19 @@
         <v>91</v>
       </c>
       <c r="E5" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+        <v>531</v>
+      </c>
+      <c r="H5" s="20">
+        <v>18</v>
+      </c>
+      <c r="I5" t="s">
+        <v>592</v>
+      </c>
+      <c r="J5" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>47</v>
       </c>
@@ -2664,10 +2897,19 @@
         <v>99</v>
       </c>
       <c r="E6" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+        <v>530</v>
+      </c>
+      <c r="H6" s="20">
+        <v>17</v>
+      </c>
+      <c r="I6" t="s">
+        <v>590</v>
+      </c>
+      <c r="J6" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -2681,10 +2923,19 @@
         <v>108</v>
       </c>
       <c r="E7" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+        <v>509</v>
+      </c>
+      <c r="H7" s="20">
+        <v>3</v>
+      </c>
+      <c r="I7" t="s">
+        <v>569</v>
+      </c>
+      <c r="J7" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>47</v>
       </c>
@@ -2698,10 +2949,19 @@
         <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+        <v>512</v>
+      </c>
+      <c r="H8" s="20">
+        <v>4</v>
+      </c>
+      <c r="I8" t="s">
+        <v>570</v>
+      </c>
+      <c r="J8" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -2717,8 +2977,17 @@
       <c r="E9" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="H9" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="I9" t="s">
+        <v>590</v>
+      </c>
+      <c r="J9" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -2732,10 +3001,19 @@
         <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+        <v>513</v>
+      </c>
+      <c r="H10" s="20">
+        <v>1</v>
+      </c>
+      <c r="I10" t="s">
+        <v>564</v>
+      </c>
+      <c r="J10" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>47</v>
       </c>
@@ -2749,10 +3027,19 @@
         <v>86</v>
       </c>
       <c r="E11" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+        <v>532</v>
+      </c>
+      <c r="H11" s="20">
+        <v>1</v>
+      </c>
+      <c r="I11" t="s">
+        <v>564</v>
+      </c>
+      <c r="J11" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -2766,10 +3053,19 @@
         <v>31</v>
       </c>
       <c r="E12" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+        <v>514</v>
+      </c>
+      <c r="H12" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="I12" t="s">
+        <v>566</v>
+      </c>
+      <c r="J12" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>47</v>
       </c>
@@ -2785,8 +3081,11 @@
       <c r="E13" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="H13" s="20" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>47</v>
       </c>
@@ -2802,8 +3101,17 @@
       <c r="E14" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="H14" s="20">
+        <v>19</v>
+      </c>
+      <c r="I14" t="s">
+        <v>594</v>
+      </c>
+      <c r="J14" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>47</v>
       </c>
@@ -2811,16 +3119,25 @@
         <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D15" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E15" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+        <v>554</v>
+      </c>
+      <c r="H15" s="20">
+        <v>2</v>
+      </c>
+      <c r="I15" t="s">
+        <v>566</v>
+      </c>
+      <c r="J15" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>47</v>
       </c>
@@ -2828,7 +3145,7 @@
         <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D16" t="s">
         <v>80</v>
@@ -2836,8 +3153,20 @@
       <c r="E16" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="H16" s="20">
+        <v>6</v>
+      </c>
+      <c r="I16" t="s">
+        <v>577</v>
+      </c>
+      <c r="J16" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="H17" s="20"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -2853,8 +3182,9 @@
       <c r="E18" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="H18" s="20"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -2868,10 +3198,19 @@
         <v>93</v>
       </c>
       <c r="E19" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+        <v>515</v>
+      </c>
+      <c r="H19" s="20">
+        <v>7</v>
+      </c>
+      <c r="I19" t="s">
+        <v>579</v>
+      </c>
+      <c r="J19" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -2887,8 +3226,17 @@
       <c r="E20" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="H20" s="20">
+        <v>7</v>
+      </c>
+      <c r="I20" t="s">
+        <v>595</v>
+      </c>
+      <c r="J20" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -2902,10 +3250,19 @@
         <v>119</v>
       </c>
       <c r="E21" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+        <v>523</v>
+      </c>
+      <c r="H21" s="20">
+        <v>8</v>
+      </c>
+      <c r="I21" t="s">
+        <v>581</v>
+      </c>
+      <c r="J21" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -2919,10 +3276,25 @@
         <v>10</v>
       </c>
       <c r="E22" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+        <v>516</v>
+      </c>
+      <c r="H22" s="20">
+        <v>9</v>
+      </c>
+      <c r="I22" t="s">
+        <v>582</v>
+      </c>
+      <c r="J22" t="s">
+        <v>583</v>
+      </c>
+      <c r="K22" s="20">
+        <v>10</v>
+      </c>
+      <c r="L22" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -2936,10 +3308,19 @@
         <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+        <v>534</v>
+      </c>
+      <c r="H23" s="20">
+        <v>11</v>
+      </c>
+      <c r="I23" t="s">
+        <v>584</v>
+      </c>
+      <c r="J23" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>47</v>
       </c>
@@ -2953,10 +3334,19 @@
         <v>8</v>
       </c>
       <c r="E24" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+        <v>535</v>
+      </c>
+      <c r="H24" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="I24" t="s">
+        <v>599</v>
+      </c>
+      <c r="J24" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>47</v>
       </c>
@@ -2970,10 +3360,19 @@
         <v>20</v>
       </c>
       <c r="E25" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+        <v>517</v>
+      </c>
+      <c r="H25" s="20">
+        <v>12</v>
+      </c>
+      <c r="I25" t="s">
+        <v>585</v>
+      </c>
+      <c r="J25" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>47</v>
       </c>
@@ -2987,10 +3386,19 @@
         <v>23</v>
       </c>
       <c r="E26" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+        <v>518</v>
+      </c>
+      <c r="H26" s="20">
+        <v>4</v>
+      </c>
+      <c r="I26" t="s">
+        <v>570</v>
+      </c>
+      <c r="J26" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>47</v>
       </c>
@@ -3004,10 +3412,19 @@
         <v>26</v>
       </c>
       <c r="E27" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+        <v>519</v>
+      </c>
+      <c r="H27" s="20">
+        <v>4</v>
+      </c>
+      <c r="I27" t="s">
+        <v>570</v>
+      </c>
+      <c r="J27" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -3023,8 +3440,17 @@
       <c r="E28" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="H28" s="20">
+        <v>6</v>
+      </c>
+      <c r="I28" t="s">
+        <v>577</v>
+      </c>
+      <c r="J28" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>47</v>
       </c>
@@ -3038,10 +3464,13 @@
         <v>50</v>
       </c>
       <c r="E29" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+        <v>533</v>
+      </c>
+      <c r="H29" s="20" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>47</v>
       </c>
@@ -3055,10 +3484,31 @@
         <v>100</v>
       </c>
       <c r="E30" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+        <v>521</v>
+      </c>
+      <c r="H30" s="20">
+        <v>13</v>
+      </c>
+      <c r="I30" t="s">
+        <v>586</v>
+      </c>
+      <c r="J30" t="s">
+        <v>583</v>
+      </c>
+      <c r="K30" s="20">
+        <v>6</v>
+      </c>
+      <c r="L30" t="s">
+        <v>587</v>
+      </c>
+      <c r="M30" s="20">
+        <v>14</v>
+      </c>
+      <c r="N30" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>47</v>
       </c>
@@ -3072,10 +3522,13 @@
         <v>116</v>
       </c>
       <c r="E31" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+        <v>315</v>
+      </c>
+      <c r="H31" s="20" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>47</v>
       </c>
@@ -3089,10 +3542,19 @@
         <v>123</v>
       </c>
       <c r="E32" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+        <v>520</v>
+      </c>
+      <c r="H32" s="20">
+        <v>15</v>
+      </c>
+      <c r="I32" t="s">
+        <v>588</v>
+      </c>
+      <c r="J32" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>47</v>
       </c>
@@ -3106,10 +3568,22 @@
         <v>127</v>
       </c>
       <c r="E33" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+        <v>522</v>
+      </c>
+      <c r="H33" s="20">
+        <v>16</v>
+      </c>
+      <c r="I33" t="s">
+        <v>589</v>
+      </c>
+      <c r="J33" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="H34" s="20"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>46</v>
       </c>
@@ -3125,8 +3599,9 @@
       <c r="E35" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="H35" s="20"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>233</v>
       </c>
@@ -3140,10 +3615,19 @@
         <v>236</v>
       </c>
       <c r="E36" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+        <v>524</v>
+      </c>
+      <c r="H36" s="20">
+        <v>4</v>
+      </c>
+      <c r="I36" t="s">
+        <v>570</v>
+      </c>
+      <c r="J36" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>233</v>
       </c>
@@ -3157,10 +3641,19 @@
         <v>236</v>
       </c>
       <c r="E37" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+        <v>524</v>
+      </c>
+      <c r="H37" s="20">
+        <v>4</v>
+      </c>
+      <c r="I37" t="s">
+        <v>570</v>
+      </c>
+      <c r="J37" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>233</v>
       </c>
@@ -3174,10 +3667,19 @@
         <v>236</v>
       </c>
       <c r="E38" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+        <v>545</v>
+      </c>
+      <c r="H38" s="20">
+        <v>4</v>
+      </c>
+      <c r="I38" t="s">
+        <v>570</v>
+      </c>
+      <c r="J38" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>233</v>
       </c>
@@ -3191,10 +3693,19 @@
         <v>236</v>
       </c>
       <c r="E39" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+        <v>545</v>
+      </c>
+      <c r="H39" s="20">
+        <v>4</v>
+      </c>
+      <c r="I39" t="s">
+        <v>570</v>
+      </c>
+      <c r="J39" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>233</v>
       </c>
@@ -3208,10 +3719,19 @@
         <v>236</v>
       </c>
       <c r="E40" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+        <v>545</v>
+      </c>
+      <c r="H40" s="20">
+        <v>4</v>
+      </c>
+      <c r="I40" t="s">
+        <v>570</v>
+      </c>
+      <c r="J40" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>233</v>
       </c>
@@ -3225,10 +3745,19 @@
         <v>236</v>
       </c>
       <c r="E41" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+        <v>545</v>
+      </c>
+      <c r="H41" s="20">
+        <v>4</v>
+      </c>
+      <c r="I41" t="s">
+        <v>570</v>
+      </c>
+      <c r="J41" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>233</v>
       </c>
@@ -3242,10 +3771,19 @@
         <v>236</v>
       </c>
       <c r="E42" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+        <v>545</v>
+      </c>
+      <c r="H42" s="20">
+        <v>4</v>
+      </c>
+      <c r="I42" t="s">
+        <v>570</v>
+      </c>
+      <c r="J42" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>233</v>
       </c>
@@ -3259,10 +3797,19 @@
         <v>236</v>
       </c>
       <c r="E43" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+        <v>545</v>
+      </c>
+      <c r="H43" s="20">
+        <v>4</v>
+      </c>
+      <c r="I43" t="s">
+        <v>570</v>
+      </c>
+      <c r="J43" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>233</v>
       </c>
@@ -3276,10 +3823,19 @@
         <v>236</v>
       </c>
       <c r="E44" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+        <v>545</v>
+      </c>
+      <c r="H44" s="20">
+        <v>4</v>
+      </c>
+      <c r="I44" t="s">
+        <v>570</v>
+      </c>
+      <c r="J44" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>233</v>
       </c>
@@ -3293,10 +3849,19 @@
         <v>236</v>
       </c>
       <c r="E45" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+        <v>545</v>
+      </c>
+      <c r="H45" s="20">
+        <v>4</v>
+      </c>
+      <c r="I45" t="s">
+        <v>570</v>
+      </c>
+      <c r="J45" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>233</v>
       </c>
@@ -3310,10 +3875,19 @@
         <v>238</v>
       </c>
       <c r="E46" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+        <v>525</v>
+      </c>
+      <c r="H46" s="20">
+        <v>8</v>
+      </c>
+      <c r="I46" t="s">
+        <v>581</v>
+      </c>
+      <c r="J46" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>233</v>
       </c>
@@ -3327,10 +3901,19 @@
         <v>238</v>
       </c>
       <c r="E47" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+        <v>525</v>
+      </c>
+      <c r="H47" s="20">
+        <v>8</v>
+      </c>
+      <c r="I47" t="s">
+        <v>581</v>
+      </c>
+      <c r="J47" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>233</v>
       </c>
@@ -3344,10 +3927,19 @@
         <v>238</v>
       </c>
       <c r="E48" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+        <v>546</v>
+      </c>
+      <c r="H48" s="20">
+        <v>8</v>
+      </c>
+      <c r="I48" t="s">
+        <v>581</v>
+      </c>
+      <c r="J48" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>233</v>
       </c>
@@ -3361,10 +3953,19 @@
         <v>238</v>
       </c>
       <c r="E49" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
+        <v>546</v>
+      </c>
+      <c r="H49" s="20">
+        <v>8</v>
+      </c>
+      <c r="I49" t="s">
+        <v>581</v>
+      </c>
+      <c r="J49" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>233</v>
       </c>
@@ -3378,10 +3979,19 @@
         <v>238</v>
       </c>
       <c r="E50" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
+        <v>546</v>
+      </c>
+      <c r="H50" s="20">
+        <v>8</v>
+      </c>
+      <c r="I50" t="s">
+        <v>581</v>
+      </c>
+      <c r="J50" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>233</v>
       </c>
@@ -3395,15 +4005,25 @@
         <v>238</v>
       </c>
       <c r="E51" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
+        <v>546</v>
+      </c>
+      <c r="H51" s="20">
+        <v>8</v>
+      </c>
+      <c r="I51" t="s">
+        <v>581</v>
+      </c>
+      <c r="J51" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="H52" s="20"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>46</v>
       </c>
@@ -3419,8 +4039,9 @@
       <c r="E53" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="H53" s="20"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>233</v>
       </c>
@@ -3434,10 +4055,19 @@
         <v>240</v>
       </c>
       <c r="E54" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
+        <v>526</v>
+      </c>
+      <c r="H54" s="20">
+        <v>1</v>
+      </c>
+      <c r="I54" t="s">
+        <v>564</v>
+      </c>
+      <c r="J54" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>233</v>
       </c>
@@ -3451,10 +4081,19 @@
         <v>240</v>
       </c>
       <c r="E55" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
+        <v>526</v>
+      </c>
+      <c r="H55" s="20">
+        <v>1</v>
+      </c>
+      <c r="I55" t="s">
+        <v>564</v>
+      </c>
+      <c r="J55" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>233</v>
       </c>
@@ -3468,10 +4107,19 @@
         <v>240</v>
       </c>
       <c r="E56" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
+        <v>547</v>
+      </c>
+      <c r="H56" s="20">
+        <v>1</v>
+      </c>
+      <c r="I56" t="s">
+        <v>564</v>
+      </c>
+      <c r="J56" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>233</v>
       </c>
@@ -3485,10 +4133,19 @@
         <v>240</v>
       </c>
       <c r="E57" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
+        <v>547</v>
+      </c>
+      <c r="H57" s="20">
+        <v>1</v>
+      </c>
+      <c r="I57" t="s">
+        <v>564</v>
+      </c>
+      <c r="J57" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>233</v>
       </c>
@@ -3502,10 +4159,19 @@
         <v>240</v>
       </c>
       <c r="E58" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
+        <v>547</v>
+      </c>
+      <c r="H58" s="20">
+        <v>1</v>
+      </c>
+      <c r="I58" t="s">
+        <v>564</v>
+      </c>
+      <c r="J58" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>233</v>
       </c>
@@ -3519,10 +4185,19 @@
         <v>240</v>
       </c>
       <c r="E59" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+        <v>547</v>
+      </c>
+      <c r="H59" s="20">
+        <v>1</v>
+      </c>
+      <c r="I59" t="s">
+        <v>564</v>
+      </c>
+      <c r="J59" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>233</v>
       </c>
@@ -3536,10 +4211,19 @@
         <v>240</v>
       </c>
       <c r="E60" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
+        <v>547</v>
+      </c>
+      <c r="H60" s="20">
+        <v>1</v>
+      </c>
+      <c r="I60" t="s">
+        <v>564</v>
+      </c>
+      <c r="J60" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>233</v>
       </c>
@@ -3553,10 +4237,19 @@
         <v>240</v>
       </c>
       <c r="E61" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
+        <v>547</v>
+      </c>
+      <c r="H61" s="20">
+        <v>1</v>
+      </c>
+      <c r="I61" t="s">
+        <v>564</v>
+      </c>
+      <c r="J61" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>233</v>
       </c>
@@ -3570,10 +4263,19 @@
         <v>240</v>
       </c>
       <c r="E62" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
+        <v>547</v>
+      </c>
+      <c r="H62" s="20">
+        <v>1</v>
+      </c>
+      <c r="I62" t="s">
+        <v>564</v>
+      </c>
+      <c r="J62" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>233</v>
       </c>
@@ -3587,10 +4289,19 @@
         <v>240</v>
       </c>
       <c r="E63" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
+        <v>547</v>
+      </c>
+      <c r="H63" s="20">
+        <v>1</v>
+      </c>
+      <c r="I63" t="s">
+        <v>564</v>
+      </c>
+      <c r="J63" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>233</v>
       </c>
@@ -3604,10 +4315,19 @@
         <v>240</v>
       </c>
       <c r="E64" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
+        <v>547</v>
+      </c>
+      <c r="H64" s="20">
+        <v>1</v>
+      </c>
+      <c r="I64" t="s">
+        <v>564</v>
+      </c>
+      <c r="J64" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>233</v>
       </c>
@@ -3621,10 +4341,19 @@
         <v>240</v>
       </c>
       <c r="E65" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
+        <v>547</v>
+      </c>
+      <c r="H65" s="20">
+        <v>1</v>
+      </c>
+      <c r="I65" t="s">
+        <v>564</v>
+      </c>
+      <c r="J65" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>233</v>
       </c>
@@ -3638,10 +4367,19 @@
         <v>240</v>
       </c>
       <c r="E66" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
+        <v>547</v>
+      </c>
+      <c r="H66" s="20">
+        <v>1</v>
+      </c>
+      <c r="I66" t="s">
+        <v>564</v>
+      </c>
+      <c r="J66" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>233</v>
       </c>
@@ -3655,10 +4393,19 @@
         <v>240</v>
       </c>
       <c r="E67" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.45">
+        <v>547</v>
+      </c>
+      <c r="H67" s="20">
+        <v>1</v>
+      </c>
+      <c r="I67" t="s">
+        <v>564</v>
+      </c>
+      <c r="J67" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>233</v>
       </c>
@@ -3672,10 +4419,19 @@
         <v>243</v>
       </c>
       <c r="E68" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
+        <v>527</v>
+      </c>
+      <c r="H68" s="20">
+        <v>20</v>
+      </c>
+      <c r="I68" t="s">
+        <v>598</v>
+      </c>
+      <c r="J68" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>233</v>
       </c>
@@ -3689,10 +4445,19 @@
         <v>243</v>
       </c>
       <c r="E69" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.45">
+        <v>527</v>
+      </c>
+      <c r="H69" s="20">
+        <v>20</v>
+      </c>
+      <c r="I69" t="s">
+        <v>598</v>
+      </c>
+      <c r="J69" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>233</v>
       </c>
@@ -3706,15 +4471,24 @@
         <v>243</v>
       </c>
       <c r="E70" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
+        <v>548</v>
+      </c>
+      <c r="H70" s="20">
+        <v>20</v>
+      </c>
+      <c r="I70" t="s">
+        <v>597</v>
+      </c>
+      <c r="J70" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>233</v>
       </c>
       <c r="B71" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C71" t="s">
         <v>242</v>
@@ -3723,10 +4497,19 @@
         <v>243</v>
       </c>
       <c r="E71" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
+        <v>548</v>
+      </c>
+      <c r="H71" s="20">
+        <v>20</v>
+      </c>
+      <c r="I71" t="s">
+        <v>597</v>
+      </c>
+      <c r="J71" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>233</v>
       </c>
@@ -3740,10 +4523,19 @@
         <v>243</v>
       </c>
       <c r="E72" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
+        <v>548</v>
+      </c>
+      <c r="H72" s="20">
+        <v>20</v>
+      </c>
+      <c r="I72" t="s">
+        <v>597</v>
+      </c>
+      <c r="J72" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>233</v>
       </c>
@@ -3757,10 +4549,19 @@
         <v>243</v>
       </c>
       <c r="E73" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
+        <v>548</v>
+      </c>
+      <c r="H73" s="20">
+        <v>20</v>
+      </c>
+      <c r="I73" t="s">
+        <v>597</v>
+      </c>
+      <c r="J73" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>233</v>
       </c>
@@ -3774,10 +4575,19 @@
         <v>243</v>
       </c>
       <c r="E74" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.45">
+        <v>548</v>
+      </c>
+      <c r="H74" s="20">
+        <v>20</v>
+      </c>
+      <c r="I74" t="s">
+        <v>597</v>
+      </c>
+      <c r="J74" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>233</v>
       </c>
@@ -3791,10 +4601,19 @@
         <v>243</v>
       </c>
       <c r="E75" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
+        <v>548</v>
+      </c>
+      <c r="H75" s="20">
+        <v>20</v>
+      </c>
+      <c r="I75" t="s">
+        <v>597</v>
+      </c>
+      <c r="J75" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>233</v>
       </c>
@@ -3808,10 +4627,19 @@
         <v>243</v>
       </c>
       <c r="E76" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
+        <v>548</v>
+      </c>
+      <c r="H76" s="20">
+        <v>20</v>
+      </c>
+      <c r="I76" t="s">
+        <v>597</v>
+      </c>
+      <c r="J76" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>233</v>
       </c>
@@ -3825,15 +4653,25 @@
         <v>243</v>
       </c>
       <c r="E77" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
+        <v>548</v>
+      </c>
+      <c r="H77" s="20">
+        <v>20</v>
+      </c>
+      <c r="I77" t="s">
+        <v>597</v>
+      </c>
+      <c r="J77" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C78" s="9"/>
       <c r="D78" s="9"/>
       <c r="E78" s="9"/>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="H78" s="20"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>46</v>
       </c>
@@ -3849,8 +4687,9 @@
       <c r="E79" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="H79" s="20"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>234</v>
       </c>
@@ -3866,8 +4705,17 @@
       <c r="E80" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="H80" s="20">
+        <v>19</v>
+      </c>
+      <c r="I80" t="s">
+        <v>594</v>
+      </c>
+      <c r="J80" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>234</v>
       </c>
@@ -3883,8 +4731,17 @@
       <c r="E81" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="H81" s="20">
+        <v>19</v>
+      </c>
+      <c r="I81" t="s">
+        <v>594</v>
+      </c>
+      <c r="J81" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>234</v>
       </c>
@@ -3898,10 +4755,19 @@
         <v>245</v>
       </c>
       <c r="E82" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.45">
+        <v>549</v>
+      </c>
+      <c r="H82" s="20">
+        <v>19</v>
+      </c>
+      <c r="I82" t="s">
+        <v>594</v>
+      </c>
+      <c r="J82" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>234</v>
       </c>
@@ -3915,10 +4781,19 @@
         <v>245</v>
       </c>
       <c r="E83" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.45">
+        <v>549</v>
+      </c>
+      <c r="H83" s="20">
+        <v>19</v>
+      </c>
+      <c r="I83" t="s">
+        <v>594</v>
+      </c>
+      <c r="J83" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>234</v>
       </c>
@@ -3932,10 +4807,19 @@
         <v>245</v>
       </c>
       <c r="E84" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.45">
+        <v>549</v>
+      </c>
+      <c r="H84" s="20">
+        <v>19</v>
+      </c>
+      <c r="I84" t="s">
+        <v>594</v>
+      </c>
+      <c r="J84" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>234</v>
       </c>
@@ -3949,10 +4833,19 @@
         <v>245</v>
       </c>
       <c r="E85" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.45">
+        <v>549</v>
+      </c>
+      <c r="H85" s="20">
+        <v>19</v>
+      </c>
+      <c r="I85" t="s">
+        <v>594</v>
+      </c>
+      <c r="J85" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>234</v>
       </c>
@@ -3966,10 +4859,19 @@
         <v>245</v>
       </c>
       <c r="E86" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.45">
+        <v>549</v>
+      </c>
+      <c r="H86" s="20">
+        <v>19</v>
+      </c>
+      <c r="I86" t="s">
+        <v>594</v>
+      </c>
+      <c r="J86" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>234</v>
       </c>
@@ -3983,10 +4885,19 @@
         <v>245</v>
       </c>
       <c r="E87" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.45">
+        <v>549</v>
+      </c>
+      <c r="H87" s="20">
+        <v>19</v>
+      </c>
+      <c r="I87" t="s">
+        <v>594</v>
+      </c>
+      <c r="J87" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>234</v>
       </c>
@@ -4000,10 +4911,19 @@
         <v>245</v>
       </c>
       <c r="E88" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.45">
+        <v>549</v>
+      </c>
+      <c r="H88" s="20">
+        <v>19</v>
+      </c>
+      <c r="I88" t="s">
+        <v>594</v>
+      </c>
+      <c r="J88" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>234</v>
       </c>
@@ -4017,10 +4937,19 @@
         <v>255</v>
       </c>
       <c r="E89" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.45">
+        <v>528</v>
+      </c>
+      <c r="H89" s="20">
+        <v>4</v>
+      </c>
+      <c r="I89" t="s">
+        <v>570</v>
+      </c>
+      <c r="J89" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>234</v>
       </c>
@@ -4034,10 +4963,19 @@
         <v>255</v>
       </c>
       <c r="E90" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.45">
+        <v>528</v>
+      </c>
+      <c r="H90" s="20">
+        <v>4</v>
+      </c>
+      <c r="I90" t="s">
+        <v>570</v>
+      </c>
+      <c r="J90" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>234</v>
       </c>
@@ -4051,10 +4989,19 @@
         <v>255</v>
       </c>
       <c r="E91" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.45">
+        <v>550</v>
+      </c>
+      <c r="H91" s="20">
+        <v>4</v>
+      </c>
+      <c r="I91" t="s">
+        <v>570</v>
+      </c>
+      <c r="J91" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>234</v>
       </c>
@@ -4068,10 +5015,19 @@
         <v>255</v>
       </c>
       <c r="E92" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.45">
+        <v>550</v>
+      </c>
+      <c r="H92" s="20">
+        <v>4</v>
+      </c>
+      <c r="I92" t="s">
+        <v>570</v>
+      </c>
+      <c r="J92" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>234</v>
       </c>
@@ -4085,10 +5041,19 @@
         <v>255</v>
       </c>
       <c r="E93" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.45">
+        <v>550</v>
+      </c>
+      <c r="H93" s="20">
+        <v>4</v>
+      </c>
+      <c r="I93" t="s">
+        <v>570</v>
+      </c>
+      <c r="J93" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>234</v>
       </c>
@@ -4102,10 +5067,19 @@
         <v>255</v>
       </c>
       <c r="E94" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.45">
+        <v>550</v>
+      </c>
+      <c r="H94" s="20">
+        <v>4</v>
+      </c>
+      <c r="I94" t="s">
+        <v>570</v>
+      </c>
+      <c r="J94" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>234</v>
       </c>
@@ -4119,10 +5093,19 @@
         <v>255</v>
       </c>
       <c r="E95" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.45">
+        <v>550</v>
+      </c>
+      <c r="H95" s="20">
+        <v>4</v>
+      </c>
+      <c r="I95" t="s">
+        <v>570</v>
+      </c>
+      <c r="J95" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>234</v>
       </c>
@@ -4136,10 +5119,19 @@
         <v>255</v>
       </c>
       <c r="E96" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.45">
+        <v>550</v>
+      </c>
+      <c r="H96" s="20">
+        <v>4</v>
+      </c>
+      <c r="I96" t="s">
+        <v>570</v>
+      </c>
+      <c r="J96" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>234</v>
       </c>
@@ -4153,10 +5145,19 @@
         <v>255</v>
       </c>
       <c r="E97" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.45">
+        <v>550</v>
+      </c>
+      <c r="H97" s="20">
+        <v>4</v>
+      </c>
+      <c r="I97" t="s">
+        <v>570</v>
+      </c>
+      <c r="J97" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>234</v>
       </c>
@@ -4170,15 +5171,25 @@
         <v>255</v>
       </c>
       <c r="E98" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.45">
+        <v>550</v>
+      </c>
+      <c r="H98" s="20">
+        <v>4</v>
+      </c>
+      <c r="I98" t="s">
+        <v>570</v>
+      </c>
+      <c r="J98" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C99" s="9"/>
       <c r="D99" s="9"/>
       <c r="E99" s="9"/>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="H99" s="20"/>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>46</v>
       </c>
@@ -4194,8 +5205,9 @@
       <c r="E100" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="H100" s="20"/>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>234</v>
       </c>
@@ -4211,8 +5223,17 @@
       <c r="E101" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="H101" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="I101" t="s">
+        <v>599</v>
+      </c>
+      <c r="J101" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>234</v>
       </c>
@@ -4228,8 +5249,17 @@
       <c r="E102" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="H102" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="I102" t="s">
+        <v>599</v>
+      </c>
+      <c r="J102" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>234</v>
       </c>
@@ -4243,10 +5273,19 @@
         <v>256</v>
       </c>
       <c r="E103" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.45">
+        <v>551</v>
+      </c>
+      <c r="H103" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="I103" t="s">
+        <v>599</v>
+      </c>
+      <c r="J103" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>234</v>
       </c>
@@ -4260,10 +5299,19 @@
         <v>256</v>
       </c>
       <c r="E104" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.45">
+        <v>551</v>
+      </c>
+      <c r="H104" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="I104" t="s">
+        <v>599</v>
+      </c>
+      <c r="J104" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>234</v>
       </c>
@@ -4277,10 +5325,19 @@
         <v>256</v>
       </c>
       <c r="E105" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.45">
+        <v>551</v>
+      </c>
+      <c r="H105" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="I105" t="s">
+        <v>599</v>
+      </c>
+      <c r="J105" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>234</v>
       </c>
@@ -4294,10 +5351,19 @@
         <v>256</v>
       </c>
       <c r="E106" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.45">
+        <v>551</v>
+      </c>
+      <c r="H106" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="I106" t="s">
+        <v>599</v>
+      </c>
+      <c r="J106" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>234</v>
       </c>
@@ -4311,10 +5377,19 @@
         <v>256</v>
       </c>
       <c r="E107" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.45">
+        <v>551</v>
+      </c>
+      <c r="H107" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="I107" t="s">
+        <v>599</v>
+      </c>
+      <c r="J107" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>234</v>
       </c>
@@ -4328,10 +5403,19 @@
         <v>256</v>
       </c>
       <c r="E108" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.45">
+        <v>551</v>
+      </c>
+      <c r="H108" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="I108" t="s">
+        <v>599</v>
+      </c>
+      <c r="J108" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>234</v>
       </c>
@@ -4345,10 +5429,19 @@
         <v>256</v>
       </c>
       <c r="E109" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.45">
+        <v>551</v>
+      </c>
+      <c r="H109" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="I109" t="s">
+        <v>599</v>
+      </c>
+      <c r="J109" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>234</v>
       </c>
@@ -4362,15 +5455,24 @@
         <v>256</v>
       </c>
       <c r="E110" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.45">
+        <v>551</v>
+      </c>
+      <c r="H110" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="I110" t="s">
+        <v>599</v>
+      </c>
+      <c r="J110" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>234</v>
       </c>
       <c r="B111" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C111" t="s">
         <v>257</v>
@@ -4379,10 +5481,19 @@
         <v>256</v>
       </c>
       <c r="E111" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.45">
+        <v>551</v>
+      </c>
+      <c r="H111" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="I111" t="s">
+        <v>599</v>
+      </c>
+      <c r="J111" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>234</v>
       </c>
@@ -4396,10 +5507,19 @@
         <v>256</v>
       </c>
       <c r="E112" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.45">
+        <v>551</v>
+      </c>
+      <c r="H112" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="I112" t="s">
+        <v>599</v>
+      </c>
+      <c r="J112" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>234</v>
       </c>
@@ -4415,8 +5535,17 @@
       <c r="E113" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="H113" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="I113" t="s">
+        <v>590</v>
+      </c>
+      <c r="J113" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>234</v>
       </c>
@@ -4432,8 +5561,17 @@
       <c r="E114" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="H114" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="I114" t="s">
+        <v>590</v>
+      </c>
+      <c r="J114" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>234</v>
       </c>
@@ -4447,10 +5585,19 @@
         <v>249</v>
       </c>
       <c r="E115" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.45">
+        <v>552</v>
+      </c>
+      <c r="H115" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="I115" t="s">
+        <v>590</v>
+      </c>
+      <c r="J115" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>234</v>
       </c>
@@ -4464,10 +5611,19 @@
         <v>249</v>
       </c>
       <c r="E116" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.45">
+        <v>552</v>
+      </c>
+      <c r="H116" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="I116" t="s">
+        <v>590</v>
+      </c>
+      <c r="J116" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>234</v>
       </c>
@@ -4481,10 +5637,19 @@
         <v>249</v>
       </c>
       <c r="E117" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.45">
+        <v>552</v>
+      </c>
+      <c r="H117" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="I117" t="s">
+        <v>590</v>
+      </c>
+      <c r="J117" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>234</v>
       </c>
@@ -4498,10 +5663,19 @@
         <v>249</v>
       </c>
       <c r="E118" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.45">
+        <v>552</v>
+      </c>
+      <c r="H118" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="I118" t="s">
+        <v>590</v>
+      </c>
+      <c r="J118" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>234</v>
       </c>
@@ -4515,10 +5689,19 @@
         <v>249</v>
       </c>
       <c r="E119" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.45">
+        <v>552</v>
+      </c>
+      <c r="H119" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="I119" t="s">
+        <v>590</v>
+      </c>
+      <c r="J119" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>234</v>
       </c>
@@ -4532,10 +5715,19 @@
         <v>249</v>
       </c>
       <c r="E120" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.45">
+        <v>552</v>
+      </c>
+      <c r="H120" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="I120" t="s">
+        <v>590</v>
+      </c>
+      <c r="J120" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>234</v>
       </c>
@@ -4549,10 +5741,19 @@
         <v>249</v>
       </c>
       <c r="E121" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.45">
+        <v>552</v>
+      </c>
+      <c r="H121" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="I121" t="s">
+        <v>590</v>
+      </c>
+      <c r="J121" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>234</v>
       </c>
@@ -4566,10 +5767,19 @@
         <v>249</v>
       </c>
       <c r="E122" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.45">
+        <v>552</v>
+      </c>
+      <c r="H122" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="I122" t="s">
+        <v>590</v>
+      </c>
+      <c r="J122" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>234</v>
       </c>
@@ -4583,10 +5793,19 @@
         <v>249</v>
       </c>
       <c r="E123" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.45">
+        <v>552</v>
+      </c>
+      <c r="H123" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="I123" t="s">
+        <v>590</v>
+      </c>
+      <c r="J123" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>234</v>
       </c>
@@ -4600,15 +5819,24 @@
         <v>249</v>
       </c>
       <c r="E124" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.45">
+        <v>552</v>
+      </c>
+      <c r="H124" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="I124" t="s">
+        <v>590</v>
+      </c>
+      <c r="J124" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C125" s="9"/>
       <c r="D125" s="9"/>
       <c r="E125" s="9"/>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>46</v>
       </c>
@@ -4625,7 +5853,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>234</v>
       </c>
@@ -4642,7 +5870,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>234</v>
       </c>
@@ -4659,7 +5887,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>234</v>
       </c>
@@ -4673,10 +5901,10 @@
         <v>259</v>
       </c>
       <c r="E129" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.45">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>234</v>
       </c>
@@ -4690,10 +5918,10 @@
         <v>259</v>
       </c>
       <c r="E130" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.45">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>234</v>
       </c>
@@ -4707,10 +5935,10 @@
         <v>259</v>
       </c>
       <c r="E131" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.45">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>234</v>
       </c>
@@ -4724,10 +5952,10 @@
         <v>259</v>
       </c>
       <c r="E132" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.45">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>234</v>
       </c>
@@ -4741,10 +5969,10 @@
         <v>259</v>
       </c>
       <c r="E133" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.45">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>234</v>
       </c>
@@ -4758,10 +5986,10 @@
         <v>259</v>
       </c>
       <c r="E134" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.45">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>234</v>
       </c>
@@ -4775,10 +6003,10 @@
         <v>259</v>
       </c>
       <c r="E135" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.45">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>234</v>
       </c>
@@ -4792,10 +6020,10 @@
         <v>259</v>
       </c>
       <c r="E136" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.45">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>234</v>
       </c>
@@ -4809,10 +6037,10 @@
         <v>259</v>
       </c>
       <c r="E137" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.45">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>234</v>
       </c>
@@ -4826,10 +6054,10 @@
         <v>259</v>
       </c>
       <c r="E138" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.45">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>46</v>
       </c>
@@ -4846,21 +6074,30 @@
         <v>12</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
+        <v>538</v>
+      </c>
+      <c r="B141" t="s">
+        <v>536</v>
+      </c>
+      <c r="C141" t="s">
         <v>539</v>
       </c>
-      <c r="B141" t="s">
-        <v>537</v>
-      </c>
-      <c r="C141" t="s">
+      <c r="D141" t="s">
         <v>540</v>
       </c>
-      <c r="D141" t="s">
-        <v>541</v>
-      </c>
       <c r="E141" t="s">
-        <v>543</v>
+        <v>542</v>
+      </c>
+      <c r="H141">
+        <v>3</v>
+      </c>
+      <c r="I141" t="s">
+        <v>569</v>
+      </c>
+      <c r="J141" t="s">
+        <v>573</v>
       </c>
     </row>
   </sheetData>
@@ -4881,33 +6118,33 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B1" t="s">
         <v>318</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>319</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>320</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
+        <v>502</v>
+      </c>
+      <c r="F1" t="s">
+        <v>505</v>
+      </c>
+      <c r="G1" t="s">
         <v>321</v>
       </c>
-      <c r="E1" t="s">
-        <v>503</v>
-      </c>
-      <c r="F1" t="s">
-        <v>506</v>
-      </c>
-      <c r="G1" t="s">
-        <v>322</v>
-      </c>
       <c r="H1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B2">
         <v>40</v>
@@ -4927,10 +6164,10 @@
         <v>96</v>
       </c>
       <c r="G2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
@@ -4955,15 +6192,15 @@
         <v>74</v>
       </c>
       <c r="G3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H3" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B4">
         <v>91</v>
@@ -4983,10 +6220,10 @@
         <v>91</v>
       </c>
       <c r="G4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H4" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
@@ -5011,15 +6248,15 @@
         <v>78</v>
       </c>
       <c r="G5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H5" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B6">
         <v>90</v>
@@ -5039,15 +6276,15 @@
         <v>94</v>
       </c>
       <c r="G6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B7">
         <v>44</v>
@@ -5067,10 +6304,10 @@
         <v>53</v>
       </c>
       <c r="G7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H7" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
@@ -5095,15 +6332,15 @@
         <v>75</v>
       </c>
       <c r="G8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H8" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B9">
         <v>56</v>
@@ -5123,15 +6360,15 @@
         <v>63</v>
       </c>
       <c r="G9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H9" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B10">
         <v>18</v>
@@ -5151,15 +6388,15 @@
         <v>72</v>
       </c>
       <c r="G10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H10" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B11">
         <v>72</v>
@@ -5179,15 +6416,15 @@
         <v>72</v>
       </c>
       <c r="G11" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H11" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B12">
         <v>59</v>
@@ -5207,15 +6444,15 @@
         <v>59</v>
       </c>
       <c r="G12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H12" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B13">
         <v>60</v>
@@ -5235,15 +6472,15 @@
         <v>60</v>
       </c>
       <c r="G13" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H13" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B14">
         <v>71</v>
@@ -5263,10 +6500,10 @@
         <v>71</v>
       </c>
       <c r="G14" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H14" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.45">
@@ -5291,15 +6528,15 @@
         <v>83</v>
       </c>
       <c r="G15" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H15" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B16">
         <v>44</v>
@@ -5319,15 +6556,15 @@
         <v>63</v>
       </c>
       <c r="G16" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H16" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B17">
         <v>36</v>
@@ -5347,10 +6584,10 @@
         <v>97</v>
       </c>
       <c r="G17" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H17" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.45">
@@ -5375,15 +6612,15 @@
         <v>76</v>
       </c>
       <c r="G18" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H18" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B19">
         <v>61</v>
@@ -5403,15 +6640,15 @@
         <v>61</v>
       </c>
       <c r="G19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H19" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B20">
         <v>35</v>
@@ -5431,15 +6668,15 @@
         <v>63</v>
       </c>
       <c r="G20" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H20" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B21">
         <v>67</v>
@@ -5459,15 +6696,15 @@
         <v>67</v>
       </c>
       <c r="G21" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H21" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B22">
         <v>42</v>
@@ -5487,10 +6724,10 @@
         <v>61</v>
       </c>
       <c r="G22" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H22" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.45">
@@ -5515,10 +6752,10 @@
         <v>100</v>
       </c>
       <c r="G23" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.45">
@@ -5543,15 +6780,15 @@
         <v>80</v>
       </c>
       <c r="G24" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H24" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B25">
         <v>68</v>
@@ -5571,10 +6808,10 @@
         <v>68</v>
       </c>
       <c r="G25" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H25" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.45">
@@ -5599,10 +6836,10 @@
         <v>88</v>
       </c>
       <c r="G26" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H26" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.45">
@@ -5627,15 +6864,15 @@
         <v>74</v>
       </c>
       <c r="G27" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H27" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B28">
         <v>73</v>
@@ -5655,15 +6892,15 @@
         <v>73</v>
       </c>
       <c r="G28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H28" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B29">
         <v>52</v>
@@ -5683,15 +6920,15 @@
         <v>52</v>
       </c>
       <c r="G29" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H29" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B30">
         <v>70</v>
@@ -5711,15 +6948,15 @@
         <v>70</v>
       </c>
       <c r="G30" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H30" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B31">
         <v>66</v>
@@ -5739,15 +6976,15 @@
         <v>66</v>
       </c>
       <c r="G31" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H31" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B32">
         <v>65</v>
@@ -5767,15 +7004,15 @@
         <v>65</v>
       </c>
       <c r="G32" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H32" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B33">
         <v>61</v>
@@ -5795,10 +7032,10 @@
         <v>95</v>
       </c>
       <c r="G33" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H33" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.45">
@@ -5823,10 +7060,10 @@
         <v>86</v>
       </c>
       <c r="G34" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H34" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.45">
@@ -5851,15 +7088,15 @@
         <v>81</v>
       </c>
       <c r="G35" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H35" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B36">
         <v>53</v>
@@ -5879,15 +7116,15 @@
         <v>61</v>
       </c>
       <c r="G36" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H36" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B37">
         <v>69</v>
@@ -5907,15 +7144,15 @@
         <v>69</v>
       </c>
       <c r="G37" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H37" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B38">
         <v>52</v>
@@ -5935,10 +7172,10 @@
         <v>62</v>
       </c>
       <c r="G38" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H38" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.45">
@@ -5963,15 +7200,15 @@
         <v>89</v>
       </c>
       <c r="G39" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H39" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B40">
         <v>57</v>
@@ -5991,10 +7228,10 @@
         <v>57</v>
       </c>
       <c r="G40" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H40" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.45">
@@ -6019,10 +7256,10 @@
         <v>69</v>
       </c>
       <c r="G41" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H41" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.45">
@@ -6047,10 +7284,10 @@
         <v>84</v>
       </c>
       <c r="G42" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H42" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.45">
@@ -6075,10 +7312,10 @@
         <v>94</v>
       </c>
       <c r="G43" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H43" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.45">
@@ -6103,7 +7340,7 @@
         <v>90</v>
       </c>
       <c r="G44" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H44" t="s">
         <v>233</v>
@@ -6131,15 +7368,15 @@
         <v>84</v>
       </c>
       <c r="G45" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H45" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B46">
         <v>65</v>
@@ -6159,15 +7396,15 @@
         <v>65</v>
       </c>
       <c r="G46" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H46" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B47">
         <v>97</v>
@@ -6187,15 +7424,15 @@
         <v>97</v>
       </c>
       <c r="G47" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H47" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B48">
         <v>58</v>
@@ -6215,15 +7452,15 @@
         <v>58</v>
       </c>
       <c r="G48" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H48" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B49">
         <v>27</v>
@@ -6243,10 +7480,10 @@
         <v>68</v>
       </c>
       <c r="G49" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H49" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.45">
@@ -6271,15 +7508,15 @@
         <v>73</v>
       </c>
       <c r="G50" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H50" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B51">
         <v>69</v>
@@ -6299,15 +7536,15 @@
         <v>69</v>
       </c>
       <c r="G51" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H51" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B52">
         <v>57</v>
@@ -6327,10 +7564,10 @@
         <v>57</v>
       </c>
       <c r="G52" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H52" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.45">
@@ -6355,10 +7592,10 @@
         <v>84</v>
       </c>
       <c r="G53" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H53" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.45">
@@ -6383,15 +7620,15 @@
         <v>91</v>
       </c>
       <c r="G54" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H54" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B55">
         <v>63</v>
@@ -6411,15 +7648,15 @@
         <v>63</v>
       </c>
       <c r="G55" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H55" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B56">
         <v>40</v>
@@ -6439,10 +7676,10 @@
         <v>64</v>
       </c>
       <c r="G56" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H56" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.45">
@@ -6467,15 +7704,15 @@
         <v>75</v>
       </c>
       <c r="G57" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H57" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B58">
         <v>94</v>
@@ -6495,15 +7732,15 @@
         <v>94</v>
       </c>
       <c r="G58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H58" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B59">
         <v>51</v>
@@ -6523,15 +7760,15 @@
         <v>98</v>
       </c>
       <c r="G59" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H59" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B60">
         <v>62</v>
@@ -6551,10 +7788,10 @@
         <v>71</v>
       </c>
       <c r="G60" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H60" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.45">
@@ -6579,15 +7816,15 @@
         <v>87</v>
       </c>
       <c r="G61" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H61" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B62">
         <v>25</v>
@@ -6607,10 +7844,10 @@
         <v>65</v>
       </c>
       <c r="G62" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H62" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.45">
@@ -6635,15 +7872,15 @@
         <v>82</v>
       </c>
       <c r="G63" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H63" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B64">
         <v>49</v>
@@ -6663,10 +7900,10 @@
         <v>58</v>
       </c>
       <c r="G64" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H64" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.45">
@@ -6691,10 +7928,10 @@
         <v>80</v>
       </c>
       <c r="G65" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H65" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.45">
@@ -6719,10 +7956,10 @@
         <v>91</v>
       </c>
       <c r="G66" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H66" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.45">
@@ -6747,10 +7984,10 @@
         <v>87</v>
       </c>
       <c r="G67" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H67" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.45">
@@ -6775,15 +8012,15 @@
         <v>85</v>
       </c>
       <c r="G68" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H68" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B69">
         <v>48</v>
@@ -6803,10 +8040,10 @@
         <v>99</v>
       </c>
       <c r="G69" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H69" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.45">
@@ -6831,10 +8068,10 @@
         <v>74</v>
       </c>
       <c r="G70" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H70" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.45">
@@ -6859,15 +8096,15 @@
         <v>82</v>
       </c>
       <c r="G71" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H71" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B72">
         <v>44</v>
@@ -6887,10 +8124,10 @@
         <v>97</v>
       </c>
       <c r="G72" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H72" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.45">
@@ -6915,15 +8152,15 @@
         <v>72</v>
       </c>
       <c r="G73" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H73" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B74">
         <v>54</v>
@@ -6943,15 +8180,15 @@
         <v>54</v>
       </c>
       <c r="G74" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H74" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B75">
         <v>91</v>
@@ -6971,15 +8208,15 @@
         <v>91</v>
       </c>
       <c r="G75" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H75" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B76">
         <v>35</v>
@@ -6999,10 +8236,10 @@
         <v>62</v>
       </c>
       <c r="G76" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H76" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.45">
@@ -7027,15 +8264,15 @@
         <v>74</v>
       </c>
       <c r="G77" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H77" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B78">
         <v>90</v>
@@ -7055,15 +8292,15 @@
         <v>90</v>
       </c>
       <c r="G78" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H78" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B79">
         <v>67</v>
@@ -7083,15 +8320,15 @@
         <v>67</v>
       </c>
       <c r="G79" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H79" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B80">
         <v>86</v>
@@ -7111,15 +8348,15 @@
         <v>87</v>
       </c>
       <c r="G80" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H80" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B81">
         <v>64</v>
@@ -7139,10 +8376,10 @@
         <v>64</v>
       </c>
       <c r="G81" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H81" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.45">
@@ -7167,15 +8404,15 @@
         <v>72</v>
       </c>
       <c r="G82" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H82" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B83">
         <v>59</v>
@@ -7195,15 +8432,15 @@
         <v>59</v>
       </c>
       <c r="G83" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H83" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B84">
         <v>64</v>
@@ -7223,15 +8460,15 @@
         <v>64</v>
       </c>
       <c r="G84" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H84" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B85">
         <v>33</v>
@@ -7251,15 +8488,15 @@
         <v>41</v>
       </c>
       <c r="G85" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H85" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B86">
         <v>45</v>
@@ -7279,10 +8516,10 @@
         <v>70</v>
       </c>
       <c r="G86" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H86" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.45">
@@ -7307,15 +8544,15 @@
         <v>73</v>
       </c>
       <c r="G87" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H87" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B88">
         <v>37</v>
@@ -7335,10 +8572,10 @@
         <v>96</v>
       </c>
       <c r="G88" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H88" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.45">
@@ -7363,15 +8600,15 @@
         <v>94</v>
       </c>
       <c r="G89" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H89" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B90">
         <v>59</v>
@@ -7391,10 +8628,10 @@
         <v>59</v>
       </c>
       <c r="G90" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H90" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.45">
@@ -7419,10 +8656,10 @@
         <v>73</v>
       </c>
       <c r="G91" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H91" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.45">
@@ -7447,15 +8684,15 @@
         <v>74</v>
       </c>
       <c r="G92" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H92" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B93">
         <v>70</v>
@@ -7475,10 +8712,10 @@
         <v>70</v>
       </c>
       <c r="G93" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H93" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.45">
@@ -7503,15 +8740,15 @@
         <v>87</v>
       </c>
       <c r="G94" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H94" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B95">
         <v>62</v>
@@ -7531,15 +8768,15 @@
         <v>62</v>
       </c>
       <c r="G95" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H95" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B96">
         <v>48</v>
@@ -7559,10 +8796,10 @@
         <v>51</v>
       </c>
       <c r="G96" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H96" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.45">
@@ -7587,15 +8824,15 @@
         <v>76</v>
       </c>
       <c r="G97" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H97" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B98">
         <v>45</v>
@@ -7615,10 +8852,10 @@
         <v>57</v>
       </c>
       <c r="G98" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H98" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.45">
@@ -7643,10 +8880,10 @@
         <v>85</v>
       </c>
       <c r="G99" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H99" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.45">
@@ -7671,15 +8908,15 @@
         <v>76</v>
       </c>
       <c r="G100" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H100" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B101">
         <v>72</v>
@@ -7699,15 +8936,15 @@
         <v>72</v>
       </c>
       <c r="G101" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H101" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B102">
         <v>45</v>
@@ -7727,15 +8964,15 @@
         <v>57</v>
       </c>
       <c r="G102" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H102" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B103">
         <v>58</v>
@@ -7755,10 +8992,10 @@
         <v>66</v>
       </c>
       <c r="G103" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H103" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.45">
@@ -7783,15 +9020,15 @@
         <v>75</v>
       </c>
       <c r="G104" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H104" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B105">
         <v>66</v>
@@ -7811,15 +9048,15 @@
         <v>66</v>
       </c>
       <c r="G105" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H105" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B106">
         <v>70</v>
@@ -7839,10 +9076,10 @@
         <v>70</v>
       </c>
       <c r="G106" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H106" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.45">
@@ -7867,15 +9104,15 @@
         <v>87</v>
       </c>
       <c r="G107" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H107" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B108">
         <v>25</v>
@@ -7895,15 +9132,15 @@
         <v>71</v>
       </c>
       <c r="G108" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H108" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B109">
         <v>51</v>
@@ -7923,15 +9160,15 @@
         <v>51</v>
       </c>
       <c r="G109" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H109" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B110">
         <v>73</v>
@@ -7951,15 +9188,15 @@
         <v>73</v>
       </c>
       <c r="G110" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H110" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B111">
         <v>84</v>
@@ -7979,15 +9216,15 @@
         <v>91</v>
       </c>
       <c r="G111" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H111" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B112">
         <v>30</v>
@@ -8007,15 +9244,15 @@
         <v>72</v>
       </c>
       <c r="G112" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H112" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B113">
         <v>57</v>
@@ -8035,15 +9272,15 @@
         <v>70</v>
       </c>
       <c r="G113" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H113" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B114">
         <v>100</v>
@@ -8063,10 +9300,10 @@
         <v>100</v>
       </c>
       <c r="G114" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H114" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.45">
@@ -8091,10 +9328,10 @@
         <v>80</v>
       </c>
       <c r="G115" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H115" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.45">
@@ -8119,15 +9356,15 @@
         <v>88</v>
       </c>
       <c r="G116" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H116" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B117">
         <v>65</v>
@@ -8147,10 +9384,10 @@
         <v>65</v>
       </c>
       <c r="G117" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H117" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.45">
@@ -8175,15 +9412,15 @@
         <v>71</v>
       </c>
       <c r="G118" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H118" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B119">
         <v>42</v>
@@ -8203,15 +9440,15 @@
         <v>60</v>
       </c>
       <c r="G119" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H119" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B120">
         <v>32</v>
@@ -8231,10 +9468,10 @@
         <v>54</v>
       </c>
       <c r="G120" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H120" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.45">
@@ -8259,10 +9496,10 @@
         <v>80</v>
       </c>
       <c r="G121" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H121" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.45">
@@ -8287,15 +9524,15 @@
         <v>74</v>
       </c>
       <c r="G122" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H122" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B123">
         <v>40</v>
@@ -8315,15 +9552,15 @@
         <v>58</v>
       </c>
       <c r="G123" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H123" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B124">
         <v>30</v>
@@ -8343,15 +9580,15 @@
         <v>70</v>
       </c>
       <c r="G124" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H124" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B125">
         <v>60</v>
@@ -8371,15 +9608,15 @@
         <v>60</v>
       </c>
       <c r="G125" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H125" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B126">
         <v>55</v>
@@ -8399,10 +9636,10 @@
         <v>55</v>
       </c>
       <c r="G126" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H126" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.45">
@@ -8427,10 +9664,10 @@
         <v>72</v>
       </c>
       <c r="G127" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H127" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.45">
@@ -8455,15 +9692,15 @@
         <v>78</v>
       </c>
       <c r="G128" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H128" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B129">
         <v>60</v>
@@ -8483,10 +9720,10 @@
         <v>62</v>
       </c>
       <c r="G129" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H129" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.45">
@@ -8511,15 +9748,15 @@
         <v>78</v>
       </c>
       <c r="G130" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H130" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B131">
         <v>23</v>
@@ -8539,15 +9776,15 @@
         <v>46</v>
       </c>
       <c r="G131" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H131" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B132">
         <v>58</v>
@@ -8567,10 +9804,10 @@
         <v>71</v>
       </c>
       <c r="G132" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H132" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.45">
@@ -8595,15 +9832,15 @@
         <v>79</v>
       </c>
       <c r="G133" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H133" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B134">
         <v>25</v>
@@ -8623,15 +9860,15 @@
         <v>59</v>
       </c>
       <c r="G134" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H134" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B135">
         <v>72</v>
@@ -8651,10 +9888,10 @@
         <v>72</v>
       </c>
       <c r="G135" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H135" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.45">
@@ -8679,15 +9916,15 @@
         <v>92</v>
       </c>
       <c r="G136" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H136" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B137">
         <v>51</v>
@@ -8707,15 +9944,15 @@
         <v>60</v>
       </c>
       <c r="G137" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H137" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B138">
         <v>30</v>
@@ -8735,15 +9972,15 @@
         <v>63</v>
       </c>
       <c r="G138" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H138" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B139">
         <v>64</v>
@@ -8763,15 +10000,15 @@
         <v>64</v>
       </c>
       <c r="G139" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H139" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B140">
         <v>53</v>
@@ -8791,15 +10028,15 @@
         <v>55</v>
       </c>
       <c r="G140" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H140" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B141">
         <v>67</v>
@@ -8819,15 +10056,15 @@
         <v>67</v>
       </c>
       <c r="G141" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H141" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B142">
         <v>63</v>
@@ -8847,10 +10084,10 @@
         <v>63</v>
       </c>
       <c r="G142" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H142" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.45">
@@ -8875,15 +10112,15 @@
         <v>91</v>
       </c>
       <c r="G143" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H143" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B144">
         <v>22</v>
@@ -8903,15 +10140,15 @@
         <v>22</v>
       </c>
       <c r="G144" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H144" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B145">
         <v>58</v>
@@ -8931,10 +10168,10 @@
         <v>58</v>
       </c>
       <c r="G145" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H145" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.45">
@@ -8959,15 +10196,15 @@
         <v>85</v>
       </c>
       <c r="G146" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H146" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B147">
         <v>52</v>
@@ -8987,15 +10224,15 @@
         <v>52</v>
       </c>
       <c r="G147" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H147" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B148">
         <v>59</v>
@@ -9015,10 +10252,10 @@
         <v>59</v>
       </c>
       <c r="G148" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H148" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.45">
@@ -9043,15 +10280,15 @@
         <v>70</v>
       </c>
       <c r="G149" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H149" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B150">
         <v>58</v>
@@ -9071,15 +10308,15 @@
         <v>58</v>
       </c>
       <c r="G150" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H150" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B151">
         <v>80</v>
@@ -9099,15 +10336,15 @@
         <v>95</v>
       </c>
       <c r="G151" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H151" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B152">
         <v>32</v>
@@ -9127,15 +10364,15 @@
         <v>68</v>
       </c>
       <c r="G152" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H152" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B153">
         <v>63</v>
@@ -9155,15 +10392,15 @@
         <v>63</v>
       </c>
       <c r="G153" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H153" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B154">
         <v>28</v>
@@ -9183,15 +10420,15 @@
         <v>58</v>
       </c>
       <c r="G154" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H154" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B155">
         <v>70</v>
@@ -9211,15 +10448,15 @@
         <v>72</v>
       </c>
       <c r="G155" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H155" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B156">
         <v>54</v>
@@ -9239,10 +10476,10 @@
         <v>68</v>
       </c>
       <c r="G156" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H156" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.45">
@@ -9267,15 +10504,15 @@
         <v>75</v>
       </c>
       <c r="G157" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H157" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B158">
         <v>73</v>
@@ -9295,10 +10532,10 @@
         <v>73</v>
       </c>
       <c r="G158" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H158" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.45">
@@ -9323,10 +10560,10 @@
         <v>90</v>
       </c>
       <c r="G159" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H159" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.45">
@@ -9351,10 +10588,10 @@
         <v>79</v>
       </c>
       <c r="G160" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H160" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.45">
@@ -9379,15 +10616,15 @@
         <v>84</v>
       </c>
       <c r="G161" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H161" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B162">
         <v>72</v>
@@ -9407,15 +10644,15 @@
         <v>73</v>
       </c>
       <c r="G162" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H162" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B163">
         <v>68</v>
@@ -9435,10 +10672,10 @@
         <v>68</v>
       </c>
       <c r="G163" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H163" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.45">
@@ -9463,15 +10700,15 @@
         <v>88</v>
       </c>
       <c r="G164" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H164" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B165">
         <v>72</v>
@@ -9491,15 +10728,15 @@
         <v>72</v>
       </c>
       <c r="G165" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H165" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B166">
         <v>56</v>
@@ -9519,10 +10756,10 @@
         <v>56</v>
       </c>
       <c r="G166" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H166" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.45">
@@ -9547,7 +10784,7 @@
         <v>80</v>
       </c>
       <c r="G167" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H167" t="s">
         <v>233</v>
@@ -9555,7 +10792,7 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B168">
         <v>57</v>
@@ -9575,15 +10812,15 @@
         <v>57</v>
       </c>
       <c r="G168" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H168" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B169">
         <v>64</v>
@@ -9603,10 +10840,10 @@
         <v>64</v>
       </c>
       <c r="G169" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H169" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.45">
@@ -9631,10 +10868,10 @@
         <v>99</v>
       </c>
       <c r="G170" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H170" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.45">
@@ -9659,10 +10896,10 @@
         <v>92</v>
       </c>
       <c r="G171" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H171" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.45">
@@ -9687,10 +10924,10 @@
         <v>86</v>
       </c>
       <c r="G172" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H172" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.45">
@@ -9715,15 +10952,15 @@
         <v>74</v>
       </c>
       <c r="G173" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H173" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B174">
         <v>64</v>
@@ -9743,10 +10980,10 @@
         <v>64</v>
       </c>
       <c r="G174" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H174" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.45">
@@ -9771,15 +11008,15 @@
         <v>85</v>
       </c>
       <c r="G175" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H175" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B176">
         <v>90</v>
@@ -9799,7 +11036,7 @@
         <v>90</v>
       </c>
       <c r="G176" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H176" t="s">
         <v>47</v>
@@ -9807,7 +11044,7 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B177">
         <v>72</v>
@@ -9827,15 +11064,15 @@
         <v>72</v>
       </c>
       <c r="G177" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H177" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B178">
         <v>59</v>
@@ -9855,10 +11092,10 @@
         <v>60</v>
       </c>
       <c r="G178" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H178" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.45">
@@ -9883,10 +11120,10 @@
         <v>87</v>
       </c>
       <c r="G179" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H179" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.45">
@@ -9911,15 +11148,15 @@
         <v>92</v>
       </c>
       <c r="G180" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H180" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B181">
         <v>90</v>
@@ -9939,10 +11176,10 @@
         <v>90</v>
       </c>
       <c r="G181" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H181" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.45">
@@ -9967,15 +11204,15 @@
         <v>78</v>
       </c>
       <c r="G182" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H182" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B183">
         <v>67</v>
@@ -9995,10 +11232,10 @@
         <v>67</v>
       </c>
       <c r="G183" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H183" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.45">
@@ -10023,10 +11260,10 @@
         <v>85</v>
       </c>
       <c r="G184" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H184" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.45">
@@ -10051,15 +11288,15 @@
         <v>90</v>
       </c>
       <c r="G185" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H185" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B186">
         <v>70</v>
@@ -10079,10 +11316,10 @@
         <v>70</v>
       </c>
       <c r="G186" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H186" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.45">
@@ -10107,10 +11344,10 @@
         <v>81</v>
       </c>
       <c r="G187" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H187" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.45">
@@ -10135,10 +11372,10 @@
         <v>75</v>
       </c>
       <c r="G188" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H188" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.45">
@@ -10163,10 +11400,10 @@
         <v>90</v>
       </c>
       <c r="G189" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H189" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.45">
@@ -10191,15 +11428,15 @@
         <v>91</v>
       </c>
       <c r="G190" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H190" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B191">
         <v>44</v>
@@ -10219,15 +11456,15 @@
         <v>100</v>
       </c>
       <c r="G191" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H191" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B192">
         <v>60</v>
@@ -10247,15 +11484,15 @@
         <v>70</v>
       </c>
       <c r="G192" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H192" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B193">
         <v>52</v>
@@ -10275,15 +11512,15 @@
         <v>54</v>
       </c>
       <c r="G193" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H193" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B194">
         <v>68</v>
@@ -10303,15 +11540,15 @@
         <v>68</v>
       </c>
       <c r="G194" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H194" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B195">
         <v>70</v>
@@ -10331,15 +11568,15 @@
         <v>70</v>
       </c>
       <c r="G195" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H195" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B196">
         <v>60</v>
@@ -10359,10 +11596,10 @@
         <v>60</v>
       </c>
       <c r="G196" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H196" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.45">
@@ -10387,15 +11624,15 @@
         <v>78</v>
       </c>
       <c r="G197" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H197" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B198">
         <v>98</v>
@@ -10415,10 +11652,10 @@
         <v>98</v>
       </c>
       <c r="G198" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H198" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.45">
@@ -10443,15 +11680,15 @@
         <v>80</v>
       </c>
       <c r="G199" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H199" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B200">
         <v>63</v>
@@ -10471,15 +11708,15 @@
         <v>63</v>
       </c>
       <c r="G200" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H200" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B201">
         <v>75</v>
@@ -10499,10 +11736,10 @@
         <v>98</v>
       </c>
       <c r="G201" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H201" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.45">
@@ -10527,10 +11764,10 @@
         <v>88</v>
       </c>
       <c r="G202" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H202" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.45">
@@ -10555,15 +11792,15 @@
         <v>93</v>
       </c>
       <c r="G203" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H203" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B204">
         <v>52</v>
@@ -10583,15 +11820,15 @@
         <v>52</v>
       </c>
       <c r="G204" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H204" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B205">
         <v>55</v>
@@ -10611,10 +11848,10 @@
         <v>55</v>
       </c>
       <c r="G205" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H205" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.45">
@@ -10639,10 +11876,10 @@
         <v>74</v>
       </c>
       <c r="G206" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H206" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.45">
@@ -10667,15 +11904,15 @@
         <v>72</v>
       </c>
       <c r="G207" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H207" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B208">
         <v>51</v>
@@ -10695,15 +11932,15 @@
         <v>68</v>
       </c>
       <c r="G208" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H208" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B209">
         <v>66</v>
@@ -10723,10 +11960,10 @@
         <v>66</v>
       </c>
       <c r="G209" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H209" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.45">
@@ -10751,10 +11988,10 @@
         <v>70</v>
       </c>
       <c r="G210" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H210" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.45">
@@ -10779,15 +12016,15 @@
         <v>74</v>
       </c>
       <c r="G211" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H211" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A212" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B212">
         <v>75</v>
@@ -10807,10 +12044,10 @@
         <v>95</v>
       </c>
       <c r="G212" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H212" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.45">
@@ -10835,10 +12072,10 @@
         <v>85</v>
       </c>
       <c r="G213" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H213" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.45">
@@ -10863,10 +12100,10 @@
         <v>87</v>
       </c>
       <c r="G214" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H214" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.45">
@@ -10891,15 +12128,15 @@
         <v>74</v>
       </c>
       <c r="G215" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H215" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A216" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B216">
         <v>54</v>
@@ -10919,7 +12156,7 @@
         <v>85</v>
       </c>
       <c r="G216" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H216" t="s">
         <v>234</v>
@@ -10927,7 +12164,7 @@
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B217">
         <v>68</v>
@@ -10947,15 +12184,15 @@
         <v>68</v>
       </c>
       <c r="G217" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H217" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B218">
         <v>36</v>
@@ -10975,10 +12212,10 @@
         <v>70</v>
       </c>
       <c r="G218" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H218" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.45">
@@ -11003,15 +12240,15 @@
         <v>80</v>
       </c>
       <c r="G219" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H219" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B220">
         <v>69</v>
@@ -11031,15 +12268,15 @@
         <v>69</v>
       </c>
       <c r="G220" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H220" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B221">
         <v>65</v>
@@ -11059,15 +12296,15 @@
         <v>65</v>
       </c>
       <c r="G221" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H221" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B222">
         <v>67</v>
@@ -11087,15 +12324,15 @@
         <v>67</v>
       </c>
       <c r="G222" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H222" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B223">
         <v>63</v>
@@ -11115,15 +12352,15 @@
         <v>63</v>
       </c>
       <c r="G223" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H223" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B224">
         <v>58</v>
@@ -11143,15 +12380,15 @@
         <v>58</v>
       </c>
       <c r="G224" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H224" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B225">
         <v>35</v>
@@ -11171,10 +12408,10 @@
         <v>65</v>
       </c>
       <c r="G225" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H225" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.45">
@@ -11199,10 +12436,10 @@
         <v>72</v>
       </c>
       <c r="G226" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H226" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.45">
@@ -11227,15 +12464,15 @@
         <v>70</v>
       </c>
       <c r="G227" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H227" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A228" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B228">
         <v>53</v>
@@ -11255,15 +12492,15 @@
         <v>53</v>
       </c>
       <c r="G228" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H228" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A229" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B229">
         <v>51</v>
@@ -11283,15 +12520,15 @@
         <v>51</v>
       </c>
       <c r="G229" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H229" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A230" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B230">
         <v>65</v>
@@ -11311,15 +12548,15 @@
         <v>65</v>
       </c>
       <c r="G230" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H230" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A231" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B231">
         <v>65</v>
@@ -11339,10 +12576,10 @@
         <v>65</v>
       </c>
       <c r="G231" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H231" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.45">
@@ -11367,15 +12604,15 @@
         <v>82</v>
       </c>
       <c r="G232" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H232" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B233">
         <v>94</v>
@@ -11395,15 +12632,15 @@
         <v>94</v>
       </c>
       <c r="G233" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H233" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A234" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B234">
         <v>34</v>
@@ -11423,15 +12660,15 @@
         <v>62</v>
       </c>
       <c r="G234" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H234" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B235">
         <v>72</v>
@@ -11451,15 +12688,15 @@
         <v>72</v>
       </c>
       <c r="G235" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H235" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A236" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B236">
         <v>69</v>
@@ -11479,15 +12716,15 @@
         <v>69</v>
       </c>
       <c r="G236" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H236" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A237" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B237">
         <v>95</v>
@@ -11507,15 +12744,15 @@
         <v>95</v>
       </c>
       <c r="G237" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H237" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A238" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B238">
         <v>72</v>
@@ -11535,15 +12772,15 @@
         <v>72</v>
       </c>
       <c r="G238" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H238" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A239" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B239">
         <v>70</v>
@@ -11563,10 +12800,10 @@
         <v>70</v>
       </c>
       <c r="G239" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H239" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.45">
@@ -11591,15 +12828,15 @@
         <v>90</v>
       </c>
       <c r="G240" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H240" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B241">
         <v>60</v>
@@ -11619,15 +12856,15 @@
         <v>62</v>
       </c>
       <c r="G241" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H241" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A242" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B242">
         <v>60</v>
@@ -11647,10 +12884,10 @@
         <v>60</v>
       </c>
       <c r="G242" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H242" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.45">
@@ -11675,15 +12912,15 @@
         <v>91</v>
       </c>
       <c r="G243" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H243" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B244">
         <v>60</v>
@@ -11703,15 +12940,15 @@
         <v>60</v>
       </c>
       <c r="G244" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H244" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A245" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B245">
         <v>65</v>
@@ -11731,15 +12968,15 @@
         <v>65</v>
       </c>
       <c r="G245" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H245" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A246" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B246">
         <v>56</v>
@@ -11759,15 +12996,15 @@
         <v>56</v>
       </c>
       <c r="G246" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H246" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A247" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B247">
         <v>61</v>
@@ -11787,15 +13024,15 @@
         <v>61</v>
       </c>
       <c r="G247" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H247" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A248" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B248">
         <v>62</v>
@@ -11815,15 +13052,15 @@
         <v>62</v>
       </c>
       <c r="G248" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H248" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B249">
         <v>57</v>
@@ -11843,10 +13080,10 @@
         <v>57</v>
       </c>
       <c r="G249" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H249" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.45">
@@ -11871,15 +13108,15 @@
         <v>78</v>
       </c>
       <c r="G250" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H250" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A251" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B251">
         <v>45</v>
@@ -11899,15 +13136,15 @@
         <v>61</v>
       </c>
       <c r="G251" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H251" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A252" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B252">
         <v>97</v>
@@ -11927,15 +13164,15 @@
         <v>97</v>
       </c>
       <c r="G252" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H252" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B253">
         <v>1</v>
@@ -11955,10 +13192,10 @@
         <v>1</v>
       </c>
       <c r="G253" t="s">
+        <v>537</v>
+      </c>
+      <c r="H253" t="s">
         <v>538</v>
-      </c>
-      <c r="H253" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.45">
@@ -11983,15 +13220,15 @@
         <v>78</v>
       </c>
       <c r="G254" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H254" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A255" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B255">
         <v>58</v>
@@ -12011,10 +13248,10 @@
         <v>58</v>
       </c>
       <c r="G255" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H255" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.45">
@@ -12039,10 +13276,10 @@
         <v>90</v>
       </c>
       <c r="G256" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H256" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.45">
@@ -12067,10 +13304,10 @@
         <v>86</v>
       </c>
       <c r="G257" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H257" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.45">
@@ -12095,15 +13332,15 @@
         <v>84</v>
       </c>
       <c r="G258" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H258" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B259">
         <v>95</v>
@@ -12123,15 +13360,15 @@
         <v>95</v>
       </c>
       <c r="G259" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H259" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A260" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B260">
         <v>65</v>
@@ -12151,15 +13388,15 @@
         <v>65</v>
       </c>
       <c r="G260" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H260" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A261" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B261">
         <v>67</v>
@@ -12179,10 +13416,10 @@
         <v>67</v>
       </c>
       <c r="G261" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H261" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
   </sheetData>
@@ -12751,7 +13988,7 @@
       <c r="AA56" s="5"/>
       <c r="AB56" s="5"/>
       <c r="AH56" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="57" spans="5:34" x14ac:dyDescent="0.45">
@@ -12908,12 +14145,12 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">
@@ -12934,9 +14171,7 @@
       <c r="H21" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="J21" s="4" t="s">
-        <v>315</v>
-      </c>
+      <c r="J21" s="4"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
@@ -12948,9 +14183,7 @@
       <c r="H22" s="11">
         <v>3</v>
       </c>
-      <c r="J22" s="17">
-        <v>1</v>
-      </c>
+      <c r="J22" s="17"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
@@ -12962,9 +14195,7 @@
       <c r="H23" s="11">
         <v>5</v>
       </c>
-      <c r="J23" s="17">
-        <v>1</v>
-      </c>
+      <c r="J23" s="17"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="G24" s="11">
@@ -12973,9 +14204,7 @@
       <c r="H24" s="11">
         <v>8</v>
       </c>
-      <c r="J24" s="17">
-        <v>1</v>
-      </c>
+      <c r="J24" s="17"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="G25" s="11">
@@ -12984,60 +14213,73 @@
       <c r="H25" s="11">
         <v>10</v>
       </c>
-      <c r="J25" s="17">
-        <v>1</v>
-      </c>
+      <c r="J25" s="17"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="G26" s="11">
         <v>6</v>
       </c>
       <c r="H26" s="11">
-        <v>15</v>
-      </c>
-      <c r="J26" s="17">
-        <v>0.9</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="J26" s="17"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="G27" s="11">
         <v>7</v>
       </c>
       <c r="H27" s="11">
-        <v>20</v>
-      </c>
-      <c r="J27" s="17">
-        <v>0.7</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="J27" s="17"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="G28" s="11">
         <v>8</v>
       </c>
       <c r="H28" s="11">
-        <v>25</v>
-      </c>
-      <c r="J28" s="17">
-        <v>0.5</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="J28" s="17"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="G29" s="11">
         <v>9</v>
       </c>
       <c r="H29" s="11">
-        <v>30</v>
-      </c>
-      <c r="J29" s="17">
-        <v>0.3</v>
+        <v>25</v>
+      </c>
+      <c r="J29" s="17"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="H30" s="19">
+        <v>100</v>
+      </c>
+      <c r="I30" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="H31" s="19">
+        <v>260</v>
+      </c>
+      <c r="I31" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="H32">
+        <f>H30*H31</f>
+        <v>26000</v>
+      </c>
+      <c r="I32" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B33" s="16" t="s">
         <v>312</v>
       </c>
@@ -13053,8 +14295,15 @@
       <c r="F33" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="H33">
+        <f>H32/5</f>
+        <v>5200</v>
+      </c>
+      <c r="I33" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.45">
       <c r="C34">
         <v>1</v>
       </c>
@@ -13067,10 +14316,17 @@
       <c r="F34">
         <v>10</v>
       </c>
-    </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="H34">
+        <f>H33*30</f>
+        <v>156000</v>
+      </c>
+      <c r="I34" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B35">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C35">
         <v>2</v>
@@ -13084,10 +14340,17 @@
       <c r="F35">
         <v>30</v>
       </c>
-    </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="H35">
+        <f>H34*100</f>
+        <v>15600000</v>
+      </c>
+      <c r="I35" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B36">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C36">
         <v>3</v>
@@ -13101,10 +14364,17 @@
       <c r="F36">
         <v>60</v>
       </c>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="H36">
+        <f>H35/10000</f>
+        <v>1560</v>
+      </c>
+      <c r="I36" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B37">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="C37">
         <v>4</v>
@@ -13119,9 +14389,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B38">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="C38">
         <v>5</v>
@@ -13136,9 +14406,9 @@
         <v>120</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B39">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C39">
         <v>6</v>
@@ -13153,9 +14423,9 @@
         <v>150</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B40">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="C40">
         <v>7</v>
@@ -13170,9 +14440,9 @@
         <v>180</v>
       </c>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B41">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C41">
         <v>8</v>
@@ -13187,7 +14457,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B42">
         <v>50</v>
       </c>
@@ -13204,8 +14474,8 @@
         <v>260</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="45" spans="2:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="44" spans="2:9" ht="17.5" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="45" spans="2:9" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B45" s="12" t="s">
         <v>261</v>
       </c>
@@ -13219,7 +14489,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="46" spans="2:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="46" spans="2:9" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B46" s="12" t="s">
         <v>265</v>
       </c>
@@ -13233,7 +14503,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="47" spans="2:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="47" spans="2:9" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B47" s="12" t="s">
         <v>269</v>
       </c>
@@ -13247,7 +14517,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="48" spans="2:6" ht="28.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="48" spans="2:9" ht="28.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B48" s="12" t="s">
         <v>272</v>
       </c>

--- a/docs/삼국지 약식체스.xlsx
+++ b/docs/삼국지 약식체스.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\SamChess\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C3AD7A-2D46-4F5D-AE65-C12F0C57F7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6D0C2C-D4BC-48A2-8ACC-E9AE70E64477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="13770" xr2:uid="{67B41BAA-AEF2-4AF0-8CD2-0E8DEEEF200D}"/>
+    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="13770" activeTab="1" xr2:uid="{67B41BAA-AEF2-4AF0-8CD2-0E8DEEEF200D}"/>
   </bookViews>
   <sheets>
     <sheet name="고유 스킬" sheetId="1" r:id="rId1"/>
-    <sheet name="장수" sheetId="12" r:id="rId2"/>
-    <sheet name="병종" sheetId="6" r:id="rId3"/>
-    <sheet name="게임 환경" sheetId="7" r:id="rId4"/>
+    <sheet name="책략" sheetId="13" r:id="rId2"/>
+    <sheet name="장수" sheetId="12" r:id="rId3"/>
+    <sheet name="병종" sheetId="6" r:id="rId4"/>
+    <sheet name="게임 환경" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'고유 스킬'!$A$1:$E$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">장수!$A$1:$H$261</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">장수!$A$1:$H$261</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1841" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1912" uniqueCount="637">
   <si>
     <t>관우</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2158,6 +2159,122 @@
   </si>
   <si>
     <t>대기시간 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>증폭</t>
+  </si>
+  <si>
+    <t>아군 1명의 1회 공격을 Critical 100% 로 만들어줌</t>
+  </si>
+  <si>
+    <t>반감</t>
+  </si>
+  <si>
+    <t>아군 1명이 1번, 받는 데미지가 절반이 됨</t>
+  </si>
+  <si>
+    <t>회복</t>
+  </si>
+  <si>
+    <t>8방향 내 아군 1명의 HP 회복 (최대 체력의 20%)</t>
+  </si>
+  <si>
+    <t>결계</t>
+  </si>
+  <si>
+    <t>화계/진화</t>
+  </si>
+  <si>
+    <t>수계/매립</t>
+  </si>
+  <si>
+    <t>선공</t>
+  </si>
+  <si>
+    <t>대회복</t>
+  </si>
+  <si>
+    <t>8방향 내 아군들의 HP 회복 (최대 체력의 20%)</t>
+  </si>
+  <si>
+    <t>time 200 동안 아군 1명이 환술에 걸리지 않음. 모든 환술 무효</t>
+  </si>
+  <si>
+    <t>가로 1 x 세로 1 영역에 time 100 마다 HP 1씩 감소하는 지형 생성</t>
+  </si>
+  <si>
+    <t>맵 중 가로 1 x 세로 1 영역에 유닛을 위치시킬 수 없는 지형 생성</t>
+  </si>
+  <si>
+    <t>아군 1명의 waiting time -100</t>
+  </si>
+  <si>
+    <t>공포</t>
+  </si>
+  <si>
+    <t>time 200 동안 적군 1명의 공격력이 절반이 됨</t>
+  </si>
+  <si>
+    <t>침묵</t>
+  </si>
+  <si>
+    <t>time 200 동안 적군 1명이 버프/환술을 사용할 수 없음</t>
+  </si>
+  <si>
+    <t>함정</t>
+  </si>
+  <si>
+    <t>적군 1명의 waiting time +50, HP 1 감소</t>
+  </si>
+  <si>
+    <t>탈진</t>
+  </si>
+  <si>
+    <t>time 200 마다 체력이 1씩 감소 (결계로 해제 가능)</t>
+  </si>
+  <si>
+    <t>유인</t>
+  </si>
+  <si>
+    <t>적군 1명을 컨트롤: 이동만 가능</t>
+  </si>
+  <si>
+    <t>경직</t>
+  </si>
+  <si>
+    <t>적군 1명의 waiting time +100</t>
+  </si>
+  <si>
+    <t>질병</t>
+  </si>
+  <si>
+    <t>time 100 마다 체력이 1씩 감소 (결계로 해제 가능)</t>
+  </si>
+  <si>
+    <t>초선</t>
+  </si>
+  <si>
+    <t>적군 1명을 컨트롤: 이동+공격</t>
+  </si>
+  <si>
+    <t>환술</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지원책</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>환술 무효</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적 책략 차단</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3084,6 +3201,12 @@
       <c r="H13" s="20" t="s">
         <v>504</v>
       </c>
+      <c r="I13" t="s">
+        <v>600</v>
+      </c>
+      <c r="J13" t="s">
+        <v>573</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
@@ -6107,6 +6230,296 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3D48C68-D319-4AF3-B386-6DF7CD4EB588}">
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="59.08203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" style="20"/>
+    <col min="4" max="4" width="13.08203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>634</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>563</v>
+      </c>
+      <c r="D1" t="s">
+        <v>565</v>
+      </c>
+      <c r="E1" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>601</v>
+      </c>
+      <c r="B2" t="s">
+        <v>602</v>
+      </c>
+      <c r="C2" s="20">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>570</v>
+      </c>
+      <c r="E2" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>603</v>
+      </c>
+      <c r="B3" t="s">
+        <v>604</v>
+      </c>
+      <c r="C3" s="20">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>564</v>
+      </c>
+      <c r="E3" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>605</v>
+      </c>
+      <c r="B4" t="s">
+        <v>606</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="D4" t="s">
+        <v>590</v>
+      </c>
+      <c r="E4" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>607</v>
+      </c>
+      <c r="B5" t="s">
+        <v>613</v>
+      </c>
+      <c r="C5" s="20">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>635</v>
+      </c>
+      <c r="E5" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>608</v>
+      </c>
+      <c r="B6" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>609</v>
+      </c>
+      <c r="B7" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>610</v>
+      </c>
+      <c r="B8" t="s">
+        <v>616</v>
+      </c>
+      <c r="C8" s="20">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
+        <v>594</v>
+      </c>
+      <c r="E8" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>611</v>
+      </c>
+      <c r="B9" t="s">
+        <v>612</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="D9" t="s">
+        <v>590</v>
+      </c>
+      <c r="E9" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>617</v>
+      </c>
+      <c r="B12" t="s">
+        <v>618</v>
+      </c>
+      <c r="C12" s="20">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s">
+        <v>582</v>
+      </c>
+      <c r="E12" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>619</v>
+      </c>
+      <c r="B13" t="s">
+        <v>620</v>
+      </c>
+      <c r="C13" s="20">
+        <v>22</v>
+      </c>
+      <c r="D13" t="s">
+        <v>636</v>
+      </c>
+      <c r="E13" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>621</v>
+      </c>
+      <c r="B14" t="s">
+        <v>622</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="D14" t="s">
+        <v>599</v>
+      </c>
+      <c r="E14" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>623</v>
+      </c>
+      <c r="B15" t="s">
+        <v>624</v>
+      </c>
+      <c r="C15" s="20">
+        <v>2</v>
+      </c>
+      <c r="D15" t="s">
+        <v>566</v>
+      </c>
+      <c r="E15" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>625</v>
+      </c>
+      <c r="B16" t="s">
+        <v>626</v>
+      </c>
+      <c r="C16" s="20">
+        <v>6</v>
+      </c>
+      <c r="D16" t="s">
+        <v>577</v>
+      </c>
+      <c r="E16" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>627</v>
+      </c>
+      <c r="B17" t="s">
+        <v>628</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="D17" t="s">
+        <v>599</v>
+      </c>
+      <c r="E17" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>629</v>
+      </c>
+      <c r="B18" t="s">
+        <v>630</v>
+      </c>
+      <c r="C18" s="20">
+        <v>2</v>
+      </c>
+      <c r="D18" t="s">
+        <v>566</v>
+      </c>
+      <c r="E18" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>631</v>
+      </c>
+      <c r="B19" t="s">
+        <v>632</v>
+      </c>
+      <c r="C19" s="20">
+        <v>6</v>
+      </c>
+      <c r="D19" t="s">
+        <v>577</v>
+      </c>
+      <c r="E19" t="s">
+        <v>576</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{413B23C3-BFB5-4D1F-A1A8-907AD9A0F554}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:H261"/>
@@ -13428,7 +13841,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B91145DE-2075-4FE3-B1DF-72C643D3E6D5}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:AH61"/>
@@ -14047,7 +14460,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7648CCAC-7865-4F6B-8452-982C92F423A8}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:J58"/>

--- a/docs/삼국지 약식체스.xlsx
+++ b/docs/삼국지 약식체스.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\SamChess\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6D0C2C-D4BC-48A2-8ACC-E9AE70E64477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A71226D-21D8-4F9A-9666-A6CC70E3B619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="13770" activeTab="1" xr2:uid="{67B41BAA-AEF2-4AF0-8CD2-0E8DEEEF200D}"/>
+    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="13770" activeTab="2" xr2:uid="{67B41BAA-AEF2-4AF0-8CD2-0E8DEEEF200D}"/>
   </bookViews>
   <sheets>
     <sheet name="고유 스킬" sheetId="1" r:id="rId1"/>
     <sheet name="책략" sheetId="13" r:id="rId2"/>
-    <sheet name="장수" sheetId="12" r:id="rId3"/>
-    <sheet name="병종" sheetId="6" r:id="rId4"/>
-    <sheet name="게임 환경" sheetId="7" r:id="rId5"/>
+    <sheet name="오라이팩트매핑" sheetId="14" r:id="rId3"/>
+    <sheet name="장수" sheetId="12" r:id="rId4"/>
+    <sheet name="병종" sheetId="6" r:id="rId5"/>
+    <sheet name="게임 환경" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'고유 스킬'!$A$1:$E$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">장수!$A$1:$H$261</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">장수!$A$1:$H$261</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1912" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2613" uniqueCount="638">
   <si>
     <t>관우</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2275,6 +2276,10 @@
   </si>
   <si>
     <t>적 책략 차단</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용한 고유기술 리셋</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3564,7 +3569,7 @@
         <v>124</v>
       </c>
       <c r="H28" s="20">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="I28" t="s">
         <v>577</v>
@@ -3591,6 +3596,12 @@
       </c>
       <c r="H29" s="20" t="s">
         <v>538</v>
+      </c>
+      <c r="I29" t="s">
+        <v>637</v>
+      </c>
+      <c r="J29" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.45">
@@ -6453,7 +6464,7 @@
         <v>626</v>
       </c>
       <c r="C16" s="20">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s">
         <v>577</v>
@@ -6520,6 +6531,2708 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F18971D-0121-411B-B4B9-5D5AD91005D7}">
+  <dimension ref="A1:J148"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.1640625" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>563</v>
+      </c>
+      <c r="E1" t="s">
+        <v>565</v>
+      </c>
+      <c r="F1" t="s">
+        <v>580</v>
+      </c>
+      <c r="G1" t="s">
+        <v>563</v>
+      </c>
+      <c r="H1" t="s">
+        <v>580</v>
+      </c>
+      <c r="I1" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="20">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>564</v>
+      </c>
+      <c r="F2" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="20">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>572</v>
+      </c>
+      <c r="F3" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" s="20">
+        <v>2</v>
+      </c>
+      <c r="E4" t="s">
+        <v>566</v>
+      </c>
+      <c r="F4" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D5" s="20">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>592</v>
+      </c>
+      <c r="F5" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" s="20">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s">
+        <v>590</v>
+      </c>
+      <c r="F6" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" s="20">
+        <v>3</v>
+      </c>
+      <c r="E7" t="s">
+        <v>569</v>
+      </c>
+      <c r="F7" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D8" s="20">
+        <v>4</v>
+      </c>
+      <c r="E8" t="s">
+        <v>570</v>
+      </c>
+      <c r="F8" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="E9" t="s">
+        <v>590</v>
+      </c>
+      <c r="F9" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="20">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>564</v>
+      </c>
+      <c r="F10" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>87</v>
+      </c>
+      <c r="D11" s="20">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>564</v>
+      </c>
+      <c r="F11" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="E12" t="s">
+        <v>566</v>
+      </c>
+      <c r="F12" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>504</v>
+      </c>
+      <c r="E13" t="s">
+        <v>600</v>
+      </c>
+      <c r="F13" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="20">
+        <v>19</v>
+      </c>
+      <c r="E14" t="s">
+        <v>594</v>
+      </c>
+      <c r="F14" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" t="s">
+        <v>508</v>
+      </c>
+      <c r="D15" s="20">
+        <v>2</v>
+      </c>
+      <c r="E15" t="s">
+        <v>566</v>
+      </c>
+      <c r="F15" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" t="s">
+        <v>555</v>
+      </c>
+      <c r="D16" s="20">
+        <v>6</v>
+      </c>
+      <c r="E16" t="s">
+        <v>577</v>
+      </c>
+      <c r="F16" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" s="20">
+        <v>7</v>
+      </c>
+      <c r="E17" t="s">
+        <v>579</v>
+      </c>
+      <c r="F17" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" s="20">
+        <v>7</v>
+      </c>
+      <c r="E18" t="s">
+        <v>595</v>
+      </c>
+      <c r="F18" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" t="s">
+        <v>117</v>
+      </c>
+      <c r="C19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D19" s="20">
+        <v>8</v>
+      </c>
+      <c r="E19" t="s">
+        <v>581</v>
+      </c>
+      <c r="F19" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="20">
+        <v>9</v>
+      </c>
+      <c r="E20" t="s">
+        <v>582</v>
+      </c>
+      <c r="F20" t="s">
+        <v>583</v>
+      </c>
+      <c r="G20" s="20">
+        <v>10</v>
+      </c>
+      <c r="H20" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1</v>
+      </c>
+      <c r="D21" s="20">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>584</v>
+      </c>
+      <c r="F21" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="E22" t="s">
+        <v>599</v>
+      </c>
+      <c r="F22" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="20">
+        <v>12</v>
+      </c>
+      <c r="E23" t="s">
+        <v>585</v>
+      </c>
+      <c r="F23" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="20">
+        <v>4</v>
+      </c>
+      <c r="E24" t="s">
+        <v>570</v>
+      </c>
+      <c r="F24" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" s="20">
+        <v>4</v>
+      </c>
+      <c r="E25" t="s">
+        <v>570</v>
+      </c>
+      <c r="F25" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26" s="20">
+        <v>23</v>
+      </c>
+      <c r="E26" t="s">
+        <v>577</v>
+      </c>
+      <c r="F26" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>538</v>
+      </c>
+      <c r="E27" t="s">
+        <v>637</v>
+      </c>
+      <c r="F27" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28" t="s">
+        <v>101</v>
+      </c>
+      <c r="D28" s="20">
+        <v>13</v>
+      </c>
+      <c r="E28" t="s">
+        <v>586</v>
+      </c>
+      <c r="F28" t="s">
+        <v>583</v>
+      </c>
+      <c r="G28" s="20">
+        <v>6</v>
+      </c>
+      <c r="H28" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" t="s">
+        <v>115</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" t="s">
+        <v>121</v>
+      </c>
+      <c r="C30" t="s">
+        <v>122</v>
+      </c>
+      <c r="D30" s="20">
+        <v>15</v>
+      </c>
+      <c r="E30" t="s">
+        <v>588</v>
+      </c>
+      <c r="F30" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" t="s">
+        <v>125</v>
+      </c>
+      <c r="C31" t="s">
+        <v>126</v>
+      </c>
+      <c r="D31" s="20">
+        <v>16</v>
+      </c>
+      <c r="E31" t="s">
+        <v>589</v>
+      </c>
+      <c r="F31" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>233</v>
+      </c>
+      <c r="B32" t="s">
+        <v>175</v>
+      </c>
+      <c r="C32" t="s">
+        <v>235</v>
+      </c>
+      <c r="D32" s="20">
+        <v>4</v>
+      </c>
+      <c r="E32" t="s">
+        <v>570</v>
+      </c>
+      <c r="F32" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>233</v>
+      </c>
+      <c r="B33" t="s">
+        <v>187</v>
+      </c>
+      <c r="C33" t="s">
+        <v>235</v>
+      </c>
+      <c r="D33" s="20">
+        <v>4</v>
+      </c>
+      <c r="E33" t="s">
+        <v>570</v>
+      </c>
+      <c r="F33" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>233</v>
+      </c>
+      <c r="B34" t="s">
+        <v>158</v>
+      </c>
+      <c r="C34" t="s">
+        <v>235</v>
+      </c>
+      <c r="D34" s="20">
+        <v>4</v>
+      </c>
+      <c r="E34" t="s">
+        <v>570</v>
+      </c>
+      <c r="F34" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>233</v>
+      </c>
+      <c r="B35" t="s">
+        <v>163</v>
+      </c>
+      <c r="C35" t="s">
+        <v>235</v>
+      </c>
+      <c r="D35" s="20">
+        <v>4</v>
+      </c>
+      <c r="E35" t="s">
+        <v>570</v>
+      </c>
+      <c r="F35" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>233</v>
+      </c>
+      <c r="B36" t="s">
+        <v>155</v>
+      </c>
+      <c r="C36" t="s">
+        <v>235</v>
+      </c>
+      <c r="D36" s="20">
+        <v>4</v>
+      </c>
+      <c r="E36" t="s">
+        <v>570</v>
+      </c>
+      <c r="F36" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>233</v>
+      </c>
+      <c r="B37" t="s">
+        <v>146</v>
+      </c>
+      <c r="C37" t="s">
+        <v>235</v>
+      </c>
+      <c r="D37" s="20">
+        <v>4</v>
+      </c>
+      <c r="E37" t="s">
+        <v>570</v>
+      </c>
+      <c r="F37" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>233</v>
+      </c>
+      <c r="B38" t="s">
+        <v>140</v>
+      </c>
+      <c r="C38" t="s">
+        <v>235</v>
+      </c>
+      <c r="D38" s="20">
+        <v>4</v>
+      </c>
+      <c r="E38" t="s">
+        <v>570</v>
+      </c>
+      <c r="F38" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>233</v>
+      </c>
+      <c r="B39" t="s">
+        <v>216</v>
+      </c>
+      <c r="C39" t="s">
+        <v>235</v>
+      </c>
+      <c r="D39" s="20">
+        <v>4</v>
+      </c>
+      <c r="E39" t="s">
+        <v>570</v>
+      </c>
+      <c r="F39" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>233</v>
+      </c>
+      <c r="B40" t="s">
+        <v>226</v>
+      </c>
+      <c r="C40" t="s">
+        <v>235</v>
+      </c>
+      <c r="D40" s="20">
+        <v>4</v>
+      </c>
+      <c r="E40" t="s">
+        <v>570</v>
+      </c>
+      <c r="F40" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>233</v>
+      </c>
+      <c r="B41" t="s">
+        <v>213</v>
+      </c>
+      <c r="C41" t="s">
+        <v>235</v>
+      </c>
+      <c r="D41" s="20">
+        <v>4</v>
+      </c>
+      <c r="E41" t="s">
+        <v>570</v>
+      </c>
+      <c r="F41" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>233</v>
+      </c>
+      <c r="B42" t="s">
+        <v>166</v>
+      </c>
+      <c r="C42" t="s">
+        <v>237</v>
+      </c>
+      <c r="D42" s="20">
+        <v>8</v>
+      </c>
+      <c r="E42" t="s">
+        <v>581</v>
+      </c>
+      <c r="F42" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>233</v>
+      </c>
+      <c r="B43" t="s">
+        <v>189</v>
+      </c>
+      <c r="C43" t="s">
+        <v>237</v>
+      </c>
+      <c r="D43" s="20">
+        <v>8</v>
+      </c>
+      <c r="E43" t="s">
+        <v>581</v>
+      </c>
+      <c r="F43" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>233</v>
+      </c>
+      <c r="B44" t="s">
+        <v>190</v>
+      </c>
+      <c r="C44" t="s">
+        <v>237</v>
+      </c>
+      <c r="D44" s="20">
+        <v>8</v>
+      </c>
+      <c r="E44" t="s">
+        <v>581</v>
+      </c>
+      <c r="F44" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>233</v>
+      </c>
+      <c r="B45" t="s">
+        <v>160</v>
+      </c>
+      <c r="C45" t="s">
+        <v>237</v>
+      </c>
+      <c r="D45" s="20">
+        <v>8</v>
+      </c>
+      <c r="E45" t="s">
+        <v>581</v>
+      </c>
+      <c r="F45" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>233</v>
+      </c>
+      <c r="B46" t="s">
+        <v>167</v>
+      </c>
+      <c r="C46" t="s">
+        <v>237</v>
+      </c>
+      <c r="D46" s="20">
+        <v>8</v>
+      </c>
+      <c r="E46" t="s">
+        <v>581</v>
+      </c>
+      <c r="F46" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>233</v>
+      </c>
+      <c r="B47" t="s">
+        <v>141</v>
+      </c>
+      <c r="C47" t="s">
+        <v>237</v>
+      </c>
+      <c r="D47" s="20">
+        <v>8</v>
+      </c>
+      <c r="E47" t="s">
+        <v>581</v>
+      </c>
+      <c r="F47" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>233</v>
+      </c>
+      <c r="B48" t="s">
+        <v>225</v>
+      </c>
+      <c r="C48" t="s">
+        <v>239</v>
+      </c>
+      <c r="D48" s="20">
+        <v>1</v>
+      </c>
+      <c r="E48" t="s">
+        <v>564</v>
+      </c>
+      <c r="F48" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>233</v>
+      </c>
+      <c r="B49" t="s">
+        <v>151</v>
+      </c>
+      <c r="C49" t="s">
+        <v>239</v>
+      </c>
+      <c r="D49" s="20">
+        <v>1</v>
+      </c>
+      <c r="E49" t="s">
+        <v>564</v>
+      </c>
+      <c r="F49" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>233</v>
+      </c>
+      <c r="B50" t="s">
+        <v>211</v>
+      </c>
+      <c r="C50" t="s">
+        <v>239</v>
+      </c>
+      <c r="D50" s="20">
+        <v>1</v>
+      </c>
+      <c r="E50" t="s">
+        <v>564</v>
+      </c>
+      <c r="F50" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>233</v>
+      </c>
+      <c r="B51" t="s">
+        <v>207</v>
+      </c>
+      <c r="C51" t="s">
+        <v>239</v>
+      </c>
+      <c r="D51" s="20">
+        <v>1</v>
+      </c>
+      <c r="E51" t="s">
+        <v>564</v>
+      </c>
+      <c r="F51" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>233</v>
+      </c>
+      <c r="B52" t="s">
+        <v>162</v>
+      </c>
+      <c r="C52" t="s">
+        <v>239</v>
+      </c>
+      <c r="D52" s="20">
+        <v>1</v>
+      </c>
+      <c r="E52" t="s">
+        <v>564</v>
+      </c>
+      <c r="F52" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>233</v>
+      </c>
+      <c r="B53" t="s">
+        <v>192</v>
+      </c>
+      <c r="C53" t="s">
+        <v>239</v>
+      </c>
+      <c r="D53" s="20">
+        <v>1</v>
+      </c>
+      <c r="E53" t="s">
+        <v>564</v>
+      </c>
+      <c r="F53" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>233</v>
+      </c>
+      <c r="B54" t="s">
+        <v>212</v>
+      </c>
+      <c r="C54" t="s">
+        <v>239</v>
+      </c>
+      <c r="D54" s="20">
+        <v>1</v>
+      </c>
+      <c r="E54" t="s">
+        <v>564</v>
+      </c>
+      <c r="F54" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>233</v>
+      </c>
+      <c r="B55" t="s">
+        <v>147</v>
+      </c>
+      <c r="C55" t="s">
+        <v>239</v>
+      </c>
+      <c r="D55" s="20">
+        <v>1</v>
+      </c>
+      <c r="E55" t="s">
+        <v>564</v>
+      </c>
+      <c r="F55" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>233</v>
+      </c>
+      <c r="B56" t="s">
+        <v>188</v>
+      </c>
+      <c r="C56" t="s">
+        <v>239</v>
+      </c>
+      <c r="D56" s="20">
+        <v>1</v>
+      </c>
+      <c r="E56" t="s">
+        <v>564</v>
+      </c>
+      <c r="F56" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>233</v>
+      </c>
+      <c r="B57" t="s">
+        <v>139</v>
+      </c>
+      <c r="C57" t="s">
+        <v>239</v>
+      </c>
+      <c r="D57" s="20">
+        <v>1</v>
+      </c>
+      <c r="E57" t="s">
+        <v>564</v>
+      </c>
+      <c r="F57" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>233</v>
+      </c>
+      <c r="B58" t="s">
+        <v>194</v>
+      </c>
+      <c r="C58" t="s">
+        <v>239</v>
+      </c>
+      <c r="D58" s="20">
+        <v>1</v>
+      </c>
+      <c r="E58" t="s">
+        <v>564</v>
+      </c>
+      <c r="F58" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>233</v>
+      </c>
+      <c r="B59" t="s">
+        <v>145</v>
+      </c>
+      <c r="C59" t="s">
+        <v>239</v>
+      </c>
+      <c r="D59" s="20">
+        <v>1</v>
+      </c>
+      <c r="E59" t="s">
+        <v>564</v>
+      </c>
+      <c r="F59" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>233</v>
+      </c>
+      <c r="B60" t="s">
+        <v>144</v>
+      </c>
+      <c r="C60" t="s">
+        <v>239</v>
+      </c>
+      <c r="D60" s="20">
+        <v>1</v>
+      </c>
+      <c r="E60" t="s">
+        <v>564</v>
+      </c>
+      <c r="F60" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>233</v>
+      </c>
+      <c r="B61" t="s">
+        <v>197</v>
+      </c>
+      <c r="C61" t="s">
+        <v>239</v>
+      </c>
+      <c r="D61" s="20">
+        <v>1</v>
+      </c>
+      <c r="E61" t="s">
+        <v>564</v>
+      </c>
+      <c r="F61" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>233</v>
+      </c>
+      <c r="B62" t="s">
+        <v>224</v>
+      </c>
+      <c r="C62" t="s">
+        <v>242</v>
+      </c>
+      <c r="D62" s="20">
+        <v>20</v>
+      </c>
+      <c r="E62" t="s">
+        <v>598</v>
+      </c>
+      <c r="F62" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>233</v>
+      </c>
+      <c r="B63" t="s">
+        <v>223</v>
+      </c>
+      <c r="C63" t="s">
+        <v>242</v>
+      </c>
+      <c r="D63" s="20">
+        <v>20</v>
+      </c>
+      <c r="E63" t="s">
+        <v>598</v>
+      </c>
+      <c r="F63" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A64" t="s">
+        <v>233</v>
+      </c>
+      <c r="B64" t="s">
+        <v>200</v>
+      </c>
+      <c r="C64" t="s">
+        <v>242</v>
+      </c>
+      <c r="D64" s="20">
+        <v>20</v>
+      </c>
+      <c r="E64" t="s">
+        <v>597</v>
+      </c>
+      <c r="F64" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
+        <v>233</v>
+      </c>
+      <c r="B65" t="s">
+        <v>556</v>
+      </c>
+      <c r="C65" t="s">
+        <v>242</v>
+      </c>
+      <c r="D65" s="20">
+        <v>20</v>
+      </c>
+      <c r="E65" t="s">
+        <v>597</v>
+      </c>
+      <c r="F65" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>233</v>
+      </c>
+      <c r="B66" t="s">
+        <v>231</v>
+      </c>
+      <c r="C66" t="s">
+        <v>242</v>
+      </c>
+      <c r="D66" s="20">
+        <v>20</v>
+      </c>
+      <c r="E66" t="s">
+        <v>597</v>
+      </c>
+      <c r="F66" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>233</v>
+      </c>
+      <c r="B67" t="s">
+        <v>206</v>
+      </c>
+      <c r="C67" t="s">
+        <v>242</v>
+      </c>
+      <c r="D67" s="20">
+        <v>20</v>
+      </c>
+      <c r="E67" t="s">
+        <v>597</v>
+      </c>
+      <c r="F67" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
+        <v>233</v>
+      </c>
+      <c r="B68" t="s">
+        <v>161</v>
+      </c>
+      <c r="C68" t="s">
+        <v>242</v>
+      </c>
+      <c r="D68" s="20">
+        <v>20</v>
+      </c>
+      <c r="E68" t="s">
+        <v>597</v>
+      </c>
+      <c r="F68" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
+        <v>233</v>
+      </c>
+      <c r="B69" t="s">
+        <v>203</v>
+      </c>
+      <c r="C69" t="s">
+        <v>242</v>
+      </c>
+      <c r="D69" s="20">
+        <v>20</v>
+      </c>
+      <c r="E69" t="s">
+        <v>597</v>
+      </c>
+      <c r="F69" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A70" t="s">
+        <v>233</v>
+      </c>
+      <c r="B70" t="s">
+        <v>204</v>
+      </c>
+      <c r="C70" t="s">
+        <v>242</v>
+      </c>
+      <c r="D70" s="20">
+        <v>20</v>
+      </c>
+      <c r="E70" t="s">
+        <v>597</v>
+      </c>
+      <c r="F70" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
+        <v>233</v>
+      </c>
+      <c r="B71" t="s">
+        <v>229</v>
+      </c>
+      <c r="C71" t="s">
+        <v>242</v>
+      </c>
+      <c r="D71" s="20">
+        <v>20</v>
+      </c>
+      <c r="E71" t="s">
+        <v>597</v>
+      </c>
+      <c r="F71" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A72" t="s">
+        <v>234</v>
+      </c>
+      <c r="B72" t="s">
+        <v>214</v>
+      </c>
+      <c r="C72" t="s">
+        <v>244</v>
+      </c>
+      <c r="D72" s="20">
+        <v>19</v>
+      </c>
+      <c r="E72" t="s">
+        <v>594</v>
+      </c>
+      <c r="F72" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A73" t="s">
+        <v>234</v>
+      </c>
+      <c r="B73" t="s">
+        <v>186</v>
+      </c>
+      <c r="C73" t="s">
+        <v>244</v>
+      </c>
+      <c r="D73" s="20">
+        <v>19</v>
+      </c>
+      <c r="E73" t="s">
+        <v>594</v>
+      </c>
+      <c r="F73" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
+        <v>234</v>
+      </c>
+      <c r="B74" t="s">
+        <v>153</v>
+      </c>
+      <c r="C74" t="s">
+        <v>244</v>
+      </c>
+      <c r="D74" s="20">
+        <v>19</v>
+      </c>
+      <c r="E74" t="s">
+        <v>594</v>
+      </c>
+      <c r="F74" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A75" t="s">
+        <v>234</v>
+      </c>
+      <c r="B75" t="s">
+        <v>230</v>
+      </c>
+      <c r="C75" t="s">
+        <v>244</v>
+      </c>
+      <c r="D75" s="20">
+        <v>19</v>
+      </c>
+      <c r="E75" t="s">
+        <v>594</v>
+      </c>
+      <c r="F75" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A76" t="s">
+        <v>234</v>
+      </c>
+      <c r="B76" t="s">
+        <v>181</v>
+      </c>
+      <c r="C76" t="s">
+        <v>244</v>
+      </c>
+      <c r="D76" s="20">
+        <v>19</v>
+      </c>
+      <c r="E76" t="s">
+        <v>594</v>
+      </c>
+      <c r="F76" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A77" t="s">
+        <v>234</v>
+      </c>
+      <c r="B77" t="s">
+        <v>143</v>
+      </c>
+      <c r="C77" t="s">
+        <v>244</v>
+      </c>
+      <c r="D77" s="20">
+        <v>19</v>
+      </c>
+      <c r="E77" t="s">
+        <v>594</v>
+      </c>
+      <c r="F77" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A78" t="s">
+        <v>234</v>
+      </c>
+      <c r="B78" t="s">
+        <v>221</v>
+      </c>
+      <c r="C78" t="s">
+        <v>244</v>
+      </c>
+      <c r="D78" s="20">
+        <v>19</v>
+      </c>
+      <c r="E78" t="s">
+        <v>594</v>
+      </c>
+      <c r="F78" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A79" t="s">
+        <v>234</v>
+      </c>
+      <c r="B79" t="s">
+        <v>154</v>
+      </c>
+      <c r="C79" t="s">
+        <v>244</v>
+      </c>
+      <c r="D79" s="20">
+        <v>19</v>
+      </c>
+      <c r="E79" t="s">
+        <v>594</v>
+      </c>
+      <c r="F79" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A80" t="s">
+        <v>234</v>
+      </c>
+      <c r="B80" t="s">
+        <v>201</v>
+      </c>
+      <c r="C80" t="s">
+        <v>244</v>
+      </c>
+      <c r="D80" s="20">
+        <v>19</v>
+      </c>
+      <c r="E80" t="s">
+        <v>594</v>
+      </c>
+      <c r="F80" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A81" t="s">
+        <v>234</v>
+      </c>
+      <c r="B81" t="s">
+        <v>195</v>
+      </c>
+      <c r="C81" t="s">
+        <v>254</v>
+      </c>
+      <c r="D81" s="20">
+        <v>4</v>
+      </c>
+      <c r="E81" t="s">
+        <v>570</v>
+      </c>
+      <c r="F81" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A82" t="s">
+        <v>234</v>
+      </c>
+      <c r="B82" t="s">
+        <v>179</v>
+      </c>
+      <c r="C82" t="s">
+        <v>254</v>
+      </c>
+      <c r="D82" s="20">
+        <v>4</v>
+      </c>
+      <c r="E82" t="s">
+        <v>570</v>
+      </c>
+      <c r="F82" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A83" t="s">
+        <v>234</v>
+      </c>
+      <c r="B83" t="s">
+        <v>209</v>
+      </c>
+      <c r="C83" t="s">
+        <v>254</v>
+      </c>
+      <c r="D83" s="20">
+        <v>4</v>
+      </c>
+      <c r="E83" t="s">
+        <v>570</v>
+      </c>
+      <c r="F83" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A84" t="s">
+        <v>234</v>
+      </c>
+      <c r="B84" t="s">
+        <v>199</v>
+      </c>
+      <c r="C84" t="s">
+        <v>254</v>
+      </c>
+      <c r="D84" s="20">
+        <v>4</v>
+      </c>
+      <c r="E84" t="s">
+        <v>570</v>
+      </c>
+      <c r="F84" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A85" t="s">
+        <v>234</v>
+      </c>
+      <c r="B85" t="s">
+        <v>148</v>
+      </c>
+      <c r="C85" t="s">
+        <v>254</v>
+      </c>
+      <c r="D85" s="20">
+        <v>4</v>
+      </c>
+      <c r="E85" t="s">
+        <v>570</v>
+      </c>
+      <c r="F85" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A86" t="s">
+        <v>234</v>
+      </c>
+      <c r="B86" t="s">
+        <v>178</v>
+      </c>
+      <c r="C86" t="s">
+        <v>254</v>
+      </c>
+      <c r="D86" s="20">
+        <v>4</v>
+      </c>
+      <c r="E86" t="s">
+        <v>570</v>
+      </c>
+      <c r="F86" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A87" t="s">
+        <v>234</v>
+      </c>
+      <c r="B87" t="s">
+        <v>218</v>
+      </c>
+      <c r="C87" t="s">
+        <v>254</v>
+      </c>
+      <c r="D87" s="20">
+        <v>4</v>
+      </c>
+      <c r="E87" t="s">
+        <v>570</v>
+      </c>
+      <c r="F87" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A88" t="s">
+        <v>234</v>
+      </c>
+      <c r="B88" t="s">
+        <v>174</v>
+      </c>
+      <c r="C88" t="s">
+        <v>254</v>
+      </c>
+      <c r="D88" s="20">
+        <v>4</v>
+      </c>
+      <c r="E88" t="s">
+        <v>570</v>
+      </c>
+      <c r="F88" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A89" t="s">
+        <v>234</v>
+      </c>
+      <c r="B89" t="s">
+        <v>180</v>
+      </c>
+      <c r="C89" t="s">
+        <v>254</v>
+      </c>
+      <c r="D89" s="20">
+        <v>4</v>
+      </c>
+      <c r="E89" t="s">
+        <v>570</v>
+      </c>
+      <c r="F89" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A90" t="s">
+        <v>234</v>
+      </c>
+      <c r="B90" t="s">
+        <v>219</v>
+      </c>
+      <c r="C90" t="s">
+        <v>254</v>
+      </c>
+      <c r="D90" s="20">
+        <v>4</v>
+      </c>
+      <c r="E90" t="s">
+        <v>570</v>
+      </c>
+      <c r="F90" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A91" t="s">
+        <v>234</v>
+      </c>
+      <c r="B91" t="s">
+        <v>202</v>
+      </c>
+      <c r="C91" t="s">
+        <v>257</v>
+      </c>
+      <c r="D91" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="E91" t="s">
+        <v>599</v>
+      </c>
+      <c r="F91" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A92" t="s">
+        <v>234</v>
+      </c>
+      <c r="B92" t="s">
+        <v>172</v>
+      </c>
+      <c r="C92" t="s">
+        <v>257</v>
+      </c>
+      <c r="D92" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="E92" t="s">
+        <v>599</v>
+      </c>
+      <c r="F92" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A93" t="s">
+        <v>234</v>
+      </c>
+      <c r="B93" t="s">
+        <v>227</v>
+      </c>
+      <c r="C93" t="s">
+        <v>257</v>
+      </c>
+      <c r="D93" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="E93" t="s">
+        <v>599</v>
+      </c>
+      <c r="F93" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A94" t="s">
+        <v>234</v>
+      </c>
+      <c r="B94" t="s">
+        <v>169</v>
+      </c>
+      <c r="C94" t="s">
+        <v>257</v>
+      </c>
+      <c r="D94" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="E94" t="s">
+        <v>599</v>
+      </c>
+      <c r="F94" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A95" t="s">
+        <v>234</v>
+      </c>
+      <c r="B95" t="s">
+        <v>152</v>
+      </c>
+      <c r="C95" t="s">
+        <v>257</v>
+      </c>
+      <c r="D95" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="E95" t="s">
+        <v>599</v>
+      </c>
+      <c r="F95" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A96" t="s">
+        <v>234</v>
+      </c>
+      <c r="B96" t="s">
+        <v>149</v>
+      </c>
+      <c r="C96" t="s">
+        <v>257</v>
+      </c>
+      <c r="D96" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="E96" t="s">
+        <v>599</v>
+      </c>
+      <c r="F96" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A97" t="s">
+        <v>234</v>
+      </c>
+      <c r="B97" t="s">
+        <v>184</v>
+      </c>
+      <c r="C97" t="s">
+        <v>257</v>
+      </c>
+      <c r="D97" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="E97" t="s">
+        <v>599</v>
+      </c>
+      <c r="F97" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A98" t="s">
+        <v>234</v>
+      </c>
+      <c r="B98" t="s">
+        <v>164</v>
+      </c>
+      <c r="C98" t="s">
+        <v>257</v>
+      </c>
+      <c r="D98" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="E98" t="s">
+        <v>599</v>
+      </c>
+      <c r="F98" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A99" t="s">
+        <v>234</v>
+      </c>
+      <c r="B99" t="s">
+        <v>191</v>
+      </c>
+      <c r="C99" t="s">
+        <v>257</v>
+      </c>
+      <c r="D99" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="E99" t="s">
+        <v>599</v>
+      </c>
+      <c r="F99" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A100" t="s">
+        <v>234</v>
+      </c>
+      <c r="B100" t="s">
+        <v>150</v>
+      </c>
+      <c r="C100" t="s">
+        <v>257</v>
+      </c>
+      <c r="D100" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="E100" t="s">
+        <v>599</v>
+      </c>
+      <c r="F100" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A101" t="s">
+        <v>234</v>
+      </c>
+      <c r="B101" t="s">
+        <v>506</v>
+      </c>
+      <c r="C101" t="s">
+        <v>257</v>
+      </c>
+      <c r="D101" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="E101" t="s">
+        <v>599</v>
+      </c>
+      <c r="F101" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A102" t="s">
+        <v>234</v>
+      </c>
+      <c r="B102" t="s">
+        <v>176</v>
+      </c>
+      <c r="C102" t="s">
+        <v>257</v>
+      </c>
+      <c r="D102" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="E102" t="s">
+        <v>599</v>
+      </c>
+      <c r="F102" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A103" t="s">
+        <v>234</v>
+      </c>
+      <c r="B103" t="s">
+        <v>232</v>
+      </c>
+      <c r="C103" t="s">
+        <v>248</v>
+      </c>
+      <c r="D103" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="E103" t="s">
+        <v>590</v>
+      </c>
+      <c r="F103" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A104" t="s">
+        <v>234</v>
+      </c>
+      <c r="B104" t="s">
+        <v>205</v>
+      </c>
+      <c r="C104" t="s">
+        <v>248</v>
+      </c>
+      <c r="D104" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="E104" t="s">
+        <v>590</v>
+      </c>
+      <c r="F104" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A105" t="s">
+        <v>234</v>
+      </c>
+      <c r="B105" t="s">
+        <v>193</v>
+      </c>
+      <c r="C105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D105" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="E105" t="s">
+        <v>590</v>
+      </c>
+      <c r="F105" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A106" t="s">
+        <v>234</v>
+      </c>
+      <c r="B106" t="s">
+        <v>177</v>
+      </c>
+      <c r="C106" t="s">
+        <v>248</v>
+      </c>
+      <c r="D106" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="E106" t="s">
+        <v>590</v>
+      </c>
+      <c r="F106" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A107" t="s">
+        <v>234</v>
+      </c>
+      <c r="B107" t="s">
+        <v>222</v>
+      </c>
+      <c r="C107" t="s">
+        <v>248</v>
+      </c>
+      <c r="D107" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="E107" t="s">
+        <v>590</v>
+      </c>
+      <c r="F107" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A108" t="s">
+        <v>234</v>
+      </c>
+      <c r="B108" t="s">
+        <v>142</v>
+      </c>
+      <c r="C108" t="s">
+        <v>248</v>
+      </c>
+      <c r="D108" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="E108" t="s">
+        <v>590</v>
+      </c>
+      <c r="F108" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A109" t="s">
+        <v>234</v>
+      </c>
+      <c r="B109" t="s">
+        <v>168</v>
+      </c>
+      <c r="C109" t="s">
+        <v>248</v>
+      </c>
+      <c r="D109" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="E109" t="s">
+        <v>590</v>
+      </c>
+      <c r="F109" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A110" t="s">
+        <v>234</v>
+      </c>
+      <c r="B110" t="s">
+        <v>165</v>
+      </c>
+      <c r="C110" t="s">
+        <v>248</v>
+      </c>
+      <c r="D110" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="E110" t="s">
+        <v>590</v>
+      </c>
+      <c r="F110" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A111" t="s">
+        <v>234</v>
+      </c>
+      <c r="B111" t="s">
+        <v>185</v>
+      </c>
+      <c r="C111" t="s">
+        <v>248</v>
+      </c>
+      <c r="D111" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="E111" t="s">
+        <v>590</v>
+      </c>
+      <c r="F111" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A112" t="s">
+        <v>234</v>
+      </c>
+      <c r="B112" t="s">
+        <v>198</v>
+      </c>
+      <c r="C112" t="s">
+        <v>248</v>
+      </c>
+      <c r="D112" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="E112" t="s">
+        <v>590</v>
+      </c>
+      <c r="F112" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A113" t="s">
+        <v>234</v>
+      </c>
+      <c r="B113" t="s">
+        <v>156</v>
+      </c>
+      <c r="C113" t="s">
+        <v>248</v>
+      </c>
+      <c r="D113" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="E113" t="s">
+        <v>590</v>
+      </c>
+      <c r="F113" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A114" t="s">
+        <v>234</v>
+      </c>
+      <c r="B114" t="s">
+        <v>157</v>
+      </c>
+      <c r="C114" t="s">
+        <v>248</v>
+      </c>
+      <c r="D114" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="E114" t="s">
+        <v>590</v>
+      </c>
+      <c r="F114" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A115" t="s">
+        <v>234</v>
+      </c>
+      <c r="B115" t="s">
+        <v>196</v>
+      </c>
+      <c r="C115" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A116" t="s">
+        <v>234</v>
+      </c>
+      <c r="B116" t="s">
+        <v>210</v>
+      </c>
+      <c r="C116" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A117" t="s">
+        <v>234</v>
+      </c>
+      <c r="B117" t="s">
+        <v>183</v>
+      </c>
+      <c r="C117" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A118" t="s">
+        <v>234</v>
+      </c>
+      <c r="B118" t="s">
+        <v>228</v>
+      </c>
+      <c r="C118" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A119" t="s">
+        <v>234</v>
+      </c>
+      <c r="B119" t="s">
+        <v>171</v>
+      </c>
+      <c r="C119" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A120" t="s">
+        <v>234</v>
+      </c>
+      <c r="B120" t="s">
+        <v>220</v>
+      </c>
+      <c r="C120" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A121" t="s">
+        <v>234</v>
+      </c>
+      <c r="B121" t="s">
+        <v>217</v>
+      </c>
+      <c r="C121" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A122" t="s">
+        <v>234</v>
+      </c>
+      <c r="B122" t="s">
+        <v>173</v>
+      </c>
+      <c r="C122" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A123" t="s">
+        <v>234</v>
+      </c>
+      <c r="B123" t="s">
+        <v>208</v>
+      </c>
+      <c r="C123" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A124" t="s">
+        <v>234</v>
+      </c>
+      <c r="B124" t="s">
+        <v>182</v>
+      </c>
+      <c r="C124" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A125" t="s">
+        <v>234</v>
+      </c>
+      <c r="B125" t="s">
+        <v>159</v>
+      </c>
+      <c r="C125" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A126" t="s">
+        <v>234</v>
+      </c>
+      <c r="B126" t="s">
+        <v>170</v>
+      </c>
+      <c r="C126" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A127" t="s">
+        <v>538</v>
+      </c>
+      <c r="B127" t="s">
+        <v>536</v>
+      </c>
+      <c r="C127" t="s">
+        <v>539</v>
+      </c>
+      <c r="D127">
+        <v>3</v>
+      </c>
+      <c r="E127" t="s">
+        <v>569</v>
+      </c>
+      <c r="F127" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A130" t="s">
+        <v>634</v>
+      </c>
+      <c r="D130" s="20" t="s">
+        <v>563</v>
+      </c>
+      <c r="E130" t="s">
+        <v>565</v>
+      </c>
+      <c r="F130" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C131" t="s">
+        <v>601</v>
+      </c>
+      <c r="D131" s="20">
+        <v>4</v>
+      </c>
+      <c r="E131" t="s">
+        <v>570</v>
+      </c>
+      <c r="F131" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C132" t="s">
+        <v>603</v>
+      </c>
+      <c r="D132" s="20">
+        <v>1</v>
+      </c>
+      <c r="E132" t="s">
+        <v>564</v>
+      </c>
+      <c r="F132" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C133" t="s">
+        <v>605</v>
+      </c>
+      <c r="D133" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="E133" t="s">
+        <v>590</v>
+      </c>
+      <c r="F133" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C134" t="s">
+        <v>607</v>
+      </c>
+      <c r="D134" s="20">
+        <v>21</v>
+      </c>
+      <c r="E134" t="s">
+        <v>635</v>
+      </c>
+      <c r="F134" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C135" t="s">
+        <v>608</v>
+      </c>
+      <c r="D135" s="20"/>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C136" t="s">
+        <v>609</v>
+      </c>
+      <c r="D136" s="20"/>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C137" t="s">
+        <v>610</v>
+      </c>
+      <c r="D137" s="20">
+        <v>19</v>
+      </c>
+      <c r="E137" t="s">
+        <v>594</v>
+      </c>
+      <c r="F137" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C138" t="s">
+        <v>611</v>
+      </c>
+      <c r="D138" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="E138" t="s">
+        <v>590</v>
+      </c>
+      <c r="F138" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="D139" s="20"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A140" t="s">
+        <v>633</v>
+      </c>
+      <c r="D140" s="20"/>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C141" t="s">
+        <v>617</v>
+      </c>
+      <c r="D141" s="20">
+        <v>9</v>
+      </c>
+      <c r="E141" t="s">
+        <v>582</v>
+      </c>
+      <c r="F141" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C142" t="s">
+        <v>619</v>
+      </c>
+      <c r="D142" s="20">
+        <v>22</v>
+      </c>
+      <c r="E142" t="s">
+        <v>636</v>
+      </c>
+      <c r="F142" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C143" t="s">
+        <v>621</v>
+      </c>
+      <c r="D143" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="E143" t="s">
+        <v>599</v>
+      </c>
+      <c r="F143" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C144" t="s">
+        <v>623</v>
+      </c>
+      <c r="D144" s="20">
+        <v>2</v>
+      </c>
+      <c r="E144" t="s">
+        <v>566</v>
+      </c>
+      <c r="F144" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="145" spans="3:6" x14ac:dyDescent="0.45">
+      <c r="C145" t="s">
+        <v>625</v>
+      </c>
+      <c r="D145" s="20">
+        <v>23</v>
+      </c>
+      <c r="E145" t="s">
+        <v>577</v>
+      </c>
+      <c r="F145" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="146" spans="3:6" x14ac:dyDescent="0.45">
+      <c r="C146" t="s">
+        <v>627</v>
+      </c>
+      <c r="D146" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="E146" t="s">
+        <v>599</v>
+      </c>
+      <c r="F146" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="147" spans="3:6" x14ac:dyDescent="0.45">
+      <c r="C147" t="s">
+        <v>629</v>
+      </c>
+      <c r="D147" s="20">
+        <v>2</v>
+      </c>
+      <c r="E147" t="s">
+        <v>566</v>
+      </c>
+      <c r="F147" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="148" spans="3:6" x14ac:dyDescent="0.45">
+      <c r="C148" t="s">
+        <v>631</v>
+      </c>
+      <c r="D148" s="20">
+        <v>6</v>
+      </c>
+      <c r="E148" t="s">
+        <v>577</v>
+      </c>
+      <c r="F148" t="s">
+        <v>576</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{413B23C3-BFB5-4D1F-A1A8-907AD9A0F554}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:H261"/>
@@ -13841,7 +16554,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B91145DE-2075-4FE3-B1DF-72C643D3E6D5}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:AH61"/>
@@ -14460,7 +17173,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7648CCAC-7865-4F6B-8452-982C92F423A8}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:J58"/>

--- a/docs/삼국지 약식체스.xlsx
+++ b/docs/삼국지 약식체스.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\SamChess\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A71226D-21D8-4F9A-9666-A6CC70E3B619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC304F9D-4B0D-40A9-ACDE-119792005746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="13770" activeTab="2" xr2:uid="{67B41BAA-AEF2-4AF0-8CD2-0E8DEEEF200D}"/>
+    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="13770" activeTab="1" xr2:uid="{67B41BAA-AEF2-4AF0-8CD2-0E8DEEEF200D}"/>
   </bookViews>
   <sheets>
     <sheet name="고유 스킬" sheetId="1" r:id="rId1"/>
     <sheet name="책략" sheetId="13" r:id="rId2"/>
-    <sheet name="오라이팩트매핑" sheetId="14" r:id="rId3"/>
+    <sheet name="오라매핑" sheetId="14" r:id="rId3"/>
     <sheet name="장수" sheetId="12" r:id="rId4"/>
     <sheet name="병종" sheetId="6" r:id="rId5"/>
     <sheet name="게임 환경" sheetId="7" r:id="rId6"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2613" uniqueCount="638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2649" uniqueCount="641">
   <si>
     <t>관우</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2280,6 +2280,18 @@
   </si>
   <si>
     <t>사용한 고유기술 리셋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>G</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SP 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적 SP</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6003,6 +6015,15 @@
       <c r="E127" t="s">
         <v>258</v>
       </c>
+      <c r="H127" s="20" t="s">
+        <v>638</v>
+      </c>
+      <c r="I127" t="s">
+        <v>639</v>
+      </c>
+      <c r="J127" t="s">
+        <v>640</v>
+      </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
@@ -6020,6 +6041,15 @@
       <c r="E128" t="s">
         <v>258</v>
       </c>
+      <c r="H128" s="20" t="s">
+        <v>638</v>
+      </c>
+      <c r="I128" t="s">
+        <v>639</v>
+      </c>
+      <c r="J128" t="s">
+        <v>640</v>
+      </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
@@ -6037,6 +6067,15 @@
       <c r="E129" t="s">
         <v>553</v>
       </c>
+      <c r="H129" s="20" t="s">
+        <v>638</v>
+      </c>
+      <c r="I129" t="s">
+        <v>639</v>
+      </c>
+      <c r="J129" t="s">
+        <v>640</v>
+      </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
@@ -6054,6 +6093,15 @@
       <c r="E130" t="s">
         <v>553</v>
       </c>
+      <c r="H130" s="20" t="s">
+        <v>638</v>
+      </c>
+      <c r="I130" t="s">
+        <v>639</v>
+      </c>
+      <c r="J130" t="s">
+        <v>640</v>
+      </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
@@ -6071,6 +6119,15 @@
       <c r="E131" t="s">
         <v>553</v>
       </c>
+      <c r="H131" s="20" t="s">
+        <v>638</v>
+      </c>
+      <c r="I131" t="s">
+        <v>639</v>
+      </c>
+      <c r="J131" t="s">
+        <v>640</v>
+      </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
@@ -6088,6 +6145,15 @@
       <c r="E132" t="s">
         <v>553</v>
       </c>
+      <c r="H132" s="20" t="s">
+        <v>638</v>
+      </c>
+      <c r="I132" t="s">
+        <v>639</v>
+      </c>
+      <c r="J132" t="s">
+        <v>640</v>
+      </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
@@ -6105,6 +6171,15 @@
       <c r="E133" t="s">
         <v>553</v>
       </c>
+      <c r="H133" s="20" t="s">
+        <v>638</v>
+      </c>
+      <c r="I133" t="s">
+        <v>639</v>
+      </c>
+      <c r="J133" t="s">
+        <v>640</v>
+      </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
@@ -6122,6 +6197,15 @@
       <c r="E134" t="s">
         <v>553</v>
       </c>
+      <c r="H134" s="20" t="s">
+        <v>638</v>
+      </c>
+      <c r="I134" t="s">
+        <v>639</v>
+      </c>
+      <c r="J134" t="s">
+        <v>640</v>
+      </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
@@ -6139,6 +6223,15 @@
       <c r="E135" t="s">
         <v>553</v>
       </c>
+      <c r="H135" s="20" t="s">
+        <v>638</v>
+      </c>
+      <c r="I135" t="s">
+        <v>639</v>
+      </c>
+      <c r="J135" t="s">
+        <v>640</v>
+      </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
@@ -6156,6 +6249,15 @@
       <c r="E136" t="s">
         <v>553</v>
       </c>
+      <c r="H136" s="20" t="s">
+        <v>638</v>
+      </c>
+      <c r="I136" t="s">
+        <v>639</v>
+      </c>
+      <c r="J136" t="s">
+        <v>640</v>
+      </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
@@ -6173,6 +6275,15 @@
       <c r="E137" t="s">
         <v>553</v>
       </c>
+      <c r="H137" s="20" t="s">
+        <v>638</v>
+      </c>
+      <c r="I137" t="s">
+        <v>639</v>
+      </c>
+      <c r="J137" t="s">
+        <v>640</v>
+      </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
@@ -6190,6 +6301,18 @@
       <c r="E138" t="s">
         <v>553</v>
       </c>
+      <c r="H138" s="20" t="s">
+        <v>638</v>
+      </c>
+      <c r="I138" t="s">
+        <v>639</v>
+      </c>
+      <c r="J138" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="H139" s="20"/>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A140" t="s">

--- a/docs/삼국지 약식체스.xlsx
+++ b/docs/삼국지 약식체스.xlsx
@@ -398,11 +398,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>單齒渡江</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>단치도강</t>
+    <t>單騎渡江</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>단기도강</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -966,11 +966,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내 차례가 한 번 돌아올 동안 waiting time -30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아무 위치에 있는 적군 1명의 waiting time +50</t>
+    <t>내 차례가 한 번 돌아올 동안 waiting time -50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아무 위치에 있는 적군 1명의 waiting time +90</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1886,7 +1886,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>맵 중 1칸에 time 100 마다 HP 1씩 회복되는 지형을 만듦</t>
+    <t>맵 중 1칸에 time 90 마다 HP 1씩 회복되는 지형을 만듦</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1906,7 +1906,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>모든 적군의 waiting time + 110 (한턴 쉬는 효과)</t>
+    <t>모든 적군의 waiting time + 150 (한턴 쉬는 효과)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1958,13 +1958,13 @@
     <t>time 190 동안 책략/환술 시 MP 소모량 0</t>
   </si>
   <si>
-    <t>내 차례가 한 번 돌아올 동안 waiting time -30</t>
+    <t>내 차례가 한 번 돌아올 동안 waiting time -50</t>
   </si>
   <si>
     <t>time 90 동안 Critical 100% 발동</t>
   </si>
   <si>
-    <t>아무 위치에 있는 적군 1명의 waiting time +50</t>
+    <t>아무 위치에 있는 적군 1명의 waiting time +90</t>
   </si>
   <si>
     <t>자신 포함 주변 8방향에 있는 아군들이 HP 1씩 회복</t>
@@ -1973,7 +1973,7 @@
     <t>적의 SP 값을 1 내린다.</t>
   </si>
   <si>
-    <t>적군 1명을 지정. 그 적은 게임이 끝날 때 까지 time 200 마다 HP 1 감소</t>
+    <t>적군 1명을 지정. 그 적은 게임이 끝날 때 까지 time 110 마다 HP 1 감소</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>

--- a/docs/삼국지 약식체스.xlsx
+++ b/docs/삼국지 약식체스.xlsx
@@ -19,6 +19,7 @@
     <sheet name="장수" sheetId="12" r:id="rId4"/>
     <sheet name="병종" sheetId="6" r:id="rId5"/>
     <sheet name="게임 환경" sheetId="7" r:id="rId6"/>
+    <sheet name="도시 건물" sheetId="15" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'고유 스킬'!$A$1:$E$31</definedName>
@@ -18052,4 +18053,952 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K44"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="4" width="14" customWidth="1"/>
+    <col min="11" max="11" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도시 건물 — 2026-09-04 확정 (GDD §5 · pptx 54~59쪽)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[1] 도시 레벨</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">레벨이 정하는 것은 증축 자재와 건물 해금 게이트 둘뿐이다</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">레벨</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">증축 자재</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시작 레벨</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>6</v>
+      </c>
+      <c r="B10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>8</v>
+      </c>
+      <c r="B12">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>9</v>
+      </c>
+      <c r="B13">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>10</v>
+      </c>
+      <c r="B14">
+        <v>50</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">황궁 — 헌제를 보유해야 갈 수 있다</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[2] 건물 해금</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">칸의 값 = 그 건물 레벨에 필요한 도시 레벨. 빈 칸은 기본 건물이라 건설 행동이 없다는 뜻</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">건물</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">종류</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lv1</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lv2</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lv3</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lv4</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lv5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">궁궐</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">palace</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기본</t>
+        </is>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18">
+        <v>4</v>
+      </c>
+      <c r="G18">
+        <v>7</v>
+      </c>
+      <c r="H18">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">병영</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barracks</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기본</t>
+        </is>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19">
+        <v>5</v>
+      </c>
+      <c r="G19">
+        <v>7</v>
+      </c>
+      <c r="H19">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시장</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">market</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기본</t>
+        </is>
+      </c>
+      <c r="E20">
+        <v>3</v>
+      </c>
+      <c r="F20">
+        <v>5</v>
+      </c>
+      <c r="G20">
+        <v>7</v>
+      </c>
+      <c r="H20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">태학</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">academy</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">추가</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>3</v>
+      </c>
+      <c r="F21">
+        <v>5</v>
+      </c>
+      <c r="G21">
+        <v>8</v>
+      </c>
+      <c r="H21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농지</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">farm</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">추가</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>3</v>
+      </c>
+      <c r="F22">
+        <v>6</v>
+      </c>
+      <c r="G22">
+        <v>8</v>
+      </c>
+      <c r="H22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">병원</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hospital</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">추가</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>4</v>
+      </c>
+      <c r="F23">
+        <v>6</v>
+      </c>
+      <c r="G23">
+        <v>8</v>
+      </c>
+      <c r="H23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대장간</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">forge</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">추가</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24">
+        <v>4</v>
+      </c>
+      <c r="F24">
+        <v>6</v>
+      </c>
+      <c r="G24">
+        <v>9</v>
+      </c>
+      <c r="H24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[3] 건물 효과</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「없음」은 그 건물을 짓지 않았을 때의 값. 기본 건물은 언제나 있으므로 빈 칸이다</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">건물</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">효과</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">단위</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">없음</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lv1</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lv2</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lv3</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lv4</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lv5</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">궁궐</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">palace</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 풀</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">명</t>
+        </is>
+      </c>
+      <c r="F28">
+        <v>60</v>
+      </c>
+      <c r="G28">
+        <v>110</v>
+      </c>
+      <c r="H28">
+        <v>160</v>
+      </c>
+      <c r="I28">
+        <v>210</v>
+      </c>
+      <c r="J28">
+        <v>260</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lv5가 전체 장수 260과 같다</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">병영</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barracks</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최대 군량</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">군량</t>
+        </is>
+      </c>
+      <c r="F29">
+        <v>20</v>
+      </c>
+      <c r="G29">
+        <v>40</v>
+      </c>
+      <c r="H29">
+        <v>60</v>
+      </c>
+      <c r="I29">
+        <v>80</v>
+      </c>
+      <c r="J29">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농지</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">farm</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시간당 군량</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">군량/시간</t>
+        </is>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>2</v>
+      </c>
+      <c r="G30">
+        <v>4</v>
+      </c>
+      <c r="H30">
+        <v>6</v>
+      </c>
+      <c r="I30">
+        <v>8</v>
+      </c>
+      <c r="J30">
+        <v>10</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">없어도 1은 찬다</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">병원</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hospital</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">치료 room</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개</t>
+        </is>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <v>2</v>
+      </c>
+      <c r="H31">
+        <v>3</v>
+      </c>
+      <c r="I31">
+        <v>4</v>
+      </c>
+      <c r="J31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">태학</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">academy</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">훈련 보정</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">능력치</t>
+        </is>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>2</v>
+      </c>
+      <c r="G32">
+        <v>4</v>
+      </c>
+      <c r="H32">
+        <v>6</v>
+      </c>
+      <c r="I32">
+        <v>8</v>
+      </c>
+      <c r="J32">
+        <v>10</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">쓰임새는 태학 화면을 설계할 때 정한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시장</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">market</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구매 아이템</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">종류</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">품목 표 미정</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대장간</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">forge</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구매 장비</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">종류</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">품목 표 미정</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[4] 상수</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">항목</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">값</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">단위</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">황궁 해금 도시 레벨</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">emperorCityLevel</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>10</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">레벨</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">헌제가 없으면 Lv9가 상한이다</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">증축당 건설 기회</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buildActionsPerUpgrade</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>3</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">회</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">쌓인다. 황궁 레벨에서는 제한이 풀린다</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부대 저장 개수</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">squadCap</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>10</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도시 레벨과 무관하게 고정</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부상 능력치 감소</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">injuryPenalty</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>10</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">무·지·통 각</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하한 1. 헌제는 부상하지 않는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부상 자연 회복</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">injuryRecoverMin</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>60</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">분</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">장수마다 따로 돈다</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">병원 치료 소요</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">healMin</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">분</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">즉시가 아니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">병원 room 쿨타임</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roomCooldownMin</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>5</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">분</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">재사용 주기는 치료 1분 + 쿨 5분 = 6분</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/docs/삼국지 약식체스.xlsx
+++ b/docs/삼국지 약식체스.xlsx
@@ -18057,7 +18057,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -18192,12 +18192,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">[2] 건물 해금</t>
+          <t xml:space="preserve">[2] 건물</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">칸의 값 = 그 건물 레벨에 필요한 도시 레벨. 빈 칸은 기본 건물이라 건설 행동이 없다는 뜻</t>
+          <t xml:space="preserve">기본 건물은 도시 Lv1부터 Lv1 상태로 있다. 추가 건물은 지어야 생기고 지으면 Lv1이다</t>
         </is>
       </c>
     </row>
@@ -18219,27 +18219,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lv1</t>
+          <t xml:space="preserve">최대 레벨</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lv2</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lv3</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lv4</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lv5</t>
+          <t xml:space="preserve">비고</t>
         </is>
       </c>
     </row>
@@ -18259,17 +18244,8 @@
           <t xml:space="preserve">기본</t>
         </is>
       </c>
-      <c r="E18">
-        <v>2</v>
-      </c>
-      <c r="F18">
-        <v>4</v>
-      </c>
-      <c r="G18">
-        <v>7</v>
-      </c>
-      <c r="H18">
-        <v>9</v>
+      <c r="D18">
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -18288,17 +18264,8 @@
           <t xml:space="preserve">기본</t>
         </is>
       </c>
-      <c r="E19">
-        <v>2</v>
-      </c>
-      <c r="F19">
+      <c r="D19">
         <v>5</v>
-      </c>
-      <c r="G19">
-        <v>7</v>
-      </c>
-      <c r="H19">
-        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -18317,17 +18284,8 @@
           <t xml:space="preserve">기본</t>
         </is>
       </c>
-      <c r="E20">
-        <v>3</v>
-      </c>
-      <c r="F20">
+      <c r="D20">
         <v>5</v>
-      </c>
-      <c r="G20">
-        <v>7</v>
-      </c>
-      <c r="H20">
-        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -18347,19 +18305,7 @@
         </is>
       </c>
       <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21">
-        <v>3</v>
-      </c>
-      <c r="F21">
         <v>5</v>
-      </c>
-      <c r="G21">
-        <v>8</v>
-      </c>
-      <c r="H21">
-        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -18379,19 +18325,7 @@
         </is>
       </c>
       <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22">
-        <v>3</v>
-      </c>
-      <c r="F22">
-        <v>6</v>
-      </c>
-      <c r="G22">
-        <v>8</v>
-      </c>
-      <c r="H22">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -18411,19 +18345,7 @@
         </is>
       </c>
       <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="E23">
-        <v>4</v>
-      </c>
-      <c r="F23">
-        <v>6</v>
-      </c>
-      <c r="G23">
-        <v>8</v>
-      </c>
-      <c r="H23">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -18443,19 +18365,7 @@
         </is>
       </c>
       <c r="D24">
-        <v>2</v>
-      </c>
-      <c r="E24">
-        <v>4</v>
-      </c>
-      <c r="F24">
-        <v>6</v>
-      </c>
-      <c r="G24">
-        <v>9</v>
-      </c>
-      <c r="H24">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -18852,116 +18762,116 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t xml:space="preserve">건설·증축 가능 도시 레벨</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buildCityLevel</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">레벨</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그 아래에서는 기본 건물 셋만 Lv1로 있다</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t xml:space="preserve">증축당 건설 기회</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t xml:space="preserve">buildActionsPerUpgrade</t>
         </is>
       </c>
-      <c r="C39">
+      <c r="C40">
         <v>3</v>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t xml:space="preserve">회</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t xml:space="preserve">쌓인다. 황궁 레벨에서는 제한이 풀린다</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t xml:space="preserve">부대 저장 개수</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t xml:space="preserve">squadCap</t>
         </is>
       </c>
-      <c r="C40">
+      <c r="C41">
         <v>10</v>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t xml:space="preserve">도시 레벨과 무관하게 고정</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t xml:space="preserve">부상 능력치 감소</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t xml:space="preserve">injuryPenalty</t>
         </is>
       </c>
-      <c r="C41">
+      <c r="C42">
         <v>10</v>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t xml:space="preserve">무·지·통 각</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t xml:space="preserve">하한 1. 헌제는 부상하지 않는다</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t xml:space="preserve">부상 자연 회복</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t xml:space="preserve">injuryRecoverMin</t>
         </is>
       </c>
-      <c r="C42">
+      <c r="C43">
         <v>60</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">분</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">장수마다 따로 돈다</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">병원 치료 소요</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">healMin</t>
-        </is>
-      </c>
-      <c r="C43">
-        <v>1</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -18970,23 +18880,23 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">즉시가 아니다</t>
+          <t xml:space="preserve">장수마다 따로 돈다</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">병원 room 쿨타임</t>
+          <t xml:space="preserve">병원 치료 소요</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">roomCooldownMin</t>
+          <t xml:space="preserve">healMin</t>
         </is>
       </c>
       <c r="C44">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -18995,6 +18905,31 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t xml:space="preserve">즉시가 아니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">병원 room 쿨타임</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roomCooldownMin</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>5</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">분</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t xml:space="preserve">재사용 주기는 치료 1분 + 쿨 5분 = 6분</t>
         </is>
       </c>

--- a/docs/삼국지 약식체스.xlsx
+++ b/docs/삼국지 약식체스.xlsx
@@ -18224,7 +18224,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">비고</t>
+          <t xml:space="preserve">안 지었을 때 보여 줄 말</t>
         </is>
       </c>
     </row>
@@ -18307,6 +18307,11 @@
       <c r="D21">
         <v>5</v>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">장수 훈련 가능</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -18327,6 +18332,11 @@
       <c r="D22">
         <v>5</v>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시간당 군량 증가 1</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -18347,6 +18357,11 @@
       <c r="D23">
         <v>5</v>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부상 장수 치료 가능</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
